--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33FEEAC-0E83-4D60-9238-76D1D843E7AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9123456-D840-475D-B245-839243D8B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="relations_daily" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="322">
   <si>
     <t>data</t>
   </si>
@@ -921,6 +921,123 @@
   </si>
   <si>
     <t>AZUL age de forma responsável e alinhada com os princípios humanitários.</t>
+  </si>
+  <si>
+    <t>Atualização (28 Out 25)</t>
+  </si>
+  <si>
+    <t>Incidente Marítimo: Desaparecimento de navio Vermelho gera crise diplomática; Azul responde com transparência e operações de busca e salvamento.</t>
+  </si>
+  <si>
+    <t>Desaparecimento de navio Vermelho</t>
+  </si>
+  <si>
+    <t>político</t>
+  </si>
+  <si>
+    <t>false flag</t>
+  </si>
+  <si>
+    <t>OCOR 02</t>
+  </si>
+  <si>
+    <t>Reação positiva natural à transparência e às buscas promovidas por AZUL</t>
+  </si>
+  <si>
+    <t>Crise Humanitária em Topázio e Registro-SP:
+Tempestades e surto de cólera deflagram disputa entre Azul e Vermelho por legitimidade na ajuda humanitária.</t>
+  </si>
+  <si>
+    <t>Crise Humanitária em Topázio e Registro-SP</t>
+  </si>
+  <si>
+    <t>Assuntos Civis; Aj Humanitária</t>
+  </si>
+  <si>
+    <t>Campanha de Comunicação e Narrativas Internacionais:
+Ambos os lados travam guerra informacional buscando reconhecimento e apoio da comunidade internacional.</t>
+  </si>
+  <si>
+    <t>Campanha de Comunicação e Narrativas Internacionais</t>
+  </si>
+  <si>
+    <t>Op Info</t>
+  </si>
+  <si>
+    <t>Respostas às Aç dos partidos em busca de legitimidade</t>
+  </si>
+  <si>
+    <t>Respostas às Aç Informacionais desempenhadas pelos partidos</t>
+  </si>
+  <si>
+    <t>Guerra Cibernética:
+Ataques e defesas no ciberespaço visam sistemas de comando, infraestrutura e informações estratégicas.</t>
+  </si>
+  <si>
+    <t>Guerra Cibernética</t>
+  </si>
+  <si>
+    <t>Ciber</t>
+  </si>
+  <si>
+    <t>Respostas às Aç de Cibernética desempenhadas pelos partidos</t>
+  </si>
+  <si>
+    <t>Guerra Eletrônica e Neutralização de C²:
+Ações para suprimir comunicações e sensores, degradando a capacidade de comando e controle inimiga.</t>
+  </si>
+  <si>
+    <t>Guerra Eletrônica e Neutralização de C²</t>
+  </si>
+  <si>
+    <t>Respostas às Aç de Guerra Eletrônica desempenhadas pelos partidos</t>
+  </si>
+  <si>
+    <t>Operações Psicológicas e Campanhas de Influência:
+Disputa pela percepção pública e moral das populações em território e redes regionais.</t>
+  </si>
+  <si>
+    <t>Operações Psicológicas e Campanhas de Influência</t>
+  </si>
+  <si>
+    <t>Respostas às Aç de Op Psico desempenhadas pelos partidos</t>
+  </si>
+  <si>
+    <t>Proteção de Infraestruturas Críticas:
+Defesa e recuperação de sistemas civis essenciais após ataques cibernéticos e sabotagens.</t>
+  </si>
+  <si>
+    <t>Proteção de Infraestruturas Críticas</t>
+  </si>
+  <si>
+    <t>Respostas às Aç de Ptç de Etta Estrt desempenhadas pelos partidos</t>
+  </si>
+  <si>
+    <t>Crise Ambiental em FENO:
+Vermelho explora evacuação civil e danos ambientais para acusar Azul de ocupação e negligência.</t>
+  </si>
+  <si>
+    <t>Crise Ambiental em FENO</t>
+  </si>
+  <si>
+    <t>Diplomacia e Gestão de Crises Internas:
+Vermelho gerencia deslocamentos e pressões internas enquanto reforça sua narrativa diplomática.</t>
+  </si>
+  <si>
+    <t>Diplomacia e Gestão de Crises Internas</t>
+  </si>
+  <si>
+    <t>Respostas às Aç de Aj Hum e Op Info desempenhadas pelos partidos</t>
+  </si>
+  <si>
+    <t>Influência sobre o MPL:
+Vermelho tenta cooptar grupo irregular para fortalecer pressão militar e política sobre Azul.</t>
+  </si>
+  <si>
+    <t>Influência sobre o MPL</t>
+  </si>
+  <si>
+    <t>Respostas às Aç de VERMELHO em busca de apoio ao MPL</t>
   </si>
 </sst>
 </file>
@@ -1125,7 +1242,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1171,6 +1288,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1523,8 +1646,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K328" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
-  <autoFilter ref="A1:K328" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K327" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:K327" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{BAF761B8-D6AF-48D3-A1F5-3D35088A4234}" name="event_id"/>
     <tableColumn id="2" xr3:uid="{78C225EA-4EED-44B0-BBCE-FD76B432B72B}" name="actor_id" dataDxfId="1">
@@ -1829,7 +1952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I67"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -3734,6 +3857,934 @@
       </c>
       <c r="I67" t="s">
         <v>257</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="30">
+      <c r="A69" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B69" t="s">
+        <v>9</v>
+      </c>
+      <c r="C69" t="s">
+        <v>10</v>
+      </c>
+      <c r="D69">
+        <v>43</v>
+      </c>
+      <c r="E69">
+        <v>62</v>
+      </c>
+      <c r="F69" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G69" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H69" t="s">
+        <v>12</v>
+      </c>
+      <c r="I69" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="30">
+      <c r="A70" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B70" t="s">
+        <v>15</v>
+      </c>
+      <c r="C70" t="s">
+        <v>10</v>
+      </c>
+      <c r="D70">
+        <v>55</v>
+      </c>
+      <c r="E70">
+        <v>65</v>
+      </c>
+      <c r="F70" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H70" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="30">
+      <c r="A71" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B71" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" t="s">
+        <v>10</v>
+      </c>
+      <c r="D71">
+        <v>63</v>
+      </c>
+      <c r="E71">
+        <v>54</v>
+      </c>
+      <c r="F71" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H71" t="s">
+        <v>12</v>
+      </c>
+      <c r="I71" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="30">
+      <c r="A72" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B72" t="s">
+        <v>38</v>
+      </c>
+      <c r="C72" t="s">
+        <v>10</v>
+      </c>
+      <c r="D72">
+        <v>50</v>
+      </c>
+      <c r="E72">
+        <v>51</v>
+      </c>
+      <c r="F72" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="30">
+      <c r="A73" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B73" t="s">
+        <v>39</v>
+      </c>
+      <c r="C73" t="s">
+        <v>10</v>
+      </c>
+      <c r="D73">
+        <v>7</v>
+      </c>
+      <c r="E73">
+        <v>61</v>
+      </c>
+      <c r="F73" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G73" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H73" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30">
+      <c r="A74" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B74" t="s">
+        <v>40</v>
+      </c>
+      <c r="C74" t="s">
+        <v>10</v>
+      </c>
+      <c r="D74">
+        <v>69</v>
+      </c>
+      <c r="E74">
+        <v>64</v>
+      </c>
+      <c r="F74" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G74" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H74" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="30">
+      <c r="A75" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B75" t="s">
+        <v>41</v>
+      </c>
+      <c r="C75" t="s">
+        <v>10</v>
+      </c>
+      <c r="D75">
+        <v>43</v>
+      </c>
+      <c r="E75">
+        <v>58</v>
+      </c>
+      <c r="F75" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G75" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H75" t="s">
+        <v>12</v>
+      </c>
+      <c r="I75" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="30">
+      <c r="A76" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B76" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" t="s">
+        <v>10</v>
+      </c>
+      <c r="D76">
+        <v>48</v>
+      </c>
+      <c r="E76">
+        <v>50</v>
+      </c>
+      <c r="F76" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G76" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H76" t="s">
+        <v>12</v>
+      </c>
+      <c r="I76" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30">
+      <c r="A77" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="D77">
+        <v>56</v>
+      </c>
+      <c r="E77">
+        <v>61</v>
+      </c>
+      <c r="F77" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="30">
+      <c r="A78" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B78" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="D78">
+        <v>56</v>
+      </c>
+      <c r="E78">
+        <v>61</v>
+      </c>
+      <c r="F78" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H78" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="30">
+      <c r="A79" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B79" t="s">
+        <v>45</v>
+      </c>
+      <c r="C79" t="s">
+        <v>10</v>
+      </c>
+      <c r="D79">
+        <v>43</v>
+      </c>
+      <c r="E79">
+        <v>52</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="G79" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H79" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="30">
+      <c r="A80" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B80" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="D80">
+        <v>31</v>
+      </c>
+      <c r="E80">
+        <v>45</v>
+      </c>
+      <c r="F80" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G80" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H80" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="30">
+      <c r="A81" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B81" t="s">
+        <v>47</v>
+      </c>
+      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="D81">
+        <v>48</v>
+      </c>
+      <c r="E81">
+        <v>47</v>
+      </c>
+      <c r="F81" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G81" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H81" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="30">
+      <c r="A82" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B82" t="s">
+        <v>48</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82">
+        <v>61</v>
+      </c>
+      <c r="E82">
+        <v>66</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G82" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H82" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="30">
+      <c r="A83" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B83" t="s">
+        <v>49</v>
+      </c>
+      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="D83">
+        <v>63</v>
+      </c>
+      <c r="E83">
+        <v>72</v>
+      </c>
+      <c r="F83" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H83" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9">
+      <c r="A84" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B84" t="s">
+        <v>71</v>
+      </c>
+      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="D84">
+        <v>10</v>
+      </c>
+      <c r="E84">
+        <v>34</v>
+      </c>
+      <c r="F84" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G84" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="H84" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="30">
+      <c r="A85" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B85" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" t="s">
+        <v>14</v>
+      </c>
+      <c r="D85">
+        <v>64</v>
+      </c>
+      <c r="E85">
+        <v>55</v>
+      </c>
+      <c r="F85" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G85" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H85" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="30">
+      <c r="A86" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B86" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" t="s">
+        <v>14</v>
+      </c>
+      <c r="D86">
+        <v>60</v>
+      </c>
+      <c r="E86">
+        <v>62</v>
+      </c>
+      <c r="F86" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G86" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H86" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="30">
+      <c r="A87" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B87" t="s">
+        <v>20</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
+      </c>
+      <c r="D87">
+        <v>53</v>
+      </c>
+      <c r="E87">
+        <v>53</v>
+      </c>
+      <c r="F87" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H87" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="30">
+      <c r="A88" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B88" t="s">
+        <v>38</v>
+      </c>
+      <c r="C88" t="s">
+        <v>14</v>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+      <c r="E88">
+        <v>48</v>
+      </c>
+      <c r="F88" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="G88" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H88" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="30">
+      <c r="A89" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B89" t="s">
+        <v>39</v>
+      </c>
+      <c r="C89" t="s">
+        <v>14</v>
+      </c>
+      <c r="D89">
+        <v>36</v>
+      </c>
+      <c r="E89">
+        <v>66</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="G89" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H89" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="30">
+      <c r="A90" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B90" t="s">
+        <v>40</v>
+      </c>
+      <c r="C90" t="s">
+        <v>14</v>
+      </c>
+      <c r="D90">
+        <v>36</v>
+      </c>
+      <c r="E90">
+        <v>43</v>
+      </c>
+      <c r="F90" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G90" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H90" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="30">
+      <c r="A91" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B91" t="s">
+        <v>41</v>
+      </c>
+      <c r="C91" t="s">
+        <v>14</v>
+      </c>
+      <c r="D91">
+        <v>34</v>
+      </c>
+      <c r="E91">
+        <v>59</v>
+      </c>
+      <c r="F91" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G91" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H91" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="30">
+      <c r="A92" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B92" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" t="s">
+        <v>14</v>
+      </c>
+      <c r="D92">
+        <v>50</v>
+      </c>
+      <c r="E92">
+        <v>50</v>
+      </c>
+      <c r="F92" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H92" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="30">
+      <c r="A93" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B93" t="s">
+        <v>43</v>
+      </c>
+      <c r="C93" t="s">
+        <v>14</v>
+      </c>
+      <c r="D93">
+        <v>52</v>
+      </c>
+      <c r="E93">
+        <v>62</v>
+      </c>
+      <c r="F93" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H93" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="30">
+      <c r="A94" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" t="s">
+        <v>14</v>
+      </c>
+      <c r="D94">
+        <v>53</v>
+      </c>
+      <c r="E94">
+        <v>62</v>
+      </c>
+      <c r="F94" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H94" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="30">
+      <c r="A95" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B95" t="s">
+        <v>45</v>
+      </c>
+      <c r="C95" t="s">
+        <v>14</v>
+      </c>
+      <c r="D95">
+        <v>52</v>
+      </c>
+      <c r="E95">
+        <v>51</v>
+      </c>
+      <c r="F95" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H95" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="30">
+      <c r="A96" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B96" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
+      </c>
+      <c r="D96">
+        <v>76</v>
+      </c>
+      <c r="E96">
+        <v>52</v>
+      </c>
+      <c r="F96" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="G96" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H96" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="30">
+      <c r="A97" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B97" t="s">
+        <v>47</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
+      </c>
+      <c r="D97">
+        <v>49</v>
+      </c>
+      <c r="E97">
+        <v>50</v>
+      </c>
+      <c r="F97" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="G97" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H97" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="30">
+      <c r="A98" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C98" t="s">
+        <v>14</v>
+      </c>
+      <c r="D98">
+        <v>56</v>
+      </c>
+      <c r="E98">
+        <v>66</v>
+      </c>
+      <c r="F98" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H98" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="30">
+      <c r="A99" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B99" t="s">
+        <v>49</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+      <c r="D99">
+        <v>62</v>
+      </c>
+      <c r="E99">
+        <v>73</v>
+      </c>
+      <c r="F99" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="H99" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="30">
+      <c r="A100" s="1">
+        <v>45958</v>
+      </c>
+      <c r="B100" t="s">
+        <v>71</v>
+      </c>
+      <c r="C100" t="s">
+        <v>14</v>
+      </c>
+      <c r="D100">
+        <v>57</v>
+      </c>
+      <c r="E100">
+        <v>56</v>
+      </c>
+      <c r="F100" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H100" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +5077,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="28" style="14" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51" style="14" customWidth="1"/>
     <col min="5" max="5" width="16.140625" style="14" bestFit="1" customWidth="1"/>
@@ -4113,58 +5164,264 @@
         <v>261</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="45">
       <c r="A4" t="s">
         <v>81</v>
       </c>
-      <c r="B4" s="1"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="B4" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>290</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H4" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="60">
       <c r="A5" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="B5" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="60">
       <c r="A6" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="B6" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>297</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>298</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="45">
       <c r="A7" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="B7" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>301</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="G7" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="60">
       <c r="A8" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="B8" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="57.75">
       <c r="A9" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="17"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="B9" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="D9" s="17" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>309</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="45">
       <c r="A10" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="B10" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="45">
       <c r="A11" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="B11" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>315</v>
+      </c>
+      <c r="G11" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H11" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="45">
       <c r="A12" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="B12" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C12" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>317</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="45">
       <c r="A13" t="s">
         <v>94</v>
+      </c>
+      <c r="B13" s="22">
+        <v>45958</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -4988,7 +6245,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:K328"/>
+  <dimension ref="A1:K327"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" bestFit="1" customWidth="1"/>
@@ -5039,66 +6296,82 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" ht="30">
       <c r="A2" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B2" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C2, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G2" s="14"/>
-      <c r="I2" s="14"/>
-    </row>
-    <row r="3" spans="1:11" ht="30">
+        <v>ATO001</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>-2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2" s="14" t="s">
+        <v>263</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>33</v>
       </c>
       <c r="B3" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C3, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO001</v>
+        <v>ATO002</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
         <v>14</v>
       </c>
       <c r="E3">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" ht="30">
       <c r="A4" t="s">
         <v>33</v>
       </c>
       <c r="B4" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C4, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO002</v>
+        <v>ATO003</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
         <v>14</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -5110,157 +6383,157 @@
       </c>
       <c r="B5" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C5, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO003</v>
+        <v>ATO004</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
         <v>14</v>
       </c>
       <c r="E5">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30">
+    <row r="6" spans="1:11" ht="45">
       <c r="A6" t="s">
         <v>33</v>
       </c>
       <c r="B6" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C6, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO004</v>
+        <v>ATO005</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
         <v>14</v>
       </c>
       <c r="E6">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="45">
+    <row r="7" spans="1:11" ht="30">
       <c r="A7" t="s">
         <v>33</v>
       </c>
       <c r="B7" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C7, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO005</v>
+        <v>ATO006</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
         <v>14</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>-8</v>
       </c>
       <c r="F7">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="30">
+    <row r="8" spans="1:11" ht="60">
       <c r="A8" t="s">
         <v>33</v>
       </c>
       <c r="B8" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C8, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO006</v>
+        <v>ATO007</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" t="s">
         <v>14</v>
       </c>
       <c r="E8">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="F8">
-        <v>-7</v>
+        <v>3</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="60">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>33</v>
       </c>
       <c r="B9" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C9, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO007</v>
+        <v>ATO008</v>
       </c>
       <c r="C9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D9" t="s">
         <v>14</v>
       </c>
       <c r="E9">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:11" ht="30">
       <c r="A10" t="s">
         <v>33</v>
       </c>
       <c r="B10" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C10, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO008</v>
+        <v>ATO009</v>
       </c>
       <c r="C10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D10" t="s">
         <v>14</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -5272,10 +6545,10 @@
       </c>
       <c r="B11" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C11, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO009</v>
+        <v>ATO010</v>
       </c>
       <c r="C11" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D11" t="s">
         <v>14</v>
@@ -5299,22 +6572,22 @@
       </c>
       <c r="B12" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C12, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO010</v>
+        <v>ATO011</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D12" t="s">
         <v>14</v>
       </c>
       <c r="E12">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H12">
         <v>0</v>
@@ -5326,22 +6599,22 @@
       </c>
       <c r="B13" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C13, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO011</v>
+        <v>ATO012</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" t="s">
         <v>14</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5353,22 +6626,22 @@
       </c>
       <c r="B14" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C14, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO012</v>
+        <v>ATO013</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D14" t="s">
         <v>14</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F14">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5380,22 +6653,22 @@
       </c>
       <c r="B15" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C15, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO013</v>
+        <v>ATO014</v>
       </c>
       <c r="C15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="s">
         <v>14</v>
       </c>
       <c r="E15">
+        <v>-2</v>
+      </c>
+      <c r="F15">
         <v>3</v>
       </c>
-      <c r="F15">
-        <v>2</v>
-      </c>
       <c r="G15" s="14" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -5407,22 +6680,22 @@
       </c>
       <c r="B16" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C16, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO014</v>
+        <v>ATO015</v>
       </c>
       <c r="C16" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
         <v>14</v>
       </c>
       <c r="E16">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="F16">
         <v>3</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -5434,22 +6707,22 @@
       </c>
       <c r="B17" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C17, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO015</v>
+        <v>ATO016</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
         <v>14</v>
       </c>
       <c r="E17">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H17">
         <v>0</v>
@@ -5461,22 +6734,22 @@
       </c>
       <c r="B18" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C18, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO016</v>
+        <v>ATO001</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E18">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F18">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H18">
         <v>0</v>
@@ -5488,22 +6761,22 @@
       </c>
       <c r="B19" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C19, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO001</v>
+        <v>ATO002</v>
       </c>
       <c r="C19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H19">
         <v>0</v>
@@ -5515,22 +6788,22 @@
       </c>
       <c r="B20" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C20, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO002</v>
+        <v>ATO003</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
         <v>10</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -5542,22 +6815,22 @@
       </c>
       <c r="B21" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C21, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO003</v>
+        <v>ATO004</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>10</v>
       </c>
       <c r="E21">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -5569,130 +6842,130 @@
       </c>
       <c r="B22" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C22, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO004</v>
+        <v>ATO005</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
         <v>10</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="F22">
         <v>1</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="30">
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" t="s">
         <v>33</v>
       </c>
       <c r="B23" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C23, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO005</v>
+        <v>ATO006</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23" t="s">
         <v>10</v>
       </c>
       <c r="E23">
-        <v>-3</v>
+        <v>9</v>
       </c>
       <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>280</v>
+        <v>9</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>281</v>
       </c>
       <c r="H23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="42.75">
+    <row r="24" spans="1:8" ht="30">
       <c r="A24" t="s">
         <v>33</v>
       </c>
       <c r="B24" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C24, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO006</v>
+        <v>ATO007</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D24" t="s">
         <v>10</v>
       </c>
       <c r="E24">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F24">
-        <v>9</v>
-      </c>
-      <c r="G24" s="18" t="s">
-        <v>281</v>
+        <v>0</v>
+      </c>
+      <c r="G24" s="14" t="s">
+        <v>282</v>
       </c>
       <c r="H24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="30">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>33</v>
       </c>
       <c r="B25" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C25, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO007</v>
+        <v>ATO008</v>
       </c>
       <c r="C25" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D25" t="s">
         <v>10</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>0</v>
       </c>
       <c r="G25" s="14" t="s">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="H25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" ht="30">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C26, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO008</v>
+        <v>ATO009</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
         <v>10</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" s="14" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -5704,10 +6977,10 @@
       </c>
       <c r="B27" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C27, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO009</v>
+        <v>ATO010</v>
       </c>
       <c r="C27" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
         <v>10</v>
@@ -5731,130 +7004,130 @@
       </c>
       <c r="B28" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C28, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO010</v>
+        <v>ATO011</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
         <v>10</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="H28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30">
+    <row r="29" spans="1:8" ht="45">
       <c r="A29" t="s">
         <v>33</v>
       </c>
       <c r="B29" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C29, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO011</v>
+        <v>ATO012</v>
       </c>
       <c r="C29" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
         <v>10</v>
       </c>
       <c r="E29">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="F29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="45">
+    <row r="30" spans="1:8" ht="30">
       <c r="A30" t="s">
         <v>33</v>
       </c>
       <c r="B30" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C30, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO012</v>
+        <v>ATO013</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D30" t="s">
         <v>10</v>
       </c>
       <c r="E30">
-        <v>-4</v>
+        <v>3</v>
       </c>
       <c r="F30">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H30">
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="30">
+    <row r="31" spans="1:8" ht="28.5">
       <c r="A31" t="s">
         <v>33</v>
       </c>
       <c r="B31" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C31, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO013</v>
+        <v>ATO014</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D31" t="s">
         <v>10</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31">
-        <v>2</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>283</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="18" t="s">
+        <v>277</v>
       </c>
       <c r="H31">
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="28.5">
+    <row r="32" spans="1:8" ht="30">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C32, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO014</v>
+        <v>ATO015</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
         <v>10</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" s="18" t="s">
-        <v>277</v>
+        <v>4</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>285</v>
       </c>
       <c r="H32">
         <v>0</v>
@@ -5866,22 +7139,22 @@
       </c>
       <c r="B33" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C33, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO015</v>
+        <v>ATO016</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D33" t="s">
         <v>10</v>
       </c>
       <c r="E33">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="F33">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -5889,907 +7162,2808 @@
     </row>
     <row r="34" spans="1:8" ht="30">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="B34" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C34, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v>ATO016</v>
+        <v>ATO006</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="D34" t="s">
         <v>10</v>
       </c>
       <c r="E34">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="F34">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="H34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="30">
+      <c r="A35" t="s">
+        <v>81</v>
+      </c>
       <c r="B35" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C35, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G35" s="14"/>
-    </row>
-    <row r="36" spans="1:8">
+        <v>ATO003</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="D35" t="s">
+        <v>10</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="F35">
+        <v>2</v>
+      </c>
+      <c r="G35" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="30">
+      <c r="A36" t="s">
+        <v>81</v>
+      </c>
       <c r="B36" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C36, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G36" s="14"/>
-    </row>
-    <row r="37" spans="1:8">
+        <v>ATO005</v>
+      </c>
+      <c r="C36" t="s">
+        <v>55</v>
+      </c>
+      <c r="D36" t="s">
+        <v>10</v>
+      </c>
+      <c r="E36">
+        <v>-6</v>
+      </c>
+      <c r="F36">
+        <v>5</v>
+      </c>
+      <c r="G36" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="30">
+      <c r="A37" t="s">
+        <v>81</v>
+      </c>
       <c r="B37" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C37, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G37" s="14"/>
-    </row>
-    <row r="38" spans="1:8">
+        <v>ATO002</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" t="s">
+        <v>10</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
+      </c>
+      <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="30">
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
       <c r="B38" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C38, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G38" s="14"/>
-    </row>
-    <row r="39" spans="1:8">
+        <v>ATO009</v>
+      </c>
+      <c r="C38" t="s">
+        <v>63</v>
+      </c>
+      <c r="D38" t="s">
+        <v>10</v>
+      </c>
+      <c r="E38">
+        <v>3</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="G38" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="30">
+      <c r="A39" t="s">
+        <v>81</v>
+      </c>
       <c r="B39" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C39, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G39" s="14"/>
-    </row>
-    <row r="40" spans="1:8">
+        <v>ATO010</v>
+      </c>
+      <c r="C39" t="s">
+        <v>64</v>
+      </c>
+      <c r="D39" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39">
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
+      </c>
+      <c r="G39" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="30">
+      <c r="A40" t="s">
+        <v>81</v>
+      </c>
       <c r="B40" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C40, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G40" s="14"/>
-    </row>
-    <row r="41" spans="1:8">
+        <v>ATO014</v>
+      </c>
+      <c r="C40" t="s">
+        <v>68</v>
+      </c>
+      <c r="D40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40">
+        <v>3</v>
+      </c>
+      <c r="F40">
+        <v>3</v>
+      </c>
+      <c r="G40" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="30">
+      <c r="A41" t="s">
+        <v>81</v>
+      </c>
       <c r="B41" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C41, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G41" s="14"/>
-    </row>
-    <row r="42" spans="1:8">
+        <v>ATO001</v>
+      </c>
+      <c r="C41" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
+        <v>2</v>
+      </c>
+      <c r="G41" s="14" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="30">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
       <c r="B42" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C42, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G42" s="14"/>
-    </row>
-    <row r="43" spans="1:8">
+        <v>ATO012</v>
+      </c>
+      <c r="C42" t="s">
+        <v>66</v>
+      </c>
+      <c r="D42" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>-7</v>
+      </c>
+      <c r="F42">
+        <v>3</v>
+      </c>
+      <c r="G42" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="30">
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
       <c r="B43" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C43, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G43" s="14"/>
-    </row>
-    <row r="44" spans="1:8">
+        <v>ATO012</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
+      </c>
+      <c r="D43" t="s">
+        <v>14</v>
+      </c>
+      <c r="E43">
+        <v>8</v>
+      </c>
+      <c r="F43">
+        <v>4</v>
+      </c>
+      <c r="G43" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="30">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
       <c r="B44" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C44, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G44" s="14"/>
-    </row>
-    <row r="45" spans="1:8">
+        <v>ATO015</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>10</v>
+      </c>
+      <c r="E44" s="23">
+        <v>6</v>
+      </c>
+      <c r="F44" s="23">
+        <v>5</v>
+      </c>
+      <c r="G44" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="30">
+      <c r="A45" t="s">
+        <v>82</v>
+      </c>
       <c r="B45" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C45, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G45" s="14"/>
-    </row>
-    <row r="46" spans="1:8">
+        <v>ATO015</v>
+      </c>
+      <c r="C45" t="s">
+        <v>69</v>
+      </c>
+      <c r="D45" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="23">
+        <v>2</v>
+      </c>
+      <c r="F45" s="23">
+        <v>1</v>
+      </c>
+      <c r="G45" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="30">
+      <c r="A46" t="s">
+        <v>82</v>
+      </c>
       <c r="B46" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C46, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G46" s="14"/>
-    </row>
-    <row r="47" spans="1:8">
+        <v>ATO003</v>
+      </c>
+      <c r="C46" t="s">
+        <v>52</v>
+      </c>
+      <c r="D46" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="23">
+        <v>3</v>
+      </c>
+      <c r="F46" s="23">
+        <v>4</v>
+      </c>
+      <c r="G46" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="30">
+      <c r="A47" t="s">
+        <v>82</v>
+      </c>
       <c r="B47" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C47, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G47" s="14"/>
-    </row>
-    <row r="48" spans="1:8">
+        <v>ATO003</v>
+      </c>
+      <c r="C47" t="s">
+        <v>52</v>
+      </c>
+      <c r="D47" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="23">
+        <v>4</v>
+      </c>
+      <c r="F47" s="23">
+        <v>2</v>
+      </c>
+      <c r="G47" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="30">
+      <c r="A48" t="s">
+        <v>82</v>
+      </c>
       <c r="B48" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C48, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G48" s="14"/>
-    </row>
-    <row r="49" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C48" t="s">
+        <v>57</v>
+      </c>
+      <c r="D48" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="23">
+        <v>5</v>
+      </c>
+      <c r="F48" s="23">
+        <v>5</v>
+      </c>
+      <c r="G48" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30">
+      <c r="A49" t="s">
+        <v>82</v>
+      </c>
       <c r="B49" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C49, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G49" s="14"/>
-    </row>
-    <row r="50" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E49" s="23">
+        <v>-7</v>
+      </c>
+      <c r="F49" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G49" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="30">
+      <c r="A50" t="s">
+        <v>82</v>
+      </c>
       <c r="B50" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C50, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G50" s="14"/>
-    </row>
-    <row r="51" spans="2:7">
+        <v>ATO013</v>
+      </c>
+      <c r="C50" t="s">
+        <v>67</v>
+      </c>
+      <c r="D50" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="23">
+        <v>5</v>
+      </c>
+      <c r="F50" s="23">
+        <v>4</v>
+      </c>
+      <c r="G50" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30">
+      <c r="A51" t="s">
+        <v>82</v>
+      </c>
       <c r="B51" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C51, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G51" s="14"/>
-    </row>
-    <row r="52" spans="2:7">
+        <v>ATO013</v>
+      </c>
+      <c r="C51" t="s">
+        <v>67</v>
+      </c>
+      <c r="D51" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="23">
+        <v>-4</v>
+      </c>
+      <c r="F51" s="23">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30">
+      <c r="A52" t="s">
+        <v>82</v>
+      </c>
       <c r="B52" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C52, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G52" s="14"/>
-    </row>
-    <row r="53" spans="2:7">
+        <v>ATO016</v>
+      </c>
+      <c r="C52" t="s">
+        <v>72</v>
+      </c>
+      <c r="D52" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F52" s="23">
+        <v>6</v>
+      </c>
+      <c r="G52" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="30">
+      <c r="A53" t="s">
+        <v>82</v>
+      </c>
       <c r="B53" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C53, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G53" s="14"/>
-    </row>
-    <row r="54" spans="2:7">
+        <v>ATO016</v>
+      </c>
+      <c r="C53" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" t="s">
+        <v>14</v>
+      </c>
+      <c r="E53" s="23">
+        <v>2</v>
+      </c>
+      <c r="F53" s="23">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="30">
+      <c r="A54" t="s">
+        <v>83</v>
+      </c>
       <c r="B54" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C54, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G54" s="14"/>
-    </row>
-    <row r="55" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D54" t="s">
+        <v>10</v>
+      </c>
+      <c r="E54" s="23">
+        <v>3</v>
+      </c>
+      <c r="F54" s="23">
+        <v>3</v>
+      </c>
+      <c r="G54" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="30">
+      <c r="A55" t="s">
+        <v>83</v>
+      </c>
       <c r="B55" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C55, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G55" s="14"/>
-    </row>
-    <row r="56" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C55" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D55" t="s">
+        <v>10</v>
+      </c>
+      <c r="E55" s="23">
+        <v>5</v>
+      </c>
+      <c r="F55" s="23">
+        <v>3</v>
+      </c>
+      <c r="G55" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="30">
+      <c r="A56" t="s">
+        <v>83</v>
+      </c>
       <c r="B56" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C56, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G56" s="14"/>
-    </row>
-    <row r="57" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D56" t="s">
+        <v>10</v>
+      </c>
+      <c r="E56" s="23">
+        <v>3</v>
+      </c>
+      <c r="F56" s="23">
+        <v>2</v>
+      </c>
+      <c r="G56" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="30">
+      <c r="A57" t="s">
+        <v>83</v>
+      </c>
       <c r="B57" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C57, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G57" s="14"/>
-    </row>
-    <row r="58" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D57" t="s">
+        <v>10</v>
+      </c>
+      <c r="E57" s="23">
+        <v>3</v>
+      </c>
+      <c r="F57" s="23">
+        <v>2</v>
+      </c>
+      <c r="G57" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="30">
+      <c r="A58" t="s">
+        <v>83</v>
+      </c>
       <c r="B58" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C58, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G58" s="14"/>
-    </row>
-    <row r="59" spans="2:7">
+        <v>ATO011</v>
+      </c>
+      <c r="C58" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" s="23">
+        <v>5</v>
+      </c>
+      <c r="F58" s="23">
+        <v>3</v>
+      </c>
+      <c r="G58" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="30">
+      <c r="A59" t="s">
+        <v>83</v>
+      </c>
       <c r="B59" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C59, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G59" s="14"/>
-    </row>
-    <row r="60" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C59" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D59" t="s">
+        <v>10</v>
+      </c>
+      <c r="E59" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F59" s="23">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="30">
+      <c r="A60" t="s">
+        <v>83</v>
+      </c>
       <c r="B60" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C60, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G60" s="14"/>
-    </row>
-    <row r="61" spans="2:7">
+        <v>ATO014</v>
+      </c>
+      <c r="C60" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D60" t="s">
+        <v>10</v>
+      </c>
+      <c r="E60" s="23">
+        <v>4</v>
+      </c>
+      <c r="F60" s="23">
+        <v>4</v>
+      </c>
+      <c r="G60" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="30">
+      <c r="A61" t="s">
+        <v>83</v>
+      </c>
       <c r="B61" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C61, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G61" s="14"/>
-    </row>
-    <row r="62" spans="2:7">
+        <v>ATO002</v>
+      </c>
+      <c r="C61" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D61" t="s">
+        <v>10</v>
+      </c>
+      <c r="E61" s="23">
+        <v>0</v>
+      </c>
+      <c r="F61" s="23">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="30">
+      <c r="A62" t="s">
+        <v>83</v>
+      </c>
       <c r="B62" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C62, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G62" s="14"/>
-    </row>
-    <row r="63" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C62" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62" t="s">
+        <v>14</v>
+      </c>
+      <c r="E62" s="23">
+        <v>4</v>
+      </c>
+      <c r="F62" s="23">
+        <v>1</v>
+      </c>
+      <c r="G62" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="30">
+      <c r="A63" t="s">
+        <v>83</v>
+      </c>
       <c r="B63" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C63, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G63" s="14"/>
-    </row>
-    <row r="64" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63" t="s">
+        <v>14</v>
+      </c>
+      <c r="E63" s="23">
+        <v>6</v>
+      </c>
+      <c r="F63" s="23">
+        <v>2</v>
+      </c>
+      <c r="G63" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="30">
+      <c r="A64" t="s">
+        <v>83</v>
+      </c>
       <c r="B64" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C64, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G64" s="14"/>
-    </row>
-    <row r="65" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C64" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D64" t="s">
+        <v>14</v>
+      </c>
+      <c r="E64" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F64" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G64" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="30">
+      <c r="A65" t="s">
+        <v>83</v>
+      </c>
       <c r="B65" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C65, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G65" s="14"/>
-    </row>
-    <row r="66" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F65" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G65" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="30">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
       <c r="B66" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C66, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G66" s="14"/>
-    </row>
-    <row r="67" spans="2:7">
+        <v>ATO011</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F66" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="30">
+      <c r="A67" t="s">
+        <v>83</v>
+      </c>
       <c r="B67" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C67, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G67" s="14"/>
-    </row>
-    <row r="68" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" s="23">
+        <v>8</v>
+      </c>
+      <c r="F67" s="23">
+        <v>3</v>
+      </c>
+      <c r="G67" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="30">
+      <c r="A68" t="s">
+        <v>83</v>
+      </c>
       <c r="B68" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C68, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G68" s="14"/>
-    </row>
-    <row r="69" spans="2:7">
+        <v>ATO014</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D68" t="s">
+        <v>14</v>
+      </c>
+      <c r="E68" s="23">
+        <v>-5</v>
+      </c>
+      <c r="F68" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G68" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="30">
+      <c r="A69" t="s">
+        <v>83</v>
+      </c>
       <c r="B69" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C69, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G69" s="14"/>
-    </row>
-    <row r="70" spans="2:7">
+        <v>ATO002</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D69" t="s">
+        <v>14</v>
+      </c>
+      <c r="E69" s="23">
+        <v>2</v>
+      </c>
+      <c r="F69" s="23">
+        <v>2</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="30">
+      <c r="A70" t="s">
+        <v>84</v>
+      </c>
       <c r="B70" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C70, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G70" s="14"/>
-    </row>
-    <row r="71" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D70" t="s">
+        <v>10</v>
+      </c>
+      <c r="E70" s="23">
+        <v>-10</v>
+      </c>
+      <c r="F70" s="23">
+        <v>6</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="30">
+      <c r="A71" t="s">
+        <v>84</v>
+      </c>
       <c r="B71" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C71, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G71" s="14"/>
-    </row>
-    <row r="72" spans="2:7">
+        <v>ATO002</v>
+      </c>
+      <c r="C71" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D71" t="s">
+        <v>10</v>
+      </c>
+      <c r="E71" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F71" s="23">
+        <v>4</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="30">
+      <c r="A72" t="s">
+        <v>84</v>
+      </c>
       <c r="B72" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C72, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G72" s="14"/>
-    </row>
-    <row r="73" spans="2:7">
+        <v>ATO014</v>
+      </c>
+      <c r="C72" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D72" t="s">
+        <v>10</v>
+      </c>
+      <c r="E72" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F72" s="23">
+        <v>4</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="30">
+      <c r="A73" t="s">
+        <v>84</v>
+      </c>
       <c r="B73" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C73, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G73" s="14"/>
-    </row>
-    <row r="74" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C73" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D73" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F73" s="23">
+        <v>4</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="30">
+      <c r="A74" t="s">
+        <v>84</v>
+      </c>
       <c r="B74" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C74, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G74" s="14"/>
-    </row>
-    <row r="75" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C74" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D74" t="s">
+        <v>10</v>
+      </c>
+      <c r="E74" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F74" s="23">
+        <v>4</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="30">
+      <c r="A75" t="s">
+        <v>84</v>
+      </c>
       <c r="B75" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C75, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G75" s="14"/>
-    </row>
-    <row r="76" spans="2:7">
+        <v>ATO011</v>
+      </c>
+      <c r="C75" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D75" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="23">
+        <v>8</v>
+      </c>
+      <c r="F75" s="23">
+        <v>7</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="30">
+      <c r="A76" t="s">
+        <v>84</v>
+      </c>
       <c r="B76" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C76, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G76" s="14"/>
-    </row>
-    <row r="77" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C76" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D76" t="s">
+        <v>10</v>
+      </c>
+      <c r="E76" s="23">
+        <v>7</v>
+      </c>
+      <c r="F76" s="23">
+        <v>8</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="30">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
       <c r="B77" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C77, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G77" s="14"/>
-    </row>
-    <row r="78" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C77" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D77" t="s">
+        <v>10</v>
+      </c>
+      <c r="E77" s="23">
+        <v>-8</v>
+      </c>
+      <c r="F77" s="23">
+        <v>5</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="30">
+      <c r="A78" t="s">
+        <v>84</v>
+      </c>
       <c r="B78" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C78, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G78" s="14"/>
-    </row>
-    <row r="79" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C78" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D78" t="s">
+        <v>10</v>
+      </c>
+      <c r="E78" s="23">
+        <v>-10</v>
+      </c>
+      <c r="F78" s="23">
+        <v>2</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="30">
+      <c r="A79" t="s">
+        <v>84</v>
+      </c>
       <c r="B79" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C79, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G79" s="14"/>
-    </row>
-    <row r="80" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C79" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" s="23">
+        <v>8</v>
+      </c>
+      <c r="F79" s="23">
+        <v>4</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="30">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
       <c r="B80" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C80, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G80" s="14"/>
-    </row>
-    <row r="81" spans="2:7">
+        <v>ATO002</v>
+      </c>
+      <c r="C80" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="D80" t="s">
+        <v>14</v>
+      </c>
+      <c r="E80" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F80" s="23">
+        <v>4</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="30">
+      <c r="A81" t="s">
+        <v>84</v>
+      </c>
       <c r="B81" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C81, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G81" s="14"/>
-    </row>
-    <row r="82" spans="2:7">
+        <v>ATO014</v>
+      </c>
+      <c r="C81" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="D81" t="s">
+        <v>14</v>
+      </c>
+      <c r="E81" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F81" s="23">
+        <v>4</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="30">
+      <c r="A82" t="s">
+        <v>84</v>
+      </c>
       <c r="B82" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C82, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G82" s="14"/>
-    </row>
-    <row r="83" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C82" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D82" t="s">
+        <v>14</v>
+      </c>
+      <c r="E82" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F82" s="23">
+        <v>4</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" ht="30">
+      <c r="A83" t="s">
+        <v>84</v>
+      </c>
       <c r="B83" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C83, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G83" s="14"/>
-    </row>
-    <row r="84" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C83" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D83" t="s">
+        <v>14</v>
+      </c>
+      <c r="E83" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F83" s="23">
+        <v>4</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="30">
+      <c r="A84" t="s">
+        <v>84</v>
+      </c>
       <c r="B84" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C84, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G84" s="14"/>
-    </row>
-    <row r="85" spans="2:7">
+        <v>ATO011</v>
+      </c>
+      <c r="C84" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D84" t="s">
+        <v>14</v>
+      </c>
+      <c r="E84" s="23">
+        <v>-9</v>
+      </c>
+      <c r="F84" s="23">
+        <v>4</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="30">
+      <c r="A85" t="s">
+        <v>84</v>
+      </c>
       <c r="B85" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C85, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G85" s="14"/>
-    </row>
-    <row r="86" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C85" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85" s="23">
+        <v>-10</v>
+      </c>
+      <c r="F85" s="23">
+        <v>2</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="30">
+      <c r="A86" t="s">
+        <v>84</v>
+      </c>
       <c r="B86" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C86, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G86" s="14"/>
-    </row>
-    <row r="87" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C86" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D86" t="s">
+        <v>14</v>
+      </c>
+      <c r="E86" s="23">
+        <v>-8</v>
+      </c>
+      <c r="F86" s="23">
+        <v>5</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="30">
+      <c r="A87" t="s">
+        <v>84</v>
+      </c>
       <c r="B87" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C87, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G87" s="14"/>
-    </row>
-    <row r="88" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C87" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D87" t="s">
+        <v>14</v>
+      </c>
+      <c r="E87" s="23">
+        <v>7</v>
+      </c>
+      <c r="F87" s="23">
+        <v>8</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="30">
+      <c r="A88" t="s">
+        <v>85</v>
+      </c>
       <c r="B88" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C88, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G88" s="14"/>
-    </row>
-    <row r="89" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C88" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88" t="s">
+        <v>10</v>
+      </c>
+      <c r="E88" s="23">
+        <v>6</v>
+      </c>
+      <c r="F88" s="23">
+        <v>9</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="30">
+      <c r="A89" t="s">
+        <v>85</v>
+      </c>
       <c r="B89" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C89, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G89" s="14"/>
-    </row>
-    <row r="90" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C89" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D89" t="s">
+        <v>10</v>
+      </c>
+      <c r="E89" s="23">
+        <v>-10</v>
+      </c>
+      <c r="F89" s="23">
+        <v>8</v>
+      </c>
+      <c r="G89" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="30">
+      <c r="A90" t="s">
+        <v>85</v>
+      </c>
       <c r="B90" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C90, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G90" s="14"/>
-    </row>
-    <row r="91" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C90" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D90" t="s">
+        <v>10</v>
+      </c>
+      <c r="E90" s="23">
+        <v>-8</v>
+      </c>
+      <c r="F90" s="23">
+        <v>8</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="30">
+      <c r="A91" t="s">
+        <v>85</v>
+      </c>
       <c r="B91" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C91, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G91" s="14"/>
-    </row>
-    <row r="92" spans="2:7">
+        <v>ATO008</v>
+      </c>
+      <c r="C91" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D91" t="s">
+        <v>10</v>
+      </c>
+      <c r="E91" s="23">
+        <v>-4</v>
+      </c>
+      <c r="F91" s="23">
+        <v>5</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="30">
+      <c r="A92" t="s">
+        <v>85</v>
+      </c>
       <c r="B92" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C92, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G92" s="14"/>
-    </row>
-    <row r="93" spans="2:7">
+        <v>ATO016</v>
+      </c>
+      <c r="C92" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D92" t="s">
+        <v>10</v>
+      </c>
+      <c r="E92" s="23">
+        <v>-7</v>
+      </c>
+      <c r="F92" s="23">
+        <v>8</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="30">
+      <c r="A93" t="s">
+        <v>85</v>
+      </c>
       <c r="B93" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C93, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G93" s="14"/>
-    </row>
-    <row r="94" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C93" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" t="s">
+        <v>14</v>
+      </c>
+      <c r="E93" s="23">
+        <v>0</v>
+      </c>
+      <c r="F93" s="23">
+        <v>0</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="30">
+      <c r="A94" t="s">
+        <v>85</v>
+      </c>
       <c r="B94" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C94, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G94" s="14"/>
-    </row>
-    <row r="95" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C94" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D94" t="s">
+        <v>14</v>
+      </c>
+      <c r="E94" s="23">
+        <v>-5</v>
+      </c>
+      <c r="F94" s="23">
+        <v>6</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="30">
+      <c r="A95" t="s">
+        <v>85</v>
+      </c>
       <c r="B95" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C95, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G95" s="14"/>
-    </row>
-    <row r="96" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C95" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D95" t="s">
+        <v>14</v>
+      </c>
+      <c r="E95" s="23">
+        <v>0</v>
+      </c>
+      <c r="F95" s="23">
+        <v>-4</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" ht="30">
+      <c r="A96" t="s">
+        <v>85</v>
+      </c>
       <c r="B96" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C96, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G96" s="14"/>
-    </row>
-    <row r="97" spans="2:7">
+        <v>ATO008</v>
+      </c>
+      <c r="C96" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F96" s="23">
+        <v>-4</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="30">
+      <c r="A97" t="s">
+        <v>85</v>
+      </c>
       <c r="B97" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C97, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G97" s="14"/>
-    </row>
-    <row r="98" spans="2:7">
+        <v>ATO016</v>
+      </c>
+      <c r="C97" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D97" t="s">
+        <v>14</v>
+      </c>
+      <c r="E97" s="23">
+        <v>0</v>
+      </c>
+      <c r="F97" s="23">
+        <v>-3</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="30">
+      <c r="A98" t="s">
+        <v>90</v>
+      </c>
       <c r="B98" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C98, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G98" s="14"/>
-    </row>
-    <row r="99" spans="2:7">
+        <v>ATO008</v>
+      </c>
+      <c r="C98" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D98" t="s">
+        <v>10</v>
+      </c>
+      <c r="E98" s="23">
+        <v>-7</v>
+      </c>
+      <c r="F98" s="23">
+        <v>2</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="30">
+      <c r="A99" t="s">
+        <v>90</v>
+      </c>
       <c r="B99" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C99, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G99" s="14"/>
-    </row>
-    <row r="100" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C99" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D99" t="s">
+        <v>10</v>
+      </c>
+      <c r="E99" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F99" s="23">
+        <v>2</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" ht="30">
+      <c r="A100" t="s">
+        <v>90</v>
+      </c>
       <c r="B100" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C100, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G100" s="14"/>
-    </row>
-    <row r="101" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C100" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D100" t="s">
+        <v>10</v>
+      </c>
+      <c r="E100" s="23">
+        <v>2</v>
+      </c>
+      <c r="F100" s="23">
+        <v>1</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="30">
+      <c r="A101" t="s">
+        <v>90</v>
+      </c>
       <c r="B101" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C101, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G101" s="14"/>
-    </row>
-    <row r="102" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C101" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D101" t="s">
+        <v>10</v>
+      </c>
+      <c r="E101" s="23">
+        <v>2</v>
+      </c>
+      <c r="F101" s="23">
+        <v>1</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" ht="30">
+      <c r="A102" t="s">
+        <v>90</v>
+      </c>
       <c r="B102" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C102, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G102" s="14"/>
-    </row>
-    <row r="103" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C102" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D102" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="23">
+        <v>5</v>
+      </c>
+      <c r="F102" s="23">
+        <v>4</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" ht="30">
+      <c r="A103" t="s">
+        <v>90</v>
+      </c>
       <c r="B103" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C103, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G103" s="14"/>
-    </row>
-    <row r="104" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C103" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D103" t="s">
+        <v>10</v>
+      </c>
+      <c r="E103" s="23">
+        <v>-8</v>
+      </c>
+      <c r="F103" s="23">
+        <v>2</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="30">
+      <c r="A104" t="s">
+        <v>90</v>
+      </c>
       <c r="B104" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C104, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G104" s="14"/>
-    </row>
-    <row r="105" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C104" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104" t="s">
+        <v>10</v>
+      </c>
+      <c r="E104" s="23">
+        <v>6</v>
+      </c>
+      <c r="F104" s="23">
+        <v>5</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="30">
+      <c r="A105" t="s">
+        <v>90</v>
+      </c>
       <c r="B105" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C105, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G105" s="14"/>
-    </row>
-    <row r="106" spans="2:7">
+        <v>ATO008</v>
+      </c>
+      <c r="C105" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D105" t="s">
+        <v>14</v>
+      </c>
+      <c r="E105" s="23">
+        <v>5</v>
+      </c>
+      <c r="F105" s="23">
+        <v>1</v>
+      </c>
+      <c r="G105" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="30">
+      <c r="A106" t="s">
+        <v>90</v>
+      </c>
       <c r="B106" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C106, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G106" s="14"/>
-    </row>
-    <row r="107" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C106" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D106" t="s">
+        <v>14</v>
+      </c>
+      <c r="E106" s="23">
+        <v>5</v>
+      </c>
+      <c r="F106" s="23">
+        <v>2</v>
+      </c>
+      <c r="G106" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="30">
+      <c r="A107" t="s">
+        <v>90</v>
+      </c>
       <c r="B107" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C107, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G107" s="14"/>
-    </row>
-    <row r="108" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C107" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D107" t="s">
+        <v>14</v>
+      </c>
+      <c r="E107" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F107" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="30">
+      <c r="A108" t="s">
+        <v>90</v>
+      </c>
       <c r="B108" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C108, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G108" s="14"/>
-    </row>
-    <row r="109" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C108" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D108" t="s">
+        <v>14</v>
+      </c>
+      <c r="E108" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F108" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G108" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" ht="30">
+      <c r="A109" t="s">
+        <v>90</v>
+      </c>
       <c r="B109" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C109, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G109" s="14"/>
-    </row>
-    <row r="110" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C109" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D109" t="s">
+        <v>14</v>
+      </c>
+      <c r="E109" s="23">
+        <v>4</v>
+      </c>
+      <c r="F109" s="23">
+        <v>1</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="30">
+      <c r="A110" t="s">
+        <v>90</v>
+      </c>
       <c r="B110" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C110, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G110" s="14"/>
-    </row>
-    <row r="111" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C110" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D110" t="s">
+        <v>14</v>
+      </c>
+      <c r="E110" s="23">
+        <v>9</v>
+      </c>
+      <c r="F110" s="23">
+        <v>3</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" ht="30">
+      <c r="A111" t="s">
+        <v>90</v>
+      </c>
       <c r="B111" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C111, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G111" s="14"/>
-    </row>
-    <row r="112" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C111" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D111" t="s">
+        <v>14</v>
+      </c>
+      <c r="E111" s="23">
+        <v>-9</v>
+      </c>
+      <c r="F111" s="23">
+        <v>-3</v>
+      </c>
+      <c r="G111" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" ht="30">
+      <c r="A112" t="s">
+        <v>91</v>
+      </c>
       <c r="B112" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C112, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G112" s="14"/>
-    </row>
-    <row r="113" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C112" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D112" t="s">
+        <v>10</v>
+      </c>
+      <c r="E112" s="23">
+        <v>9</v>
+      </c>
+      <c r="F112" s="23">
+        <v>7</v>
+      </c>
+      <c r="G112" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="30">
+      <c r="A113" t="s">
+        <v>91</v>
+      </c>
       <c r="B113" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C113, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G113" s="14"/>
-    </row>
-    <row r="114" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C113" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D113" t="s">
+        <v>10</v>
+      </c>
+      <c r="E113" s="23">
+        <v>8</v>
+      </c>
+      <c r="F113" s="23">
+        <v>7</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" ht="30">
+      <c r="A114" t="s">
+        <v>91</v>
+      </c>
       <c r="B114" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C114, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G114" s="14"/>
-    </row>
-    <row r="115" spans="2:7">
+        <v>ATO011</v>
+      </c>
+      <c r="C114" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D114" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" s="23">
+        <v>7</v>
+      </c>
+      <c r="F114" s="23">
+        <v>7</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" ht="30">
+      <c r="A115" t="s">
+        <v>91</v>
+      </c>
       <c r="B115" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C115, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G115" s="14"/>
-    </row>
-    <row r="116" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C115" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D115" t="s">
+        <v>10</v>
+      </c>
+      <c r="E115" s="23">
+        <v>6</v>
+      </c>
+      <c r="F115" s="23">
+        <v>7</v>
+      </c>
+      <c r="G115" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="30">
+      <c r="A116" t="s">
+        <v>91</v>
+      </c>
       <c r="B116" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C116, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G116" s="14"/>
-    </row>
-    <row r="117" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C116" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D116" t="s">
+        <v>10</v>
+      </c>
+      <c r="E116" s="23">
+        <v>0</v>
+      </c>
+      <c r="F116" s="23">
+        <v>0</v>
+      </c>
+      <c r="G116" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="30">
+      <c r="A117" t="s">
+        <v>91</v>
+      </c>
       <c r="B117" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C117, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G117" s="14"/>
-    </row>
-    <row r="118" spans="2:7">
+        <v>ATO012</v>
+      </c>
+      <c r="C117" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="D117" t="s">
+        <v>14</v>
+      </c>
+      <c r="E117" s="23">
+        <v>-4</v>
+      </c>
+      <c r="F117" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="30">
+      <c r="A118" t="s">
+        <v>91</v>
+      </c>
       <c r="B118" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C118, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G118" s="14"/>
-    </row>
-    <row r="119" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C118" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D118" t="s">
+        <v>14</v>
+      </c>
+      <c r="E118" s="23">
+        <v>2</v>
+      </c>
+      <c r="F118" s="23">
+        <v>2</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="30">
+      <c r="A119" t="s">
+        <v>91</v>
+      </c>
       <c r="B119" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C119, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G119" s="14"/>
-    </row>
-    <row r="120" spans="2:7">
+        <v>ATO011</v>
+      </c>
+      <c r="C119" s="23" t="s">
+        <v>65</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" s="23">
+        <v>0</v>
+      </c>
+      <c r="F119" s="23">
+        <v>0</v>
+      </c>
+      <c r="G119" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="30">
+      <c r="A120" t="s">
+        <v>91</v>
+      </c>
       <c r="B120" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C120, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G120" s="14"/>
-    </row>
-    <row r="121" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C120" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F120" s="23">
+        <v>-1</v>
+      </c>
+      <c r="G120" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" ht="30">
+      <c r="A121" t="s">
+        <v>91</v>
+      </c>
       <c r="B121" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C121, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G121" s="14"/>
-    </row>
-    <row r="122" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C121" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" s="23">
+        <v>4</v>
+      </c>
+      <c r="F121" s="23">
+        <v>4</v>
+      </c>
+      <c r="G121" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="30">
+      <c r="A122" t="s">
+        <v>92</v>
+      </c>
       <c r="B122" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C122, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G122" s="14"/>
-    </row>
-    <row r="123" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C122" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D122" t="s">
+        <v>10</v>
+      </c>
+      <c r="E122" s="23">
+        <v>-8</v>
+      </c>
+      <c r="F122" s="23">
+        <v>-4</v>
+      </c>
+      <c r="G122" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" ht="30">
+      <c r="A123" t="s">
+        <v>92</v>
+      </c>
       <c r="B123" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C123, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G123" s="14"/>
-    </row>
-    <row r="124" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C123" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D123" t="s">
+        <v>10</v>
+      </c>
+      <c r="E123" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F123" s="23">
+        <v>-5</v>
+      </c>
+      <c r="G123" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" ht="30">
+      <c r="A124" t="s">
+        <v>92</v>
+      </c>
       <c r="B124" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C124, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G124" s="14"/>
-    </row>
-    <row r="125" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C124" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D124" t="s">
+        <v>10</v>
+      </c>
+      <c r="E124" s="23">
+        <v>-7</v>
+      </c>
+      <c r="F124" s="23">
+        <v>-4</v>
+      </c>
+      <c r="G124" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="30">
+      <c r="A125" t="s">
+        <v>92</v>
+      </c>
       <c r="B125" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C125, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G125" s="14"/>
-    </row>
-    <row r="126" spans="2:7">
+        <v>ATO008</v>
+      </c>
+      <c r="C125" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D125" t="s">
+        <v>10</v>
+      </c>
+      <c r="E125" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F125" s="23">
+        <v>-3</v>
+      </c>
+      <c r="G125" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" ht="30">
+      <c r="A126" t="s">
+        <v>92</v>
+      </c>
       <c r="B126" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C126, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G126" s="14"/>
-    </row>
-    <row r="127" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C126" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D126" t="s">
+        <v>10</v>
+      </c>
+      <c r="E126" s="23">
+        <v>-5</v>
+      </c>
+      <c r="F126" s="23">
+        <v>-4</v>
+      </c>
+      <c r="G126" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" ht="30">
+      <c r="A127" t="s">
+        <v>92</v>
+      </c>
       <c r="B127" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C127, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G127" s="14"/>
-    </row>
-    <row r="128" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C127" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D127" t="s">
+        <v>10</v>
+      </c>
+      <c r="E127" s="23">
+        <v>-5</v>
+      </c>
+      <c r="F127" s="23">
+        <v>-4</v>
+      </c>
+      <c r="G127" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="30">
+      <c r="A128" t="s">
+        <v>92</v>
+      </c>
       <c r="B128" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C128, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G128" s="14"/>
-    </row>
-    <row r="129" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C128" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D128" t="s">
+        <v>14</v>
+      </c>
+      <c r="E128" s="23">
+        <v>6</v>
+      </c>
+      <c r="F128" s="23">
+        <v>2</v>
+      </c>
+      <c r="G128" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" ht="30">
+      <c r="A129" t="s">
+        <v>92</v>
+      </c>
       <c r="B129" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C129, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G129" s="14"/>
-    </row>
-    <row r="130" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C129" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D129" t="s">
+        <v>14</v>
+      </c>
+      <c r="E129" s="23">
+        <v>-8</v>
+      </c>
+      <c r="F129" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G129" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="30">
+      <c r="A130" t="s">
+        <v>92</v>
+      </c>
       <c r="B130" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C130, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G130" s="14"/>
-    </row>
-    <row r="131" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C130" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D130" t="s">
+        <v>14</v>
+      </c>
+      <c r="E130" s="23">
+        <v>5</v>
+      </c>
+      <c r="F130" s="23">
+        <v>1</v>
+      </c>
+      <c r="G130" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="30">
+      <c r="A131" t="s">
+        <v>92</v>
+      </c>
       <c r="B131" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C131, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G131" s="14"/>
-    </row>
-    <row r="132" spans="2:7">
+        <v>ATO008</v>
+      </c>
+      <c r="C131" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D131" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" s="23">
+        <v>4</v>
+      </c>
+      <c r="F131" s="23">
+        <v>1</v>
+      </c>
+      <c r="G131" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="30">
+      <c r="A132" t="s">
+        <v>92</v>
+      </c>
       <c r="B132" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C132, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G132" s="14"/>
-    </row>
-    <row r="133" spans="2:7">
+        <v>ATO009</v>
+      </c>
+      <c r="C132" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" s="23">
+        <v>-7</v>
+      </c>
+      <c r="F132" s="23">
+        <v>-3</v>
+      </c>
+      <c r="G132" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" ht="30">
+      <c r="A133" t="s">
+        <v>92</v>
+      </c>
       <c r="B133" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C133, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G133" s="14"/>
-    </row>
-    <row r="134" spans="2:7">
+        <v>ATO010</v>
+      </c>
+      <c r="C133" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133" s="23">
+        <v>-7</v>
+      </c>
+      <c r="F133" s="23">
+        <v>-3</v>
+      </c>
+      <c r="G133" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" ht="30">
+      <c r="A134" t="s">
+        <v>93</v>
+      </c>
       <c r="B134" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C134, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G134" s="14"/>
-    </row>
-    <row r="135" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C134" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D134" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134" s="23">
+        <v>-5</v>
+      </c>
+      <c r="F134" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G134" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" ht="30">
+      <c r="A135" t="s">
+        <v>93</v>
+      </c>
       <c r="B135" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C135, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G135" s="14"/>
-    </row>
-    <row r="136" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C135" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D135" t="s">
+        <v>10</v>
+      </c>
+      <c r="E135" s="23">
+        <v>-4</v>
+      </c>
+      <c r="F135" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G135" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" ht="30">
+      <c r="A136" t="s">
+        <v>93</v>
+      </c>
       <c r="B136" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C136, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G136" s="14"/>
-    </row>
-    <row r="137" spans="2:7">
+        <v>ATO004</v>
+      </c>
+      <c r="C136" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D136" t="s">
+        <v>10</v>
+      </c>
+      <c r="E136" s="23">
+        <v>0</v>
+      </c>
+      <c r="F136" s="23">
+        <v>0</v>
+      </c>
+      <c r="G136" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" ht="30">
+      <c r="A137" t="s">
+        <v>93</v>
+      </c>
       <c r="B137" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C137, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G137" s="14"/>
-    </row>
-    <row r="138" spans="2:7">
+        <v>ATO005</v>
+      </c>
+      <c r="C137" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D137" t="s">
+        <v>10</v>
+      </c>
+      <c r="E137" s="23">
+        <v>0</v>
+      </c>
+      <c r="F137" s="23">
+        <v>0</v>
+      </c>
+      <c r="G137" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" ht="30">
+      <c r="A138" t="s">
+        <v>93</v>
+      </c>
       <c r="B138" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C138, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G138" s="14"/>
-    </row>
-    <row r="139" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C138" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D138" t="s">
+        <v>10</v>
+      </c>
+      <c r="E138" s="23">
+        <v>0</v>
+      </c>
+      <c r="F138" s="23">
+        <v>0</v>
+      </c>
+      <c r="G138" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" ht="30">
+      <c r="A139" t="s">
+        <v>93</v>
+      </c>
       <c r="B139" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C139, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G139" s="14"/>
-    </row>
-    <row r="140" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C139" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D139" t="s">
+        <v>10</v>
+      </c>
+      <c r="E139" s="23">
+        <v>0</v>
+      </c>
+      <c r="F139" s="23">
+        <v>0</v>
+      </c>
+      <c r="G139" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" ht="30">
+      <c r="A140" t="s">
+        <v>93</v>
+      </c>
       <c r="B140" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C140, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G140" s="14"/>
-    </row>
-    <row r="141" spans="2:7">
+        <v>ATO015</v>
+      </c>
+      <c r="C140" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="D140" t="s">
+        <v>14</v>
+      </c>
+      <c r="E140" s="23">
+        <v>7</v>
+      </c>
+      <c r="F140" s="23">
+        <v>4</v>
+      </c>
+      <c r="G140" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" ht="30">
+      <c r="A141" t="s">
+        <v>93</v>
+      </c>
       <c r="B141" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C141, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G141" s="14"/>
-    </row>
-    <row r="142" spans="2:7">
+        <v>ATO003</v>
+      </c>
+      <c r="C141" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="D141" t="s">
+        <v>14</v>
+      </c>
+      <c r="E141" s="23">
+        <v>6</v>
+      </c>
+      <c r="F141" s="23">
+        <v>4</v>
+      </c>
+      <c r="G141" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" ht="30">
+      <c r="A142" t="s">
+        <v>93</v>
+      </c>
       <c r="B142" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C142, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G142" s="14"/>
-    </row>
-    <row r="143" spans="2:7">
+        <v>ATO004</v>
+      </c>
+      <c r="C142" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="D142" t="s">
+        <v>14</v>
+      </c>
+      <c r="E142" s="23">
+        <v>-2</v>
+      </c>
+      <c r="F142" s="23">
+        <v>2</v>
+      </c>
+      <c r="G142" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" ht="30">
+      <c r="A143" t="s">
+        <v>93</v>
+      </c>
       <c r="B143" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C143, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G143" s="14"/>
-    </row>
-    <row r="144" spans="2:7">
+        <v>ATO005</v>
+      </c>
+      <c r="C143" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="D143" t="s">
+        <v>14</v>
+      </c>
+      <c r="E143" s="23">
+        <v>-3</v>
+      </c>
+      <c r="F143" s="23">
+        <v>3</v>
+      </c>
+      <c r="G143" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" ht="30">
+      <c r="A144" t="s">
+        <v>93</v>
+      </c>
       <c r="B144" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C144, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G144" s="14"/>
-    </row>
-    <row r="145" spans="2:7">
+        <v>ATO001</v>
+      </c>
+      <c r="C144" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="D144" t="s">
+        <v>14</v>
+      </c>
+      <c r="E144" s="23">
+        <v>5</v>
+      </c>
+      <c r="F144" s="23">
+        <v>5</v>
+      </c>
+      <c r="G144" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" ht="30">
+      <c r="A145" t="s">
+        <v>93</v>
+      </c>
       <c r="B145" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C145, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G145" s="14"/>
-    </row>
-    <row r="146" spans="2:7">
+        <v>ATO006</v>
+      </c>
+      <c r="C145" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="D145" t="s">
+        <v>14</v>
+      </c>
+      <c r="E145" s="23">
+        <v>-6</v>
+      </c>
+      <c r="F145" s="23">
+        <v>-2</v>
+      </c>
+      <c r="G145" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" ht="30">
+      <c r="A146" t="s">
+        <v>94</v>
+      </c>
       <c r="B146" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C146, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G146" s="14"/>
-    </row>
-    <row r="147" spans="2:7">
+        <v>ATO016</v>
+      </c>
+      <c r="C146" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="D146" t="s">
+        <v>14</v>
+      </c>
+      <c r="E146" s="23">
+        <v>10</v>
+      </c>
+      <c r="F146" s="23">
+        <v>8</v>
+      </c>
+      <c r="G146" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7">
       <c r="B147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C147, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G147" s="14"/>
     </row>
-    <row r="148" spans="2:7">
+    <row r="148" spans="1:7">
       <c r="B148" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C148, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G148" s="14"/>
     </row>
-    <row r="149" spans="2:7">
+    <row r="149" spans="1:7">
       <c r="B149" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C149, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G149" s="14"/>
     </row>
-    <row r="150" spans="2:7">
+    <row r="150" spans="1:7">
       <c r="B150" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C150, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G150" s="14"/>
     </row>
-    <row r="151" spans="2:7">
+    <row r="151" spans="1:7">
       <c r="B151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C151, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G151" s="14"/>
     </row>
-    <row r="152" spans="2:7">
+    <row r="152" spans="1:7">
       <c r="B152" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C152, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G152" s="14"/>
     </row>
-    <row r="153" spans="2:7">
+    <row r="153" spans="1:7">
       <c r="B153" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C153, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G153" s="14"/>
     </row>
-    <row r="154" spans="2:7">
+    <row r="154" spans="1:7">
       <c r="B154" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C154, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G154" s="14"/>
     </row>
-    <row r="155" spans="2:7">
+    <row r="155" spans="1:7">
       <c r="B155" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C155, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G155" s="14"/>
     </row>
-    <row r="156" spans="2:7">
+    <row r="156" spans="1:7">
       <c r="B156" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C156, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G156" s="14"/>
     </row>
-    <row r="157" spans="2:7">
+    <row r="157" spans="1:7">
       <c r="B157" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C157, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G157" s="14"/>
     </row>
-    <row r="158" spans="2:7">
+    <row r="158" spans="1:7">
       <c r="B158" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C158, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G158" s="14"/>
     </row>
-    <row r="159" spans="2:7">
+    <row r="159" spans="1:7">
       <c r="B159" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C159, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G159" s="14"/>
     </row>
-    <row r="160" spans="2:7">
+    <row r="160" spans="1:7">
       <c r="B160" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C160, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -7964,13 +11138,6 @@
         <v/>
       </c>
       <c r="G327" s="14"/>
-    </row>
-    <row r="328" spans="2:7">
-      <c r="B328" t="str">
-        <f>IFERROR(_xlfn.XLOOKUP(C328, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G328" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9123456-D840-475D-B245-839243D8B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10CB83E-5DA0-4C5E-8C4E-01DAFCB1138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="relations_daily" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="325">
   <si>
     <t>data</t>
   </si>
@@ -1038,6 +1038,15 @@
   </si>
   <si>
     <t>Respostas às Aç de VERMELHO em busca de apoio ao MPL</t>
+  </si>
+  <si>
+    <t>Aliado</t>
+  </si>
+  <si>
+    <t>Dissuasão Dominante</t>
+  </si>
+  <si>
+    <t>Parceiro</t>
   </si>
 </sst>
 </file>
@@ -3859,7 +3868,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="30">
+    <row r="69" spans="1:9">
       <c r="A69" s="1">
         <v>45958</v>
       </c>
@@ -3870,15 +3879,15 @@
         <v>10</v>
       </c>
       <c r="D69">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="E69">
-        <v>62</v>
-      </c>
-      <c r="F69" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G69" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="F69" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" t="s">
         <v>77</v>
       </c>
       <c r="H69" t="s">
@@ -3888,7 +3897,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="30">
+    <row r="70" spans="1:9">
       <c r="A70" s="1">
         <v>45958</v>
       </c>
@@ -3899,15 +3908,15 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E70">
-        <v>65</v>
-      </c>
-      <c r="F70" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F70" t="s">
         <v>11</v>
       </c>
-      <c r="G70" s="21" t="s">
+      <c r="G70" t="s">
         <v>77</v>
       </c>
       <c r="H70" t="s">
@@ -3917,7 +3926,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="30">
+    <row r="71" spans="1:9">
       <c r="A71" s="1">
         <v>45958</v>
       </c>
@@ -3928,16 +3937,16 @@
         <v>10</v>
       </c>
       <c r="D71">
-        <v>63</v>
+        <v>35</v>
       </c>
       <c r="E71">
-        <v>54</v>
-      </c>
-      <c r="F71" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" s="21" t="s">
-        <v>78</v>
+        <v>70</v>
+      </c>
+      <c r="F71" t="s">
+        <v>74</v>
+      </c>
+      <c r="G71" t="s">
+        <v>77</v>
       </c>
       <c r="H71" t="s">
         <v>12</v>
@@ -3946,7 +3955,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="30">
+    <row r="72" spans="1:9">
       <c r="A72" s="1">
         <v>45958</v>
       </c>
@@ -3962,10 +3971,10 @@
       <c r="E72">
         <v>51</v>
       </c>
-      <c r="F72" s="21" t="s">
+      <c r="F72" t="s">
         <v>11</v>
       </c>
-      <c r="G72" s="21" t="s">
+      <c r="G72" t="s">
         <v>78</v>
       </c>
       <c r="H72" t="s">
@@ -3975,7 +3984,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="30">
+    <row r="73" spans="1:9">
       <c r="A73" s="1">
         <v>45958</v>
       </c>
@@ -3991,10 +4000,10 @@
       <c r="E73">
         <v>61</v>
       </c>
-      <c r="F73" s="20" t="s">
+      <c r="F73" t="s">
         <v>75</v>
       </c>
-      <c r="G73" s="21" t="s">
+      <c r="G73" t="s">
         <v>77</v>
       </c>
       <c r="H73" t="s">
@@ -4004,7 +4013,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30">
+    <row r="74" spans="1:9">
       <c r="A74" s="1">
         <v>45958</v>
       </c>
@@ -4015,16 +4024,16 @@
         <v>10</v>
       </c>
       <c r="D74">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="E74">
-        <v>64</v>
-      </c>
-      <c r="F74" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G74" s="21" t="s">
-        <v>78</v>
+        <v>93</v>
+      </c>
+      <c r="F74" t="s">
+        <v>322</v>
+      </c>
+      <c r="G74" t="s">
+        <v>323</v>
       </c>
       <c r="H74" t="s">
         <v>12</v>
@@ -4033,7 +4042,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="30">
+    <row r="75" spans="1:9">
       <c r="A75" s="1">
         <v>45958</v>
       </c>
@@ -4049,10 +4058,10 @@
       <c r="E75">
         <v>58</v>
       </c>
-      <c r="F75" s="20" t="s">
+      <c r="F75" t="s">
         <v>74</v>
       </c>
-      <c r="G75" s="21" t="s">
+      <c r="G75" t="s">
         <v>78</v>
       </c>
       <c r="H75" t="s">
@@ -4062,7 +4071,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="30">
+    <row r="76" spans="1:9">
       <c r="A76" s="1">
         <v>45958</v>
       </c>
@@ -4073,15 +4082,15 @@
         <v>10</v>
       </c>
       <c r="D76">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E76">
-        <v>50</v>
-      </c>
-      <c r="F76" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G76" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F76" t="s">
+        <v>80</v>
+      </c>
+      <c r="G76" t="s">
         <v>78</v>
       </c>
       <c r="H76" t="s">
@@ -4091,7 +4100,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="30">
+    <row r="77" spans="1:9">
       <c r="A77" s="1">
         <v>45958</v>
       </c>
@@ -4102,15 +4111,15 @@
         <v>10</v>
       </c>
       <c r="D77">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E77">
-        <v>61</v>
-      </c>
-      <c r="F77" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F77" t="s">
         <v>11</v>
       </c>
-      <c r="G77" s="21" t="s">
+      <c r="G77" t="s">
         <v>77</v>
       </c>
       <c r="H77" t="s">
@@ -4120,7 +4129,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="30">
+    <row r="78" spans="1:9">
       <c r="A78" s="1">
         <v>45958</v>
       </c>
@@ -4131,15 +4140,15 @@
         <v>10</v>
       </c>
       <c r="D78">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E78">
-        <v>61</v>
-      </c>
-      <c r="F78" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="F78" t="s">
         <v>11</v>
       </c>
-      <c r="G78" s="21" t="s">
+      <c r="G78" t="s">
         <v>77</v>
       </c>
       <c r="H78" t="s">
@@ -4149,7 +4158,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="30">
+    <row r="79" spans="1:9">
       <c r="A79" s="1">
         <v>45958</v>
       </c>
@@ -4160,16 +4169,16 @@
         <v>10</v>
       </c>
       <c r="D79">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="E79">
-        <v>52</v>
-      </c>
-      <c r="F79" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="G79" s="21" t="s">
-        <v>78</v>
+        <v>69</v>
+      </c>
+      <c r="F79" t="s">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s">
+        <v>77</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -4178,7 +4187,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="30">
+    <row r="80" spans="1:9">
       <c r="A80" s="1">
         <v>45958</v>
       </c>
@@ -4189,15 +4198,15 @@
         <v>10</v>
       </c>
       <c r="D80">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E80">
-        <v>45</v>
-      </c>
-      <c r="F80" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G80" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F80" t="s">
+        <v>75</v>
+      </c>
+      <c r="G80" t="s">
         <v>78</v>
       </c>
       <c r="H80" t="s">
@@ -4207,7 +4216,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="30">
+    <row r="81" spans="1:9">
       <c r="A81" s="1">
         <v>45958</v>
       </c>
@@ -4218,15 +4227,15 @@
         <v>10</v>
       </c>
       <c r="D81">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E81">
-        <v>47</v>
-      </c>
-      <c r="F81" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G81" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F81" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" t="s">
         <v>78</v>
       </c>
       <c r="H81" t="s">
@@ -4236,7 +4245,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="30">
+    <row r="82" spans="1:9">
       <c r="A82" s="1">
         <v>45958</v>
       </c>
@@ -4247,15 +4256,15 @@
         <v>10</v>
       </c>
       <c r="D82">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E82">
-        <v>66</v>
-      </c>
-      <c r="F82" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="F82" t="s">
         <v>76</v>
       </c>
-      <c r="G82" s="21" t="s">
+      <c r="G82" t="s">
         <v>77</v>
       </c>
       <c r="H82" t="s">
@@ -4265,7 +4274,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="30">
+    <row r="83" spans="1:9">
       <c r="A83" s="1">
         <v>45958</v>
       </c>
@@ -4276,16 +4285,16 @@
         <v>10</v>
       </c>
       <c r="D83">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="E83">
-        <v>72</v>
-      </c>
-      <c r="F83" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G83" s="21" t="s">
-        <v>77</v>
+        <v>86</v>
+      </c>
+      <c r="F83" t="s">
+        <v>76</v>
+      </c>
+      <c r="G83" t="s">
+        <v>323</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -4305,16 +4314,16 @@
         <v>10</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E84">
-        <v>34</v>
-      </c>
-      <c r="F84" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" t="s">
         <v>75</v>
       </c>
-      <c r="G84" s="21" t="s">
-        <v>79</v>
+      <c r="G84" t="s">
+        <v>78</v>
       </c>
       <c r="H84" t="s">
         <v>12</v>
@@ -4323,7 +4332,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="30">
+    <row r="85" spans="1:9">
       <c r="A85" s="1">
         <v>45958</v>
       </c>
@@ -4334,16 +4343,16 @@
         <v>14</v>
       </c>
       <c r="D85">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="E85">
-        <v>55</v>
-      </c>
-      <c r="F85" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G85" s="21" t="s">
-        <v>78</v>
+        <v>74</v>
+      </c>
+      <c r="F85" t="s">
+        <v>324</v>
+      </c>
+      <c r="G85" t="s">
+        <v>77</v>
       </c>
       <c r="H85" t="s">
         <v>12</v>
@@ -4352,7 +4361,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="30">
+    <row r="86" spans="1:9">
       <c r="A86" s="1">
         <v>45958</v>
       </c>
@@ -4366,12 +4375,12 @@
         <v>60</v>
       </c>
       <c r="E86">
-        <v>62</v>
-      </c>
-      <c r="F86" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F86" t="s">
         <v>76</v>
       </c>
-      <c r="G86" s="21" t="s">
+      <c r="G86" t="s">
         <v>77</v>
       </c>
       <c r="H86" t="s">
@@ -4381,7 +4390,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="30">
+    <row r="87" spans="1:9">
       <c r="A87" s="1">
         <v>45958</v>
       </c>
@@ -4392,16 +4401,16 @@
         <v>14</v>
       </c>
       <c r="D87">
-        <v>53</v>
+        <v>70</v>
       </c>
       <c r="E87">
-        <v>53</v>
-      </c>
-      <c r="F87" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G87" s="21" t="s">
-        <v>78</v>
+        <v>65</v>
+      </c>
+      <c r="F87" t="s">
+        <v>324</v>
+      </c>
+      <c r="G87" t="s">
+        <v>77</v>
       </c>
       <c r="H87" t="s">
         <v>12</v>
@@ -4410,7 +4419,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="30">
+    <row r="88" spans="1:9">
       <c r="A88" s="1">
         <v>45958</v>
       </c>
@@ -4421,15 +4430,15 @@
         <v>14</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E88">
-        <v>48</v>
-      </c>
-      <c r="F88" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F88" t="s">
         <v>75</v>
       </c>
-      <c r="G88" s="21" t="s">
+      <c r="G88" t="s">
         <v>78</v>
       </c>
       <c r="H88" t="s">
@@ -4439,7 +4448,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="30">
+    <row r="89" spans="1:9">
       <c r="A89" s="1">
         <v>45958</v>
       </c>
@@ -4450,15 +4459,15 @@
         <v>14</v>
       </c>
       <c r="D89">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E89">
-        <v>66</v>
-      </c>
-      <c r="F89" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="F89" t="s">
         <v>80</v>
       </c>
-      <c r="G89" s="21" t="s">
+      <c r="G89" t="s">
         <v>77</v>
       </c>
       <c r="H89" t="s">
@@ -4468,7 +4477,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="30">
+    <row r="90" spans="1:9">
       <c r="A90" s="1">
         <v>45958</v>
       </c>
@@ -4479,16 +4488,16 @@
         <v>14</v>
       </c>
       <c r="D90">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="E90">
-        <v>43</v>
-      </c>
-      <c r="F90" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G90" s="21" t="s">
-        <v>78</v>
+        <v>35</v>
+      </c>
+      <c r="F90" t="s">
+        <v>75</v>
+      </c>
+      <c r="G90" t="s">
+        <v>79</v>
       </c>
       <c r="H90" t="s">
         <v>12</v>
@@ -4497,7 +4506,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="30">
+    <row r="91" spans="1:9">
       <c r="A91" s="1">
         <v>45958</v>
       </c>
@@ -4513,10 +4522,10 @@
       <c r="E91">
         <v>59</v>
       </c>
-      <c r="F91" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="G91" s="21" t="s">
+      <c r="F91" t="s">
+        <v>80</v>
+      </c>
+      <c r="G91" t="s">
         <v>78</v>
       </c>
       <c r="H91" t="s">
@@ -4526,7 +4535,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="30">
+    <row r="92" spans="1:9">
       <c r="A92" s="1">
         <v>45958</v>
       </c>
@@ -4537,15 +4546,15 @@
         <v>14</v>
       </c>
       <c r="D92">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E92">
-        <v>50</v>
-      </c>
-      <c r="F92" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" t="s">
         <v>11</v>
       </c>
-      <c r="G92" s="21" t="s">
+      <c r="G92" t="s">
         <v>78</v>
       </c>
       <c r="H92" t="s">
@@ -4555,7 +4564,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="30">
+    <row r="93" spans="1:9">
       <c r="A93" s="1">
         <v>45958</v>
       </c>
@@ -4566,16 +4575,16 @@
         <v>14</v>
       </c>
       <c r="D93">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="E93">
-        <v>62</v>
-      </c>
-      <c r="F93" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G93" s="21" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="F93" t="s">
+        <v>74</v>
+      </c>
+      <c r="G93" t="s">
+        <v>78</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -4584,7 +4593,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="30">
+    <row r="94" spans="1:9">
       <c r="A94" s="1">
         <v>45958</v>
       </c>
@@ -4595,16 +4604,16 @@
         <v>14</v>
       </c>
       <c r="D94">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E94">
-        <v>62</v>
-      </c>
-      <c r="F94" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="21" t="s">
-        <v>77</v>
+        <v>59</v>
+      </c>
+      <c r="F94" t="s">
+        <v>74</v>
+      </c>
+      <c r="G94" t="s">
+        <v>78</v>
       </c>
       <c r="H94" t="s">
         <v>12</v>
@@ -4613,7 +4622,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="30">
+    <row r="95" spans="1:9">
       <c r="A95" s="1">
         <v>45958</v>
       </c>
@@ -4624,15 +4633,15 @@
         <v>14</v>
       </c>
       <c r="D95">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="E95">
-        <v>51</v>
-      </c>
-      <c r="F95" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G95" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F95" t="s">
+        <v>74</v>
+      </c>
+      <c r="G95" t="s">
         <v>78</v>
       </c>
       <c r="H95" t="s">
@@ -4642,7 +4651,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="30">
+    <row r="96" spans="1:9">
       <c r="A96" s="1">
         <v>45958</v>
       </c>
@@ -4653,16 +4662,16 @@
         <v>14</v>
       </c>
       <c r="D96">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="E96">
-        <v>52</v>
-      </c>
-      <c r="F96" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="G96" s="21" t="s">
-        <v>78</v>
+        <v>68</v>
+      </c>
+      <c r="F96" t="s">
+        <v>322</v>
+      </c>
+      <c r="G96" t="s">
+        <v>77</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -4671,7 +4680,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="30">
+    <row r="97" spans="1:9">
       <c r="A97" s="1">
         <v>45958</v>
       </c>
@@ -4682,15 +4691,15 @@
         <v>14</v>
       </c>
       <c r="D97">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E97">
         <v>50</v>
       </c>
-      <c r="F97" s="20" t="s">
+      <c r="F97" t="s">
         <v>74</v>
       </c>
-      <c r="G97" s="21" t="s">
+      <c r="G97" t="s">
         <v>78</v>
       </c>
       <c r="H97" t="s">
@@ -4700,7 +4709,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="30">
+    <row r="98" spans="1:9">
       <c r="A98" s="1">
         <v>45958</v>
       </c>
@@ -4711,15 +4720,15 @@
         <v>14</v>
       </c>
       <c r="D98">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="E98">
-        <v>66</v>
-      </c>
-      <c r="F98" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G98" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="F98" t="s">
+        <v>74</v>
+      </c>
+      <c r="G98" t="s">
         <v>77</v>
       </c>
       <c r="H98" t="s">
@@ -4729,7 +4738,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="30">
+    <row r="99" spans="1:9">
       <c r="A99" s="1">
         <v>45958</v>
       </c>
@@ -4740,16 +4749,16 @@
         <v>14</v>
       </c>
       <c r="D99">
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="E99">
-        <v>73</v>
-      </c>
-      <c r="F99" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" s="21" t="s">
-        <v>77</v>
+        <v>85</v>
+      </c>
+      <c r="F99" t="s">
+        <v>322</v>
+      </c>
+      <c r="G99" t="s">
+        <v>323</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -4758,7 +4767,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="30">
+    <row r="100" spans="1:9">
       <c r="A100" s="1">
         <v>45958</v>
       </c>
@@ -4769,16 +4778,16 @@
         <v>14</v>
       </c>
       <c r="D100">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E100">
-        <v>56</v>
-      </c>
-      <c r="F100" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="G100" s="21" t="s">
-        <v>78</v>
+        <v>61</v>
+      </c>
+      <c r="F100" t="s">
+        <v>76</v>
+      </c>
+      <c r="G100" t="s">
+        <v>77</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>

--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10CB83E-5DA0-4C5E-8C4E-01DAFCB1138B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BEB861-2543-4043-8CE0-49B71066976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BEB861-2543-4043-8CE0-49B71066976E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3B8402-5AAB-4030-9BD4-479EC79A1485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="325">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="333">
   <si>
     <t>data</t>
   </si>
@@ -1040,13 +1040,37 @@
     <t>Respostas às Aç de VERMELHO em busca de apoio ao MPL</t>
   </si>
   <si>
-    <t>Aliado</t>
-  </si>
-  <si>
-    <t>Dissuasão Dominante</t>
-  </si>
-  <si>
-    <t>Parceiro</t>
+    <t>Hostil (20–34)</t>
+  </si>
+  <si>
+    <t>Respeito/Temor Elevado (60–79)</t>
+  </si>
+  <si>
+    <t>Neutro (50–59)</t>
+  </si>
+  <si>
+    <t>Tenso/Desfavorável (35–49)</t>
+  </si>
+  <si>
+    <t>Respeito/Temor Moderado (40–59)</t>
+  </si>
+  <si>
+    <t>Hostilidade extrema (0–19)</t>
+  </si>
+  <si>
+    <t>Aliado (80–100)</t>
+  </si>
+  <si>
+    <t>Dissuasão Dominante (80–100)</t>
+  </si>
+  <si>
+    <t>Cooperativo (60–69)</t>
+  </si>
+  <si>
+    <t>Parceiro (70–79)</t>
+  </si>
+  <si>
+    <t>Respeito/Temor Baixo (20–39)</t>
   </si>
 </sst>
 </file>
@@ -1251,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1304,11 +1328,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="24">
+    <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1607,7 +1637,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B7E38C3E-8A3D-4434-8337-0420E18C2416}" name="Tabela4" displayName="Tabela4" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B7E38C3E-8A3D-4434-8337-0420E18C2416}" name="Tabela4" displayName="Tabela4" ref="A1:I1048576" totalsRowShown="0" headerRowDxfId="23">
   <autoFilter ref="A1:I1048576" xr:uid="{B7E38C3E-8A3D-4434-8337-0420E18C2416}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{903F7B59-588A-4677-91D4-CAFFEF4BCC9C}" name="data"/>
@@ -1616,7 +1646,7 @@
     <tableColumn id="4" xr3:uid="{7F40A552-08DB-47E5-B8C9-D234A3618AC7}" name="R"/>
     <tableColumn id="5" xr3:uid="{6D524766-1B99-4A6B-BBB8-2C07618F12BD}" name="C"/>
     <tableColumn id="6" xr3:uid="{975C8660-93D0-4033-AA43-8AA370C045E9}" name="class_R"/>
-    <tableColumn id="7" xr3:uid="{B6DA6EC3-D88E-4812-89CE-2FD27455D195}" name="class_C"/>
+    <tableColumn id="7" xr3:uid="{B6DA6EC3-D88E-4812-89CE-2FD27455D195}" name="class_C" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{2DC65DDE-891F-45C1-A625-9C1EA845FBAC}" name="fonte_regra"/>
     <tableColumn id="9" xr3:uid="{ED276677-25B8-4FBE-A338-C1FDCB7FC603}" name="obs"/>
   </tableColumns>
@@ -1625,48 +1655,48 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A3AD564-B18D-4439-A198-8AF944A99772}" name="tblActors" displayName="tblActors" ref="A1:D17" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A3AD564-B18D-4439-A198-8AF944A99772}" name="tblActors" displayName="tblActors" ref="A1:D17" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
   <autoFilter ref="A1:D17" xr:uid="{5A3AD564-B18D-4439-A198-8AF944A99772}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3122FF93-D7C9-47C4-AAE7-E5CBE0FA3A54}" name="actor_id" dataDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{2220D84D-1A4B-4A12-888A-7592053EDECC}" name="nome" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{7244E1B6-C06A-46BA-A29E-7198716E593E}" name="tipo" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{10B1B0CA-D667-4698-9FAC-A50EC4C9BE0A}" name="cluster_opcional" dataDxfId="14"/>
+    <tableColumn id="1" xr3:uid="{3122FF93-D7C9-47C4-AAE7-E5CBE0FA3A54}" name="actor_id" dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{2220D84D-1A4B-4A12-888A-7592053EDECC}" name="nome" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{7244E1B6-C06A-46BA-A29E-7198716E593E}" name="tipo" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{10B1B0CA-D667-4698-9FAC-A50EC4C9BE0A}" name="cluster_opcional" dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EE140BC-D0AD-4653-A557-FEB72E7706BB}" name="Tabela3" displayName="Tabela3" ref="A1:H279" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EE140BC-D0AD-4653-A557-FEB72E7706BB}" name="Tabela3" displayName="Tabela3" ref="A1:H279" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A1:H279" xr:uid="{8EE140BC-D0AD-4653-A557-FEB72E7706BB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A64D0630-7FB4-4675-AF15-DFA9CC4C3218}" name="event_id"/>
     <tableColumn id="2" xr3:uid="{ABB220E9-794F-4B06-80FB-EA100148E885}" name="data"/>
-    <tableColumn id="3" xr3:uid="{DEFA5E68-941A-4720-891C-051748ACEEE4}" name="titulo" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{2AA18C9F-BAB7-429C-BD76-624D918E02A6}" name="descricao" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{ACAD5301-D426-46EE-A7F5-46CA1210DCDF}" name="tipo" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{C20CACB4-38DD-423C-80F3-2EAB1574530A}" name="tags" dataDxfId="7"/>
-    <tableColumn id="7" xr3:uid="{46484C08-2E71-4200-A22E-BF604C745824}" name="fonte" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{9B6E38A2-36A7-42AA-A46E-F35C16B84F1E}" name="responsabilidade" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{DEFA5E68-941A-4720-891C-051748ACEEE4}" name="titulo" dataDxfId="11"/>
+    <tableColumn id="4" xr3:uid="{2AA18C9F-BAB7-429C-BD76-624D918E02A6}" name="descricao" dataDxfId="10"/>
+    <tableColumn id="5" xr3:uid="{ACAD5301-D426-46EE-A7F5-46CA1210DCDF}" name="tipo" dataDxfId="9"/>
+    <tableColumn id="6" xr3:uid="{C20CACB4-38DD-423C-80F3-2EAB1574530A}" name="tags" dataDxfId="8"/>
+    <tableColumn id="7" xr3:uid="{46484C08-2E71-4200-A22E-BF604C745824}" name="fonte" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{9B6E38A2-36A7-42AA-A46E-F35C16B84F1E}" name="responsabilidade" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K327" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K327" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
   <autoFilter ref="A1:K327" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{BAF761B8-D6AF-48D3-A1F5-3D35088A4234}" name="event_id"/>
-    <tableColumn id="2" xr3:uid="{78C225EA-4EED-44B0-BBCE-FD76B432B72B}" name="actor_id" dataDxfId="1">
+    <tableColumn id="2" xr3:uid="{78C225EA-4EED-44B0-BBCE-FD76B432B72B}" name="actor_id" dataDxfId="2">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(C2, tblActors[nome], tblActors[actor_id], ""), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{37AE2979-DF01-47CD-BEA5-BA034C5B3757}" name="actor_name"/>
     <tableColumn id="4" xr3:uid="{7BDACF9C-965E-4CCF-94CF-242CB57A4AC1}" name="partido"/>
     <tableColumn id="5" xr3:uid="{6A802EC2-6140-4C9F-9D92-0F2B0C6B0D2F}" name="delta_R"/>
     <tableColumn id="6" xr3:uid="{5830257E-D8FA-438E-9298-17ED813D6C77}" name="delta_C"/>
-    <tableColumn id="7" xr3:uid="{ED6BE6E1-B0BE-4C05-8C17-6A8218AD71A0}" name="racional" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{ED6BE6E1-B0BE-4C05-8C17-6A8218AD71A0}" name="racional" dataDxfId="1"/>
     <tableColumn id="8" xr3:uid="{481A5440-CA6F-4A3B-984A-1D2FFA263532}" name="atraso_dias"/>
     <tableColumn id="9" xr3:uid="{DD506A33-5271-4DFF-AAA8-7F12E055CCD0}" name="delta_opiniao_direta"/>
     <tableColumn id="10" xr3:uid="{9B94DE7A-D5B7-427A-A880-C7C51E771C9F}" name="delta_midia"/>
@@ -1961,14 +1991,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" style="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="20.42578125" bestFit="1" customWidth="1"/>
   </cols>
@@ -2901,7 +2931,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="30">
+    <row r="33" spans="1:11" ht="30">
       <c r="A33" s="1">
         <v>45946</v>
       </c>
@@ -2930,17 +2960,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:11">
       <c r="A34" s="1"/>
       <c r="F34" s="20"/>
       <c r="G34" s="21"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:11">
       <c r="A35" s="1"/>
       <c r="F35" s="20"/>
       <c r="G35" s="21"/>
     </row>
-    <row r="36" spans="1:9" ht="30">
+    <row r="36" spans="1:11" ht="30">
       <c r="A36" s="1">
         <v>45952</v>
       </c>
@@ -2969,7 +2999,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="30">
+    <row r="37" spans="1:11" ht="30">
       <c r="A37" s="1">
         <v>45952</v>
       </c>
@@ -2998,7 +3028,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="30">
+    <row r="38" spans="1:11" ht="30">
       <c r="A38" s="1">
         <v>45952</v>
       </c>
@@ -3026,8 +3056,12 @@
       <c r="I38" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="30">
+      <c r="K38">
+        <f>Tabela4[[#This Row],[R]]-25</f>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" ht="30">
       <c r="A39" s="1">
         <v>45952</v>
       </c>
@@ -3056,7 +3090,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="30">
+    <row r="40" spans="1:11" ht="30">
       <c r="A40" s="1">
         <v>45952</v>
       </c>
@@ -3085,7 +3119,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="30">
+    <row r="41" spans="1:11" ht="30">
       <c r="A41" s="1">
         <v>45952</v>
       </c>
@@ -3114,7 +3148,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="30">
+    <row r="42" spans="1:11" ht="30">
       <c r="A42" s="1">
         <v>45952</v>
       </c>
@@ -3143,7 +3177,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="30">
+    <row r="43" spans="1:11" ht="30">
       <c r="A43" s="1">
         <v>45952</v>
       </c>
@@ -3172,7 +3206,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="30">
+    <row r="44" spans="1:11" ht="30">
       <c r="A44" s="1">
         <v>45952</v>
       </c>
@@ -3201,7 +3235,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="30">
+    <row r="45" spans="1:11" ht="30">
       <c r="A45" s="1">
         <v>45952</v>
       </c>
@@ -3230,7 +3264,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="30">
+    <row r="46" spans="1:11" ht="30">
       <c r="A46" s="1">
         <v>45952</v>
       </c>
@@ -3259,7 +3293,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="30">
+    <row r="47" spans="1:11" ht="30">
       <c r="A47" s="1">
         <v>45952</v>
       </c>
@@ -3288,7 +3322,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="30">
+    <row r="48" spans="1:11" ht="30">
       <c r="A48" s="1">
         <v>45952</v>
       </c>
@@ -3868,7 +3902,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
+    <row r="69" spans="1:9" ht="30">
       <c r="A69" s="1">
         <v>45958</v>
       </c>
@@ -3879,16 +3913,16 @@
         <v>10</v>
       </c>
       <c r="D69">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E69">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F69" t="s">
-        <v>80</v>
-      </c>
-      <c r="G69" t="s">
-        <v>77</v>
+        <v>322</v>
+      </c>
+      <c r="G69" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H69" t="s">
         <v>12</v>
@@ -3897,7 +3931,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
+    <row r="70" spans="1:9" ht="30">
       <c r="A70" s="1">
         <v>45958</v>
       </c>
@@ -3908,16 +3942,16 @@
         <v>10</v>
       </c>
       <c r="D70">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E70">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F70" t="s">
-        <v>11</v>
-      </c>
-      <c r="G70" t="s">
-        <v>77</v>
+        <v>324</v>
+      </c>
+      <c r="G70" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H70" t="s">
         <v>12</v>
@@ -3926,7 +3960,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
+    <row r="71" spans="1:9" ht="30">
       <c r="A71" s="1">
         <v>45958</v>
       </c>
@@ -3937,16 +3971,16 @@
         <v>10</v>
       </c>
       <c r="D71">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E71">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F71" t="s">
-        <v>74</v>
-      </c>
-      <c r="G71" t="s">
-        <v>77</v>
+        <v>325</v>
+      </c>
+      <c r="G71" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H71" t="s">
         <v>12</v>
@@ -3955,7 +3989,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
+    <row r="72" spans="1:9" ht="30">
       <c r="A72" s="1">
         <v>45958</v>
       </c>
@@ -3972,10 +4006,10 @@
         <v>51</v>
       </c>
       <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" t="s">
-        <v>78</v>
+        <v>324</v>
+      </c>
+      <c r="G72" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H72" t="s">
         <v>12</v>
@@ -3984,7 +4018,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
+    <row r="73" spans="1:9" ht="30">
       <c r="A73" s="1">
         <v>45958</v>
       </c>
@@ -3995,16 +4029,16 @@
         <v>10</v>
       </c>
       <c r="D73">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E73">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F73" t="s">
-        <v>75</v>
-      </c>
-      <c r="G73" t="s">
-        <v>77</v>
+        <v>327</v>
+      </c>
+      <c r="G73" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H73" t="s">
         <v>12</v>
@@ -4013,7 +4047,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
+    <row r="74" spans="1:9" ht="30">
       <c r="A74" s="1">
         <v>45958</v>
       </c>
@@ -4024,16 +4058,16 @@
         <v>10</v>
       </c>
       <c r="D74">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E74">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F74" t="s">
-        <v>322</v>
-      </c>
-      <c r="G74" t="s">
-        <v>323</v>
+        <v>328</v>
+      </c>
+      <c r="G74" s="14" t="s">
+        <v>329</v>
       </c>
       <c r="H74" t="s">
         <v>12</v>
@@ -4042,7 +4076,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
+    <row r="75" spans="1:9" ht="30">
       <c r="A75" s="1">
         <v>45958</v>
       </c>
@@ -4059,10 +4093,10 @@
         <v>58</v>
       </c>
       <c r="F75" t="s">
-        <v>74</v>
-      </c>
-      <c r="G75" t="s">
-        <v>78</v>
+        <v>325</v>
+      </c>
+      <c r="G75" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H75" t="s">
         <v>12</v>
@@ -4071,7 +4105,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" ht="30">
       <c r="A76" s="1">
         <v>45958</v>
       </c>
@@ -4088,10 +4122,10 @@
         <v>54</v>
       </c>
       <c r="F76" t="s">
-        <v>80</v>
-      </c>
-      <c r="G76" t="s">
-        <v>78</v>
+        <v>322</v>
+      </c>
+      <c r="G76" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H76" t="s">
         <v>12</v>
@@ -4100,7 +4134,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
+    <row r="77" spans="1:9" ht="30">
       <c r="A77" s="1">
         <v>45958</v>
       </c>
@@ -4111,16 +4145,16 @@
         <v>10</v>
       </c>
       <c r="D77">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E77">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F77" t="s">
-        <v>11</v>
-      </c>
-      <c r="G77" t="s">
-        <v>77</v>
+        <v>324</v>
+      </c>
+      <c r="G77" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H77" t="s">
         <v>12</v>
@@ -4129,7 +4163,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
+    <row r="78" spans="1:9" ht="30">
       <c r="A78" s="1">
         <v>45958</v>
       </c>
@@ -4140,16 +4174,16 @@
         <v>10</v>
       </c>
       <c r="D78">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E78">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F78" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" t="s">
-        <v>77</v>
+        <v>324</v>
+      </c>
+      <c r="G78" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H78" t="s">
         <v>12</v>
@@ -4158,7 +4192,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
+    <row r="79" spans="1:9" ht="30">
       <c r="A79" s="1">
         <v>45958</v>
       </c>
@@ -4175,10 +4209,10 @@
         <v>69</v>
       </c>
       <c r="F79" t="s">
-        <v>76</v>
-      </c>
-      <c r="G79" t="s">
-        <v>77</v>
+        <v>330</v>
+      </c>
+      <c r="G79" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H79" t="s">
         <v>12</v>
@@ -4187,7 +4221,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
+    <row r="80" spans="1:9" ht="30">
       <c r="A80" s="1">
         <v>45958</v>
       </c>
@@ -4204,10 +4238,10 @@
         <v>59</v>
       </c>
       <c r="F80" t="s">
-        <v>75</v>
-      </c>
-      <c r="G80" t="s">
-        <v>78</v>
+        <v>327</v>
+      </c>
+      <c r="G80" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H80" t="s">
         <v>12</v>
@@ -4216,7 +4250,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
+    <row r="81" spans="1:9" ht="30">
       <c r="A81" s="1">
         <v>45958</v>
       </c>
@@ -4233,10 +4267,10 @@
         <v>51</v>
       </c>
       <c r="F81" t="s">
-        <v>11</v>
-      </c>
-      <c r="G81" t="s">
-        <v>78</v>
+        <v>324</v>
+      </c>
+      <c r="G81" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H81" t="s">
         <v>12</v>
@@ -4245,7 +4279,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
+    <row r="82" spans="1:9" ht="30">
       <c r="A82" s="1">
         <v>45958</v>
       </c>
@@ -4256,16 +4290,16 @@
         <v>10</v>
       </c>
       <c r="D82">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="E82">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F82" t="s">
-        <v>76</v>
-      </c>
-      <c r="G82" t="s">
-        <v>77</v>
+        <v>330</v>
+      </c>
+      <c r="G82" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H82" t="s">
         <v>12</v>
@@ -4274,7 +4308,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
+    <row r="83" spans="1:9" ht="30">
       <c r="A83" s="1">
         <v>45958</v>
       </c>
@@ -4285,16 +4319,16 @@
         <v>10</v>
       </c>
       <c r="D83">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="E83">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F83" t="s">
-        <v>76</v>
-      </c>
-      <c r="G83" t="s">
-        <v>323</v>
+        <v>331</v>
+      </c>
+      <c r="G83" s="14" t="s">
+        <v>329</v>
       </c>
       <c r="H83" t="s">
         <v>12</v>
@@ -4303,7 +4337,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
+    <row r="84" spans="1:9" ht="30">
       <c r="A84" s="1">
         <v>45958</v>
       </c>
@@ -4320,10 +4354,10 @@
         <v>48</v>
       </c>
       <c r="F84" t="s">
-        <v>75</v>
-      </c>
-      <c r="G84" t="s">
-        <v>78</v>
+        <v>327</v>
+      </c>
+      <c r="G84" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H84" t="s">
         <v>12</v>
@@ -4332,7 +4366,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
+    <row r="85" spans="1:9" ht="30">
       <c r="A85" s="1">
         <v>45958</v>
       </c>
@@ -4349,10 +4383,10 @@
         <v>74</v>
       </c>
       <c r="F85" t="s">
-        <v>324</v>
-      </c>
-      <c r="G85" t="s">
-        <v>77</v>
+        <v>331</v>
+      </c>
+      <c r="G85" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H85" t="s">
         <v>12</v>
@@ -4361,7 +4395,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
+    <row r="86" spans="1:9" ht="30">
       <c r="A86" s="1">
         <v>45958</v>
       </c>
@@ -4378,10 +4412,10 @@
         <v>68</v>
       </c>
       <c r="F86" t="s">
-        <v>76</v>
-      </c>
-      <c r="G86" t="s">
-        <v>77</v>
+        <v>330</v>
+      </c>
+      <c r="G86" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H86" t="s">
         <v>12</v>
@@ -4390,7 +4424,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
+    <row r="87" spans="1:9" ht="30">
       <c r="A87" s="1">
         <v>45958</v>
       </c>
@@ -4407,10 +4441,10 @@
         <v>65</v>
       </c>
       <c r="F87" t="s">
-        <v>324</v>
-      </c>
-      <c r="G87" t="s">
-        <v>77</v>
+        <v>331</v>
+      </c>
+      <c r="G87" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H87" t="s">
         <v>12</v>
@@ -4419,7 +4453,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
+    <row r="88" spans="1:9" ht="30">
       <c r="A88" s="1">
         <v>45958</v>
       </c>
@@ -4436,10 +4470,10 @@
         <v>50</v>
       </c>
       <c r="F88" t="s">
-        <v>75</v>
-      </c>
-      <c r="G88" t="s">
-        <v>78</v>
+        <v>327</v>
+      </c>
+      <c r="G88" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H88" t="s">
         <v>12</v>
@@ -4448,7 +4482,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
+    <row r="89" spans="1:9" ht="30">
       <c r="A89" s="1">
         <v>45958</v>
       </c>
@@ -4465,10 +4499,10 @@
         <v>69</v>
       </c>
       <c r="F89" t="s">
-        <v>80</v>
-      </c>
-      <c r="G89" t="s">
-        <v>77</v>
+        <v>322</v>
+      </c>
+      <c r="G89" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H89" t="s">
         <v>12</v>
@@ -4477,7 +4511,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
+    <row r="90" spans="1:9" ht="30">
       <c r="A90" s="1">
         <v>45958</v>
       </c>
@@ -4494,10 +4528,10 @@
         <v>35</v>
       </c>
       <c r="F90" t="s">
-        <v>75</v>
-      </c>
-      <c r="G90" t="s">
-        <v>79</v>
+        <v>327</v>
+      </c>
+      <c r="G90" s="14" t="s">
+        <v>332</v>
       </c>
       <c r="H90" t="s">
         <v>12</v>
@@ -4506,7 +4540,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
+    <row r="91" spans="1:9" ht="30">
       <c r="A91" s="1">
         <v>45958</v>
       </c>
@@ -4523,10 +4557,10 @@
         <v>59</v>
       </c>
       <c r="F91" t="s">
-        <v>80</v>
-      </c>
-      <c r="G91" t="s">
-        <v>78</v>
+        <v>322</v>
+      </c>
+      <c r="G91" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H91" t="s">
         <v>12</v>
@@ -4535,7 +4569,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
+    <row r="92" spans="1:9" ht="30">
       <c r="A92" s="1">
         <v>45958</v>
       </c>
@@ -4552,10 +4586,10 @@
         <v>48</v>
       </c>
       <c r="F92" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92" t="s">
-        <v>78</v>
+        <v>324</v>
+      </c>
+      <c r="G92" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H92" t="s">
         <v>12</v>
@@ -4564,7 +4598,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
+    <row r="93" spans="1:9" ht="30">
       <c r="A93" s="1">
         <v>45958</v>
       </c>
@@ -4581,10 +4615,10 @@
         <v>59</v>
       </c>
       <c r="F93" t="s">
-        <v>74</v>
-      </c>
-      <c r="G93" t="s">
-        <v>78</v>
+        <v>325</v>
+      </c>
+      <c r="G93" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H93" t="s">
         <v>12</v>
@@ -4593,7 +4627,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
+    <row r="94" spans="1:9" ht="30">
       <c r="A94" s="1">
         <v>45958</v>
       </c>
@@ -4610,10 +4644,10 @@
         <v>59</v>
       </c>
       <c r="F94" t="s">
-        <v>74</v>
-      </c>
-      <c r="G94" t="s">
-        <v>78</v>
+        <v>325</v>
+      </c>
+      <c r="G94" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H94" t="s">
         <v>12</v>
@@ -4622,7 +4656,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
+    <row r="95" spans="1:9" ht="30">
       <c r="A95" s="1">
         <v>45958</v>
       </c>
@@ -4639,10 +4673,10 @@
         <v>53</v>
       </c>
       <c r="F95" t="s">
-        <v>74</v>
-      </c>
-      <c r="G95" t="s">
-        <v>78</v>
+        <v>325</v>
+      </c>
+      <c r="G95" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H95" t="s">
         <v>12</v>
@@ -4651,7 +4685,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
+    <row r="96" spans="1:9" ht="30">
       <c r="A96" s="1">
         <v>45958</v>
       </c>
@@ -4668,10 +4702,10 @@
         <v>68</v>
       </c>
       <c r="F96" t="s">
-        <v>322</v>
-      </c>
-      <c r="G96" t="s">
-        <v>77</v>
+        <v>328</v>
+      </c>
+      <c r="G96" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H96" t="s">
         <v>12</v>
@@ -4680,7 +4714,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
+    <row r="97" spans="1:9" ht="30">
       <c r="A97" s="1">
         <v>45958</v>
       </c>
@@ -4697,10 +4731,10 @@
         <v>50</v>
       </c>
       <c r="F97" t="s">
-        <v>74</v>
-      </c>
-      <c r="G97" t="s">
-        <v>78</v>
+        <v>325</v>
+      </c>
+      <c r="G97" s="14" t="s">
+        <v>326</v>
       </c>
       <c r="H97" t="s">
         <v>12</v>
@@ -4709,7 +4743,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
+    <row r="98" spans="1:9" ht="30">
       <c r="A98" s="1">
         <v>45958</v>
       </c>
@@ -4726,10 +4760,10 @@
         <v>68</v>
       </c>
       <c r="F98" t="s">
-        <v>74</v>
-      </c>
-      <c r="G98" t="s">
-        <v>77</v>
+        <v>325</v>
+      </c>
+      <c r="G98" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H98" t="s">
         <v>12</v>
@@ -4738,7 +4772,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
+    <row r="99" spans="1:9" ht="30">
       <c r="A99" s="1">
         <v>45958</v>
       </c>
@@ -4749,16 +4783,16 @@
         <v>14</v>
       </c>
       <c r="D99">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E99">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F99" t="s">
-        <v>322</v>
-      </c>
-      <c r="G99" t="s">
-        <v>323</v>
+        <v>328</v>
+      </c>
+      <c r="G99" s="14" t="s">
+        <v>329</v>
       </c>
       <c r="H99" t="s">
         <v>12</v>
@@ -4767,7 +4801,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
+    <row r="100" spans="1:9" ht="30">
       <c r="A100" s="1">
         <v>45958</v>
       </c>
@@ -4784,10 +4818,10 @@
         <v>61</v>
       </c>
       <c r="F100" t="s">
-        <v>76</v>
-      </c>
-      <c r="G100" t="s">
-        <v>77</v>
+        <v>330</v>
+      </c>
+      <c r="G100" s="14" t="s">
+        <v>323</v>
       </c>
       <c r="H100" t="s">
         <v>12</v>
@@ -5152,7 +5186,7 @@
         <v>33</v>
       </c>
       <c r="B3" s="1">
-        <v>45952.486111111109</v>
+        <v>45952</v>
       </c>
       <c r="C3" s="14" t="s">
         <v>259</v>
@@ -6319,10 +6353,10 @@
       <c r="D2" t="s">
         <v>14</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="24">
         <v>-2</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="24">
         <v>0</v>
       </c>
       <c r="G2" s="14" t="s">
@@ -6346,10 +6380,10 @@
       <c r="D3" t="s">
         <v>14</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
+      <c r="E3" s="24">
+        <v>0</v>
+      </c>
+      <c r="F3" s="24">
         <v>0</v>
       </c>
       <c r="G3" s="14" t="s">
@@ -6373,10 +6407,10 @@
       <c r="D4" t="s">
         <v>14</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="24">
         <v>-4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="24">
         <v>1</v>
       </c>
       <c r="G4" s="14" t="s">
@@ -6400,10 +6434,10 @@
       <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="24">
         <v>-2</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="24">
         <v>0</v>
       </c>
       <c r="G5" s="14" t="s">
@@ -6427,10 +6461,10 @@
       <c r="D6" t="s">
         <v>14</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="24">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="24">
         <v>2</v>
       </c>
       <c r="G6" s="14" t="s">
@@ -6454,10 +6488,10 @@
       <c r="D7" t="s">
         <v>14</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="24">
         <v>-8</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="24">
         <v>-7</v>
       </c>
       <c r="G7" s="14" t="s">
@@ -6481,10 +6515,10 @@
       <c r="D8" t="s">
         <v>14</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="24">
         <v>-4</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="24">
         <v>3</v>
       </c>
       <c r="G8" s="14" t="s">
@@ -6508,10 +6542,10 @@
       <c r="D9" t="s">
         <v>14</v>
       </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
+      <c r="E9" s="24">
+        <v>0</v>
+      </c>
+      <c r="F9" s="24">
         <v>0</v>
       </c>
       <c r="G9" s="14" t="s">
@@ -6535,10 +6569,10 @@
       <c r="D10" t="s">
         <v>14</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="24">
         <v>-3</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="24">
         <v>2</v>
       </c>
       <c r="G10" s="14" t="s">
@@ -6562,10 +6596,10 @@
       <c r="D11" t="s">
         <v>14</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="24">
         <v>-3</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="24">
         <v>2</v>
       </c>
       <c r="G11" s="14" t="s">
@@ -6589,10 +6623,10 @@
       <c r="D12" t="s">
         <v>14</v>
       </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+      <c r="E12" s="24">
+        <v>0</v>
+      </c>
+      <c r="F12" s="24">
         <v>3</v>
       </c>
       <c r="G12" s="14" t="s">
@@ -6616,10 +6650,10 @@
       <c r="D13" t="s">
         <v>14</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="24">
         <v>8</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="24">
         <v>7</v>
       </c>
       <c r="G13" s="14" t="s">
@@ -6643,10 +6677,10 @@
       <c r="D14" t="s">
         <v>14</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="24">
         <v>3</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="24">
         <v>2</v>
       </c>
       <c r="G14" s="14" t="s">
@@ -6670,10 +6704,10 @@
       <c r="D15" t="s">
         <v>14</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="24">
         <v>-2</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="24">
         <v>3</v>
       </c>
       <c r="G15" s="14" t="s">
@@ -6697,10 +6731,10 @@
       <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="24">
         <v>3</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="24">
         <v>3</v>
       </c>
       <c r="G16" s="14" t="s">
@@ -6724,10 +6758,10 @@
       <c r="D17" t="s">
         <v>14</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="24">
         <v>7</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="24">
         <v>6</v>
       </c>
       <c r="G17" s="14" t="s">
@@ -6751,10 +6785,10 @@
       <c r="D18" t="s">
         <v>10</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="24">
         <v>1</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="24">
         <v>2</v>
       </c>
       <c r="G18" s="14" t="s">
@@ -6778,10 +6812,10 @@
       <c r="D19" t="s">
         <v>10</v>
       </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-      <c r="F19">
+      <c r="E19" s="24">
+        <v>0</v>
+      </c>
+      <c r="F19" s="24">
         <v>0</v>
       </c>
       <c r="G19" s="14" t="s">
@@ -6805,10 +6839,10 @@
       <c r="D20" t="s">
         <v>10</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="24">
         <v>5</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="24">
         <v>4</v>
       </c>
       <c r="G20" s="14" t="s">
@@ -6832,10 +6866,10 @@
       <c r="D21" t="s">
         <v>10</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
+      <c r="E21" s="24">
+        <v>0</v>
+      </c>
+      <c r="F21" s="24">
         <v>1</v>
       </c>
       <c r="G21" s="14" t="s">
@@ -6859,10 +6893,10 @@
       <c r="D22" t="s">
         <v>10</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="24">
         <v>-3</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="24">
         <v>1</v>
       </c>
       <c r="G22" s="14" t="s">
@@ -6886,10 +6920,10 @@
       <c r="D23" t="s">
         <v>10</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="24">
         <v>9</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="24">
         <v>9</v>
       </c>
       <c r="G23" s="18" t="s">
@@ -6913,10 +6947,10 @@
       <c r="D24" t="s">
         <v>10</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="24">
         <v>3</v>
       </c>
-      <c r="F24">
+      <c r="F24" s="24">
         <v>0</v>
       </c>
       <c r="G24" s="14" t="s">
@@ -6940,10 +6974,10 @@
       <c r="D25" t="s">
         <v>10</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25">
+      <c r="E25" s="24">
+        <v>0</v>
+      </c>
+      <c r="F25" s="24">
         <v>0</v>
       </c>
       <c r="G25" s="14" t="s">
@@ -6967,10 +7001,10 @@
       <c r="D26" t="s">
         <v>10</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="24">
         <v>1</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="24">
         <v>1</v>
       </c>
       <c r="G26" s="14" t="s">
@@ -6994,10 +7028,10 @@
       <c r="D27" t="s">
         <v>10</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="24">
         <v>1</v>
       </c>
-      <c r="F27">
+      <c r="F27" s="24">
         <v>1</v>
       </c>
       <c r="G27" s="14" t="s">
@@ -7021,10 +7055,10 @@
       <c r="D28" t="s">
         <v>10</v>
       </c>
-      <c r="E28">
+      <c r="E28" s="24">
         <v>3</v>
       </c>
-      <c r="F28">
+      <c r="F28" s="24">
         <v>2</v>
       </c>
       <c r="G28" s="14" t="s">
@@ -7048,10 +7082,10 @@
       <c r="D29" t="s">
         <v>10</v>
       </c>
-      <c r="E29">
+      <c r="E29" s="24">
         <v>-4</v>
       </c>
-      <c r="F29">
+      <c r="F29" s="24">
         <v>0</v>
       </c>
       <c r="G29" s="14" t="s">
@@ -7075,10 +7109,10 @@
       <c r="D30" t="s">
         <v>10</v>
       </c>
-      <c r="E30">
+      <c r="E30" s="24">
         <v>3</v>
       </c>
-      <c r="F30">
+      <c r="F30" s="24">
         <v>2</v>
       </c>
       <c r="G30" s="14" t="s">
@@ -7102,10 +7136,10 @@
       <c r="D31" t="s">
         <v>10</v>
       </c>
-      <c r="E31">
+      <c r="E31" s="24">
         <v>1</v>
       </c>
-      <c r="F31">
+      <c r="F31" s="24">
         <v>1</v>
       </c>
       <c r="G31" s="18" t="s">
@@ -7129,10 +7163,10 @@
       <c r="D32" t="s">
         <v>10</v>
       </c>
-      <c r="E32">
+      <c r="E32" s="24">
         <v>5</v>
       </c>
-      <c r="F32">
+      <c r="F32" s="24">
         <v>4</v>
       </c>
       <c r="G32" s="14" t="s">
@@ -7156,10 +7190,10 @@
       <c r="D33" t="s">
         <v>10</v>
       </c>
-      <c r="E33">
+      <c r="E33" s="24">
         <v>-2</v>
       </c>
-      <c r="F33">
+      <c r="F33" s="24">
         <v>1</v>
       </c>
       <c r="G33" s="14" t="s">
@@ -7183,14 +7217,17 @@
       <c r="D34" t="s">
         <v>10</v>
       </c>
-      <c r="E34">
+      <c r="E34" s="24">
         <v>4</v>
       </c>
-      <c r="F34">
+      <c r="F34" s="24">
         <v>3</v>
       </c>
       <c r="G34" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="30">
@@ -7207,14 +7244,17 @@
       <c r="D35" t="s">
         <v>10</v>
       </c>
-      <c r="E35">
+      <c r="E35" s="24">
         <v>3</v>
       </c>
-      <c r="F35">
+      <c r="F35" s="24">
         <v>2</v>
       </c>
       <c r="G35" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H35">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="30">
@@ -7231,14 +7271,17 @@
       <c r="D36" t="s">
         <v>10</v>
       </c>
-      <c r="E36">
+      <c r="E36" s="24">
         <v>-6</v>
       </c>
-      <c r="F36">
+      <c r="F36" s="24">
         <v>5</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H36">
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="30">
@@ -7255,14 +7298,17 @@
       <c r="D37" t="s">
         <v>10</v>
       </c>
-      <c r="E37">
+      <c r="E37" s="24">
         <v>3</v>
       </c>
-      <c r="F37">
+      <c r="F37" s="24">
         <v>3</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:8" ht="30">
@@ -7279,14 +7325,17 @@
       <c r="D38" t="s">
         <v>10</v>
       </c>
-      <c r="E38">
+      <c r="E38" s="24">
         <v>3</v>
       </c>
-      <c r="F38">
+      <c r="F38" s="24">
         <v>3</v>
       </c>
       <c r="G38" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H38">
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:8" ht="30">
@@ -7303,14 +7352,17 @@
       <c r="D39" t="s">
         <v>10</v>
       </c>
-      <c r="E39">
+      <c r="E39" s="24">
         <v>3</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="24">
         <v>3</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="30">
@@ -7327,14 +7379,17 @@
       <c r="D40" t="s">
         <v>10</v>
       </c>
-      <c r="E40">
+      <c r="E40" s="24">
         <v>3</v>
       </c>
-      <c r="F40">
+      <c r="F40" s="24">
         <v>3</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H40">
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:8" ht="30">
@@ -7351,14 +7406,17 @@
       <c r="D41" t="s">
         <v>10</v>
       </c>
-      <c r="E41">
+      <c r="E41" s="24">
         <v>1</v>
       </c>
-      <c r="F41">
+      <c r="F41" s="24">
         <v>2</v>
       </c>
       <c r="G41" s="14" t="s">
         <v>292</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:8" ht="30">
@@ -7375,14 +7433,17 @@
       <c r="D42" t="s">
         <v>10</v>
       </c>
-      <c r="E42">
+      <c r="E42" s="24">
         <v>-7</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="24">
         <v>3</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>299</v>
+      </c>
+      <c r="H42">
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:8" ht="30">
@@ -7399,14 +7460,17 @@
       <c r="D43" t="s">
         <v>14</v>
       </c>
-      <c r="E43">
+      <c r="E43" s="24">
         <v>8</v>
       </c>
-      <c r="F43">
+      <c r="F43" s="24">
         <v>4</v>
       </c>
       <c r="G43" s="14" t="s">
         <v>299</v>
+      </c>
+      <c r="H43">
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:8" ht="30">
@@ -7423,14 +7487,17 @@
       <c r="D44" t="s">
         <v>10</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <v>6</v>
       </c>
-      <c r="F44" s="23">
+      <c r="F44" s="24">
         <v>5</v>
       </c>
       <c r="G44" s="14" t="s">
         <v>299</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="30">
@@ -7447,14 +7514,17 @@
       <c r="D45" t="s">
         <v>14</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="24">
         <v>2</v>
       </c>
-      <c r="F45" s="23">
+      <c r="F45" s="24">
         <v>1</v>
       </c>
       <c r="G45" s="14" t="s">
         <v>299</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="30">
@@ -7471,14 +7541,17 @@
       <c r="D46" t="s">
         <v>10</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="24">
         <v>3</v>
       </c>
-      <c r="F46" s="23">
+      <c r="F46" s="24">
         <v>4</v>
       </c>
       <c r="G46" s="14" t="s">
         <v>299</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="30">
@@ -7495,14 +7568,17 @@
       <c r="D47" t="s">
         <v>14</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <v>4</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="24">
         <v>2</v>
       </c>
       <c r="G47" s="14" t="s">
         <v>299</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="30">
@@ -7519,17 +7595,20 @@
       <c r="D48" t="s">
         <v>10</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="24">
         <v>5</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="24">
         <v>5</v>
       </c>
       <c r="G48" s="14" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="30">
+      <c r="H48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="30">
       <c r="A49" t="s">
         <v>82</v>
       </c>
@@ -7543,17 +7622,20 @@
       <c r="D49" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="24">
         <v>-7</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="24">
         <v>-2</v>
       </c>
       <c r="G49" s="14" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="30">
+      <c r="H49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="30">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -7567,17 +7649,20 @@
       <c r="D50" t="s">
         <v>10</v>
       </c>
-      <c r="E50" s="23">
+      <c r="E50" s="24">
         <v>5</v>
       </c>
-      <c r="F50" s="23">
+      <c r="F50" s="24">
         <v>4</v>
       </c>
       <c r="G50" s="14" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="30">
+      <c r="H50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="30">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -7591,17 +7676,20 @@
       <c r="D51" t="s">
         <v>14</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="24">
         <v>-4</v>
       </c>
-      <c r="F51" s="23">
+      <c r="F51" s="24">
         <v>0</v>
       </c>
       <c r="G51" s="14" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="30">
+      <c r="H51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="30">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -7615,17 +7703,20 @@
       <c r="D52" t="s">
         <v>10</v>
       </c>
-      <c r="E52" s="23">
+      <c r="E52" s="24">
         <v>-6</v>
       </c>
-      <c r="F52" s="23">
+      <c r="F52" s="24">
         <v>6</v>
       </c>
       <c r="G52" s="14" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="30">
+      <c r="H52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="30">
       <c r="A53" t="s">
         <v>82</v>
       </c>
@@ -7639,17 +7730,20 @@
       <c r="D53" t="s">
         <v>14</v>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="24">
         <v>2</v>
       </c>
-      <c r="F53" s="23">
+      <c r="F53" s="24">
         <v>0</v>
       </c>
       <c r="G53" s="14" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="30">
+      <c r="H53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="30">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -7663,17 +7757,20 @@
       <c r="D54" t="s">
         <v>10</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="24">
         <v>3</v>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="24">
         <v>3</v>
       </c>
       <c r="G54" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="30">
+      <c r="H54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="30">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -7687,17 +7784,20 @@
       <c r="D55" t="s">
         <v>10</v>
       </c>
-      <c r="E55" s="23">
+      <c r="E55" s="24">
         <v>5</v>
       </c>
-      <c r="F55" s="23">
+      <c r="F55" s="24">
         <v>3</v>
       </c>
       <c r="G55" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="30">
+      <c r="H55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="30">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -7711,17 +7811,20 @@
       <c r="D56" t="s">
         <v>10</v>
       </c>
-      <c r="E56" s="23">
+      <c r="E56" s="24">
         <v>3</v>
       </c>
-      <c r="F56" s="23">
+      <c r="F56" s="24">
         <v>2</v>
       </c>
       <c r="G56" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="30">
+      <c r="H56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="30">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -7735,17 +7838,20 @@
       <c r="D57" t="s">
         <v>10</v>
       </c>
-      <c r="E57" s="23">
+      <c r="E57" s="24">
         <v>3</v>
       </c>
-      <c r="F57" s="23">
+      <c r="F57" s="24">
         <v>2</v>
       </c>
       <c r="G57" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="30">
+      <c r="H57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="30">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -7759,17 +7865,20 @@
       <c r="D58" t="s">
         <v>10</v>
       </c>
-      <c r="E58" s="23">
+      <c r="E58" s="24">
         <v>5</v>
       </c>
-      <c r="F58" s="23">
+      <c r="F58" s="24">
         <v>3</v>
       </c>
       <c r="G58" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="30">
+      <c r="H58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="30">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -7783,17 +7892,20 @@
       <c r="D59" t="s">
         <v>10</v>
       </c>
-      <c r="E59" s="23">
+      <c r="E59" s="24">
         <v>-6</v>
       </c>
-      <c r="F59" s="23">
+      <c r="F59" s="24">
         <v>0</v>
       </c>
       <c r="G59" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="30">
+      <c r="H59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="30">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -7807,17 +7919,20 @@
       <c r="D60" t="s">
         <v>10</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="24">
         <v>4</v>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="24">
         <v>4</v>
       </c>
       <c r="G60" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="30">
+      <c r="H60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="30">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -7831,17 +7946,20 @@
       <c r="D61" t="s">
         <v>10</v>
       </c>
-      <c r="E61" s="23">
-        <v>0</v>
-      </c>
-      <c r="F61" s="23">
+      <c r="E61" s="24">
+        <v>0</v>
+      </c>
+      <c r="F61" s="24">
         <v>0</v>
       </c>
       <c r="G61" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="30">
+      <c r="H61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="30">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -7855,17 +7973,20 @@
       <c r="D62" t="s">
         <v>14</v>
       </c>
-      <c r="E62" s="23">
+      <c r="E62" s="24">
         <v>4</v>
       </c>
-      <c r="F62" s="23">
+      <c r="F62" s="24">
         <v>1</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="30">
+      <c r="H62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="30">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -7879,17 +8000,20 @@
       <c r="D63" t="s">
         <v>14</v>
       </c>
-      <c r="E63" s="23">
+      <c r="E63" s="24">
         <v>6</v>
       </c>
-      <c r="F63" s="23">
+      <c r="F63" s="24">
         <v>2</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="30">
+      <c r="H63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="30">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -7903,17 +8027,20 @@
       <c r="D64" t="s">
         <v>14</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="24">
         <v>-2</v>
       </c>
-      <c r="F64" s="23">
+      <c r="F64" s="24">
         <v>-2</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="30">
+      <c r="H64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="30">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -7927,17 +8054,20 @@
       <c r="D65" t="s">
         <v>14</v>
       </c>
-      <c r="E65" s="23">
+      <c r="E65" s="24">
         <v>-2</v>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="24">
         <v>-2</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="30">
+      <c r="H65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="30">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -7951,17 +8081,20 @@
       <c r="D66" t="s">
         <v>14</v>
       </c>
-      <c r="E66" s="23">
+      <c r="E66" s="24">
         <v>-6</v>
       </c>
-      <c r="F66" s="23">
+      <c r="F66" s="24">
         <v>-2</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="30">
+      <c r="H66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="30">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -7975,17 +8108,20 @@
       <c r="D67" t="s">
         <v>14</v>
       </c>
-      <c r="E67" s="23">
+      <c r="E67" s="24">
         <v>8</v>
       </c>
-      <c r="F67" s="23">
+      <c r="F67" s="24">
         <v>3</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="30">
+      <c r="H67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="30">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -7999,17 +8135,20 @@
       <c r="D68" t="s">
         <v>14</v>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="24">
         <v>-5</v>
       </c>
-      <c r="F68" s="23">
+      <c r="F68" s="24">
         <v>-2</v>
       </c>
       <c r="G68" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="30">
+      <c r="H68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="30">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -8023,17 +8162,20 @@
       <c r="D69" t="s">
         <v>14</v>
       </c>
-      <c r="E69" s="23">
+      <c r="E69" s="24">
         <v>2</v>
       </c>
-      <c r="F69" s="23">
+      <c r="F69" s="24">
         <v>2</v>
       </c>
       <c r="G69" s="14" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="30">
+      <c r="H69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="30">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -8047,17 +8189,20 @@
       <c r="D70" t="s">
         <v>10</v>
       </c>
-      <c r="E70" s="23">
+      <c r="E70" s="24">
         <v>-10</v>
       </c>
-      <c r="F70" s="23">
+      <c r="F70" s="24">
         <v>6</v>
       </c>
       <c r="G70" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="30">
+      <c r="H70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="30">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -8071,17 +8216,20 @@
       <c r="D71" t="s">
         <v>10</v>
       </c>
-      <c r="E71" s="23">
+      <c r="E71" s="24">
         <v>-2</v>
       </c>
-      <c r="F71" s="23">
+      <c r="F71" s="24">
         <v>4</v>
       </c>
       <c r="G71" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="30">
+      <c r="H71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="30">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -8095,17 +8243,20 @@
       <c r="D72" t="s">
         <v>10</v>
       </c>
-      <c r="E72" s="23">
+      <c r="E72" s="24">
         <v>-2</v>
       </c>
-      <c r="F72" s="23">
+      <c r="F72" s="24">
         <v>4</v>
       </c>
       <c r="G72" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="30">
+      <c r="H72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="30">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -8119,17 +8270,20 @@
       <c r="D73" t="s">
         <v>10</v>
       </c>
-      <c r="E73" s="23">
+      <c r="E73" s="24">
         <v>-2</v>
       </c>
-      <c r="F73" s="23">
+      <c r="F73" s="24">
         <v>4</v>
       </c>
       <c r="G73" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="30">
+      <c r="H73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="30">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -8143,17 +8297,20 @@
       <c r="D74" t="s">
         <v>10</v>
       </c>
-      <c r="E74" s="23">
+      <c r="E74" s="24">
         <v>-2</v>
       </c>
-      <c r="F74" s="23">
+      <c r="F74" s="24">
         <v>4</v>
       </c>
       <c r="G74" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="30">
+      <c r="H74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="30">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -8167,17 +8324,20 @@
       <c r="D75" t="s">
         <v>10</v>
       </c>
-      <c r="E75" s="23">
+      <c r="E75" s="24">
         <v>8</v>
       </c>
-      <c r="F75" s="23">
+      <c r="F75" s="24">
         <v>7</v>
       </c>
       <c r="G75" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="30">
+      <c r="H75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="30">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -8191,17 +8351,20 @@
       <c r="D76" t="s">
         <v>10</v>
       </c>
-      <c r="E76" s="23">
+      <c r="E76" s="24">
         <v>7</v>
       </c>
-      <c r="F76" s="23">
+      <c r="F76" s="24">
         <v>8</v>
       </c>
       <c r="G76" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" ht="30">
+      <c r="H76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="30">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -8215,17 +8378,20 @@
       <c r="D77" t="s">
         <v>10</v>
       </c>
-      <c r="E77" s="23">
+      <c r="E77" s="24">
         <v>-8</v>
       </c>
-      <c r="F77" s="23">
+      <c r="F77" s="24">
         <v>5</v>
       </c>
       <c r="G77" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="30">
+      <c r="H77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="30">
       <c r="A78" t="s">
         <v>84</v>
       </c>
@@ -8239,17 +8405,20 @@
       <c r="D78" t="s">
         <v>10</v>
       </c>
-      <c r="E78" s="23">
+      <c r="E78" s="24">
         <v>-10</v>
       </c>
-      <c r="F78" s="23">
+      <c r="F78" s="24">
         <v>2</v>
       </c>
       <c r="G78" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="30">
+      <c r="H78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="30">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -8263,17 +8432,20 @@
       <c r="D79" t="s">
         <v>14</v>
       </c>
-      <c r="E79" s="23">
+      <c r="E79" s="24">
         <v>8</v>
       </c>
-      <c r="F79" s="23">
+      <c r="F79" s="24">
         <v>4</v>
       </c>
       <c r="G79" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" ht="30">
+      <c r="H79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="30">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -8287,17 +8459,20 @@
       <c r="D80" t="s">
         <v>14</v>
       </c>
-      <c r="E80" s="23">
+      <c r="E80" s="24">
         <v>-2</v>
       </c>
-      <c r="F80" s="23">
+      <c r="F80" s="24">
         <v>4</v>
       </c>
       <c r="G80" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" ht="30">
+      <c r="H80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="30">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -8311,17 +8486,20 @@
       <c r="D81" t="s">
         <v>14</v>
       </c>
-      <c r="E81" s="23">
+      <c r="E81" s="24">
         <v>-2</v>
       </c>
-      <c r="F81" s="23">
+      <c r="F81" s="24">
         <v>4</v>
       </c>
       <c r="G81" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="30">
+      <c r="H81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="30">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -8335,17 +8513,20 @@
       <c r="D82" t="s">
         <v>14</v>
       </c>
-      <c r="E82" s="23">
+      <c r="E82" s="24">
         <v>-2</v>
       </c>
-      <c r="F82" s="23">
+      <c r="F82" s="24">
         <v>4</v>
       </c>
       <c r="G82" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="30">
+      <c r="H82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="30">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -8359,17 +8540,20 @@
       <c r="D83" t="s">
         <v>14</v>
       </c>
-      <c r="E83" s="23">
+      <c r="E83" s="24">
         <v>-2</v>
       </c>
-      <c r="F83" s="23">
+      <c r="F83" s="24">
         <v>4</v>
       </c>
       <c r="G83" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="30">
+      <c r="H83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="30">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -8383,17 +8567,20 @@
       <c r="D84" t="s">
         <v>14</v>
       </c>
-      <c r="E84" s="23">
+      <c r="E84" s="24">
         <v>-9</v>
       </c>
-      <c r="F84" s="23">
+      <c r="F84" s="24">
         <v>4</v>
       </c>
       <c r="G84" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="30">
+      <c r="H84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="30">
       <c r="A85" t="s">
         <v>84</v>
       </c>
@@ -8407,17 +8594,20 @@
       <c r="D85" t="s">
         <v>14</v>
       </c>
-      <c r="E85" s="23">
+      <c r="E85" s="24">
         <v>-10</v>
       </c>
-      <c r="F85" s="23">
+      <c r="F85" s="24">
         <v>2</v>
       </c>
       <c r="G85" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="30">
+      <c r="H85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="30">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -8431,17 +8621,20 @@
       <c r="D86" t="s">
         <v>14</v>
       </c>
-      <c r="E86" s="23">
+      <c r="E86" s="24">
         <v>-8</v>
       </c>
-      <c r="F86" s="23">
+      <c r="F86" s="24">
         <v>5</v>
       </c>
       <c r="G86" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="30">
+      <c r="H86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="30">
       <c r="A87" t="s">
         <v>84</v>
       </c>
@@ -8455,17 +8648,20 @@
       <c r="D87" t="s">
         <v>14</v>
       </c>
-      <c r="E87" s="23">
+      <c r="E87" s="24">
         <v>7</v>
       </c>
-      <c r="F87" s="23">
+      <c r="F87" s="24">
         <v>8</v>
       </c>
       <c r="G87" s="14" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="30">
+      <c r="H87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="30">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -8479,17 +8675,20 @@
       <c r="D88" t="s">
         <v>10</v>
       </c>
-      <c r="E88" s="23">
+      <c r="E88" s="24">
         <v>6</v>
       </c>
-      <c r="F88" s="23">
+      <c r="F88" s="24">
         <v>9</v>
       </c>
       <c r="G88" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="30">
+      <c r="H88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="30">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -8503,17 +8702,20 @@
       <c r="D89" t="s">
         <v>10</v>
       </c>
-      <c r="E89" s="23">
+      <c r="E89" s="24">
         <v>-10</v>
       </c>
-      <c r="F89" s="23">
+      <c r="F89" s="24">
         <v>8</v>
       </c>
       <c r="G89" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="30">
+      <c r="H89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="30">
       <c r="A90" t="s">
         <v>85</v>
       </c>
@@ -8527,17 +8729,20 @@
       <c r="D90" t="s">
         <v>10</v>
       </c>
-      <c r="E90" s="23">
+      <c r="E90" s="24">
         <v>-8</v>
       </c>
-      <c r="F90" s="23">
+      <c r="F90" s="24">
         <v>8</v>
       </c>
       <c r="G90" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="30">
+      <c r="H90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="30">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -8551,17 +8756,20 @@
       <c r="D91" t="s">
         <v>10</v>
       </c>
-      <c r="E91" s="23">
+      <c r="E91" s="24">
         <v>-4</v>
       </c>
-      <c r="F91" s="23">
+      <c r="F91" s="24">
         <v>5</v>
       </c>
       <c r="G91" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="30">
+      <c r="H91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="30">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -8575,17 +8783,20 @@
       <c r="D92" t="s">
         <v>10</v>
       </c>
-      <c r="E92" s="23">
+      <c r="E92" s="24">
         <v>-7</v>
       </c>
-      <c r="F92" s="23">
+      <c r="F92" s="24">
         <v>8</v>
       </c>
       <c r="G92" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="30">
+      <c r="H92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="30">
       <c r="A93" t="s">
         <v>85</v>
       </c>
@@ -8599,17 +8810,20 @@
       <c r="D93" t="s">
         <v>14</v>
       </c>
-      <c r="E93" s="23">
-        <v>0</v>
-      </c>
-      <c r="F93" s="23">
+      <c r="E93" s="24">
+        <v>0</v>
+      </c>
+      <c r="F93" s="24">
         <v>0</v>
       </c>
       <c r="G93" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="30">
+      <c r="H93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="30">
       <c r="A94" t="s">
         <v>85</v>
       </c>
@@ -8623,17 +8837,20 @@
       <c r="D94" t="s">
         <v>14</v>
       </c>
-      <c r="E94" s="23">
+      <c r="E94" s="24">
         <v>-5</v>
       </c>
-      <c r="F94" s="23">
+      <c r="F94" s="24">
         <v>6</v>
       </c>
       <c r="G94" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="30">
+      <c r="H94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="30">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -8647,17 +8864,20 @@
       <c r="D95" t="s">
         <v>14</v>
       </c>
-      <c r="E95" s="23">
-        <v>0</v>
-      </c>
-      <c r="F95" s="23">
+      <c r="E95" s="24">
+        <v>0</v>
+      </c>
+      <c r="F95" s="24">
         <v>-4</v>
       </c>
       <c r="G95" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="30">
+      <c r="H95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="30">
       <c r="A96" t="s">
         <v>85</v>
       </c>
@@ -8671,17 +8891,20 @@
       <c r="D96" t="s">
         <v>14</v>
       </c>
-      <c r="E96" s="23">
+      <c r="E96" s="24">
         <v>-2</v>
       </c>
-      <c r="F96" s="23">
+      <c r="F96" s="24">
         <v>-4</v>
       </c>
       <c r="G96" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="30">
+      <c r="H96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="30">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -8695,17 +8918,20 @@
       <c r="D97" t="s">
         <v>14</v>
       </c>
-      <c r="E97" s="23">
-        <v>0</v>
-      </c>
-      <c r="F97" s="23">
+      <c r="E97" s="24">
+        <v>0</v>
+      </c>
+      <c r="F97" s="24">
         <v>-3</v>
       </c>
       <c r="G97" s="14" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" ht="30">
+      <c r="H97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="30">
       <c r="A98" t="s">
         <v>90</v>
       </c>
@@ -8719,17 +8945,20 @@
       <c r="D98" t="s">
         <v>10</v>
       </c>
-      <c r="E98" s="23">
+      <c r="E98" s="24">
         <v>-7</v>
       </c>
-      <c r="F98" s="23">
+      <c r="F98" s="24">
         <v>2</v>
       </c>
       <c r="G98" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="30">
+      <c r="H98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="30">
       <c r="A99" t="s">
         <v>90</v>
       </c>
@@ -8743,17 +8972,20 @@
       <c r="D99" t="s">
         <v>10</v>
       </c>
-      <c r="E99" s="23">
+      <c r="E99" s="24">
         <v>-6</v>
       </c>
-      <c r="F99" s="23">
+      <c r="F99" s="24">
         <v>2</v>
       </c>
       <c r="G99" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="30">
+      <c r="H99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="30">
       <c r="A100" t="s">
         <v>90</v>
       </c>
@@ -8767,17 +8999,20 @@
       <c r="D100" t="s">
         <v>10</v>
       </c>
-      <c r="E100" s="23">
+      <c r="E100" s="24">
         <v>2</v>
       </c>
-      <c r="F100" s="23">
+      <c r="F100" s="24">
         <v>1</v>
       </c>
       <c r="G100" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="30">
+      <c r="H100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="30">
       <c r="A101" t="s">
         <v>90</v>
       </c>
@@ -8791,17 +9026,20 @@
       <c r="D101" t="s">
         <v>10</v>
       </c>
-      <c r="E101" s="23">
+      <c r="E101" s="24">
         <v>2</v>
       </c>
-      <c r="F101" s="23">
+      <c r="F101" s="24">
         <v>1</v>
       </c>
       <c r="G101" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" ht="30">
+      <c r="H101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="30">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -8815,17 +9053,20 @@
       <c r="D102" t="s">
         <v>10</v>
       </c>
-      <c r="E102" s="23">
+      <c r="E102" s="24">
         <v>5</v>
       </c>
-      <c r="F102" s="23">
+      <c r="F102" s="24">
         <v>4</v>
       </c>
       <c r="G102" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="103" spans="1:7" ht="30">
+      <c r="H102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="30">
       <c r="A103" t="s">
         <v>90</v>
       </c>
@@ -8839,17 +9080,20 @@
       <c r="D103" t="s">
         <v>10</v>
       </c>
-      <c r="E103" s="23">
+      <c r="E103" s="24">
         <v>-8</v>
       </c>
-      <c r="F103" s="23">
+      <c r="F103" s="24">
         <v>2</v>
       </c>
       <c r="G103" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="104" spans="1:7" ht="30">
+      <c r="H103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="30">
       <c r="A104" t="s">
         <v>90</v>
       </c>
@@ -8863,17 +9107,20 @@
       <c r="D104" t="s">
         <v>10</v>
       </c>
-      <c r="E104" s="23">
+      <c r="E104" s="24">
         <v>6</v>
       </c>
-      <c r="F104" s="23">
+      <c r="F104" s="24">
         <v>5</v>
       </c>
       <c r="G104" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="105" spans="1:7" ht="30">
+      <c r="H104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="30">
       <c r="A105" t="s">
         <v>90</v>
       </c>
@@ -8887,17 +9134,20 @@
       <c r="D105" t="s">
         <v>14</v>
       </c>
-      <c r="E105" s="23">
+      <c r="E105" s="24">
         <v>5</v>
       </c>
-      <c r="F105" s="23">
+      <c r="F105" s="24">
         <v>1</v>
       </c>
       <c r="G105" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="106" spans="1:7" ht="30">
+      <c r="H105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="30">
       <c r="A106" t="s">
         <v>90</v>
       </c>
@@ -8911,17 +9161,20 @@
       <c r="D106" t="s">
         <v>14</v>
       </c>
-      <c r="E106" s="23">
+      <c r="E106" s="24">
         <v>5</v>
       </c>
-      <c r="F106" s="23">
+      <c r="F106" s="24">
         <v>2</v>
       </c>
       <c r="G106" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="107" spans="1:7" ht="30">
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="30">
       <c r="A107" t="s">
         <v>90</v>
       </c>
@@ -8935,17 +9188,20 @@
       <c r="D107" t="s">
         <v>14</v>
       </c>
-      <c r="E107" s="23">
+      <c r="E107" s="24">
         <v>-2</v>
       </c>
-      <c r="F107" s="23">
+      <c r="F107" s="24">
         <v>-2</v>
       </c>
       <c r="G107" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="108" spans="1:7" ht="30">
+      <c r="H107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="30">
       <c r="A108" t="s">
         <v>90</v>
       </c>
@@ -8959,17 +9215,20 @@
       <c r="D108" t="s">
         <v>14</v>
       </c>
-      <c r="E108" s="23">
+      <c r="E108" s="24">
         <v>-2</v>
       </c>
-      <c r="F108" s="23">
+      <c r="F108" s="24">
         <v>-2</v>
       </c>
       <c r="G108" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="109" spans="1:7" ht="30">
+      <c r="H108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="30">
       <c r="A109" t="s">
         <v>90</v>
       </c>
@@ -8983,17 +9242,20 @@
       <c r="D109" t="s">
         <v>14</v>
       </c>
-      <c r="E109" s="23">
+      <c r="E109" s="24">
         <v>4</v>
       </c>
-      <c r="F109" s="23">
+      <c r="F109" s="24">
         <v>1</v>
       </c>
       <c r="G109" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="110" spans="1:7" ht="30">
+      <c r="H109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="30">
       <c r="A110" t="s">
         <v>90</v>
       </c>
@@ -9007,17 +9269,20 @@
       <c r="D110" t="s">
         <v>14</v>
       </c>
-      <c r="E110" s="23">
+      <c r="E110" s="24">
         <v>9</v>
       </c>
-      <c r="F110" s="23">
+      <c r="F110" s="24">
         <v>3</v>
       </c>
       <c r="G110" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="111" spans="1:7" ht="30">
+      <c r="H110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="30">
       <c r="A111" t="s">
         <v>90</v>
       </c>
@@ -9031,17 +9296,20 @@
       <c r="D111" t="s">
         <v>14</v>
       </c>
-      <c r="E111" s="23">
+      <c r="E111" s="24">
         <v>-9</v>
       </c>
-      <c r="F111" s="23">
+      <c r="F111" s="24">
         <v>-3</v>
       </c>
       <c r="G111" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="112" spans="1:7" ht="30">
+      <c r="H111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="30">
       <c r="A112" t="s">
         <v>91</v>
       </c>
@@ -9055,17 +9323,20 @@
       <c r="D112" t="s">
         <v>10</v>
       </c>
-      <c r="E112" s="23">
+      <c r="E112" s="24">
         <v>9</v>
       </c>
-      <c r="F112" s="23">
+      <c r="F112" s="24">
         <v>7</v>
       </c>
       <c r="G112" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="113" spans="1:7" ht="30">
+      <c r="H112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="30">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -9079,17 +9350,20 @@
       <c r="D113" t="s">
         <v>10</v>
       </c>
-      <c r="E113" s="23">
+      <c r="E113" s="24">
         <v>8</v>
       </c>
-      <c r="F113" s="23">
+      <c r="F113" s="24">
         <v>7</v>
       </c>
       <c r="G113" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="114" spans="1:7" ht="30">
+      <c r="H113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="30">
       <c r="A114" t="s">
         <v>91</v>
       </c>
@@ -9103,17 +9377,20 @@
       <c r="D114" t="s">
         <v>10</v>
       </c>
-      <c r="E114" s="23">
+      <c r="E114" s="24">
         <v>7</v>
       </c>
-      <c r="F114" s="23">
+      <c r="F114" s="24">
         <v>7</v>
       </c>
       <c r="G114" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="115" spans="1:7" ht="30">
+      <c r="H114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="30">
       <c r="A115" t="s">
         <v>91</v>
       </c>
@@ -9127,17 +9404,20 @@
       <c r="D115" t="s">
         <v>10</v>
       </c>
-      <c r="E115" s="23">
+      <c r="E115" s="24">
         <v>6</v>
       </c>
-      <c r="F115" s="23">
+      <c r="F115" s="24">
         <v>7</v>
       </c>
       <c r="G115" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="116" spans="1:7" ht="30">
+      <c r="H115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="30">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -9151,17 +9431,20 @@
       <c r="D116" t="s">
         <v>10</v>
       </c>
-      <c r="E116" s="23">
-        <v>0</v>
-      </c>
-      <c r="F116" s="23">
+      <c r="E116" s="24">
+        <v>0</v>
+      </c>
+      <c r="F116" s="24">
         <v>0</v>
       </c>
       <c r="G116" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="117" spans="1:7" ht="30">
+      <c r="H116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="30">
       <c r="A117" t="s">
         <v>91</v>
       </c>
@@ -9175,17 +9458,20 @@
       <c r="D117" t="s">
         <v>14</v>
       </c>
-      <c r="E117" s="23">
+      <c r="E117" s="24">
         <v>-4</v>
       </c>
-      <c r="F117" s="23">
+      <c r="F117" s="24">
         <v>-2</v>
       </c>
       <c r="G117" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="118" spans="1:7" ht="30">
+      <c r="H117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="30">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -9199,17 +9485,20 @@
       <c r="D118" t="s">
         <v>14</v>
       </c>
-      <c r="E118" s="23">
+      <c r="E118" s="24">
         <v>2</v>
       </c>
-      <c r="F118" s="23">
+      <c r="F118" s="24">
         <v>2</v>
       </c>
       <c r="G118" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="119" spans="1:7" ht="30">
+      <c r="H118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="30">
       <c r="A119" t="s">
         <v>91</v>
       </c>
@@ -9223,17 +9512,20 @@
       <c r="D119" t="s">
         <v>14</v>
       </c>
-      <c r="E119" s="23">
-        <v>0</v>
-      </c>
-      <c r="F119" s="23">
+      <c r="E119" s="24">
+        <v>0</v>
+      </c>
+      <c r="F119" s="24">
         <v>0</v>
       </c>
       <c r="G119" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="120" spans="1:7" ht="30">
+      <c r="H119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="30">
       <c r="A120" t="s">
         <v>91</v>
       </c>
@@ -9247,17 +9539,20 @@
       <c r="D120" t="s">
         <v>14</v>
       </c>
-      <c r="E120" s="23">
+      <c r="E120" s="24">
         <v>-2</v>
       </c>
-      <c r="F120" s="23">
+      <c r="F120" s="24">
         <v>-1</v>
       </c>
       <c r="G120" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="121" spans="1:7" ht="30">
+      <c r="H120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="30">
       <c r="A121" t="s">
         <v>91</v>
       </c>
@@ -9271,17 +9566,20 @@
       <c r="D121" t="s">
         <v>14</v>
       </c>
-      <c r="E121" s="23">
+      <c r="E121" s="24">
         <v>4</v>
       </c>
-      <c r="F121" s="23">
+      <c r="F121" s="24">
         <v>4</v>
       </c>
       <c r="G121" s="14" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="122" spans="1:7" ht="30">
+      <c r="H121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="30">
       <c r="A122" t="s">
         <v>92</v>
       </c>
@@ -9295,17 +9593,20 @@
       <c r="D122" t="s">
         <v>10</v>
       </c>
-      <c r="E122" s="23">
+      <c r="E122" s="24">
         <v>-8</v>
       </c>
-      <c r="F122" s="23">
+      <c r="F122" s="24">
         <v>-4</v>
       </c>
       <c r="G122" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="123" spans="1:7" ht="30">
+      <c r="H122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="30">
       <c r="A123" t="s">
         <v>92</v>
       </c>
@@ -9319,17 +9620,20 @@
       <c r="D123" t="s">
         <v>10</v>
       </c>
-      <c r="E123" s="23">
+      <c r="E123" s="24">
         <v>-6</v>
       </c>
-      <c r="F123" s="23">
+      <c r="F123" s="24">
         <v>-5</v>
       </c>
       <c r="G123" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="124" spans="1:7" ht="30">
+      <c r="H123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="30">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -9343,17 +9647,20 @@
       <c r="D124" t="s">
         <v>10</v>
       </c>
-      <c r="E124" s="23">
+      <c r="E124" s="24">
         <v>-7</v>
       </c>
-      <c r="F124" s="23">
+      <c r="F124" s="24">
         <v>-4</v>
       </c>
       <c r="G124" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="125" spans="1:7" ht="30">
+      <c r="H124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="30">
       <c r="A125" t="s">
         <v>92</v>
       </c>
@@ -9367,17 +9674,20 @@
       <c r="D125" t="s">
         <v>10</v>
       </c>
-      <c r="E125" s="23">
+      <c r="E125" s="24">
         <v>-6</v>
       </c>
-      <c r="F125" s="23">
+      <c r="F125" s="24">
         <v>-3</v>
       </c>
       <c r="G125" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="126" spans="1:7" ht="30">
+      <c r="H125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="30">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -9391,17 +9701,20 @@
       <c r="D126" t="s">
         <v>10</v>
       </c>
-      <c r="E126" s="23">
+      <c r="E126" s="24">
         <v>-5</v>
       </c>
-      <c r="F126" s="23">
+      <c r="F126" s="24">
         <v>-4</v>
       </c>
       <c r="G126" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" ht="30">
+      <c r="H126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="30">
       <c r="A127" t="s">
         <v>92</v>
       </c>
@@ -9415,17 +9728,20 @@
       <c r="D127" t="s">
         <v>10</v>
       </c>
-      <c r="E127" s="23">
+      <c r="E127" s="24">
         <v>-5</v>
       </c>
-      <c r="F127" s="23">
+      <c r="F127" s="24">
         <v>-4</v>
       </c>
       <c r="G127" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" ht="30">
+      <c r="H127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="30">
       <c r="A128" t="s">
         <v>92</v>
       </c>
@@ -9439,17 +9755,20 @@
       <c r="D128" t="s">
         <v>14</v>
       </c>
-      <c r="E128" s="23">
+      <c r="E128" s="24">
         <v>6</v>
       </c>
-      <c r="F128" s="23">
+      <c r="F128" s="24">
         <v>2</v>
       </c>
       <c r="G128" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="129" spans="1:7" ht="30">
+      <c r="H128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="30">
       <c r="A129" t="s">
         <v>92</v>
       </c>
@@ -9463,17 +9782,20 @@
       <c r="D129" t="s">
         <v>14</v>
       </c>
-      <c r="E129" s="23">
+      <c r="E129" s="24">
         <v>-8</v>
       </c>
-      <c r="F129" s="23">
+      <c r="F129" s="24">
         <v>-2</v>
       </c>
       <c r="G129" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="130" spans="1:7" ht="30">
+      <c r="H129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="30">
       <c r="A130" t="s">
         <v>92</v>
       </c>
@@ -9487,17 +9809,20 @@
       <c r="D130" t="s">
         <v>14</v>
       </c>
-      <c r="E130" s="23">
+      <c r="E130" s="24">
         <v>5</v>
       </c>
-      <c r="F130" s="23">
+      <c r="F130" s="24">
         <v>1</v>
       </c>
       <c r="G130" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="131" spans="1:7" ht="30">
+      <c r="H130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="30">
       <c r="A131" t="s">
         <v>92</v>
       </c>
@@ -9511,17 +9836,20 @@
       <c r="D131" t="s">
         <v>14</v>
       </c>
-      <c r="E131" s="23">
+      <c r="E131" s="24">
         <v>4</v>
       </c>
-      <c r="F131" s="23">
+      <c r="F131" s="24">
         <v>1</v>
       </c>
       <c r="G131" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="132" spans="1:7" ht="30">
+      <c r="H131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="30">
       <c r="A132" t="s">
         <v>92</v>
       </c>
@@ -9535,17 +9863,20 @@
       <c r="D132" t="s">
         <v>14</v>
       </c>
-      <c r="E132" s="23">
+      <c r="E132" s="24">
         <v>-7</v>
       </c>
-      <c r="F132" s="23">
+      <c r="F132" s="24">
         <v>-3</v>
       </c>
       <c r="G132" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="133" spans="1:7" ht="30">
+      <c r="H132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="30">
       <c r="A133" t="s">
         <v>92</v>
       </c>
@@ -9559,17 +9890,20 @@
       <c r="D133" t="s">
         <v>14</v>
       </c>
-      <c r="E133" s="23">
+      <c r="E133" s="24">
         <v>-7</v>
       </c>
-      <c r="F133" s="23">
+      <c r="F133" s="24">
         <v>-3</v>
       </c>
       <c r="G133" s="14" t="s">
         <v>310</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" ht="30">
+      <c r="H133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="30">
       <c r="A134" t="s">
         <v>93</v>
       </c>
@@ -9583,17 +9917,20 @@
       <c r="D134" t="s">
         <v>10</v>
       </c>
-      <c r="E134" s="23">
+      <c r="E134" s="24">
         <v>-5</v>
       </c>
-      <c r="F134" s="23">
+      <c r="F134" s="24">
         <v>-2</v>
       </c>
       <c r="G134" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="135" spans="1:7" ht="30">
+      <c r="H134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="30">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -9607,17 +9944,20 @@
       <c r="D135" t="s">
         <v>10</v>
       </c>
-      <c r="E135" s="23">
+      <c r="E135" s="24">
         <v>-4</v>
       </c>
-      <c r="F135" s="23">
+      <c r="F135" s="24">
         <v>-2</v>
       </c>
       <c r="G135" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="136" spans="1:7" ht="30">
+      <c r="H135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="30">
       <c r="A136" t="s">
         <v>93</v>
       </c>
@@ -9631,17 +9971,20 @@
       <c r="D136" t="s">
         <v>10</v>
       </c>
-      <c r="E136" s="23">
-        <v>0</v>
-      </c>
-      <c r="F136" s="23">
+      <c r="E136" s="24">
+        <v>0</v>
+      </c>
+      <c r="F136" s="24">
         <v>0</v>
       </c>
       <c r="G136" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="137" spans="1:7" ht="30">
+      <c r="H136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="30">
       <c r="A137" t="s">
         <v>93</v>
       </c>
@@ -9655,17 +9998,20 @@
       <c r="D137" t="s">
         <v>10</v>
       </c>
-      <c r="E137" s="23">
-        <v>0</v>
-      </c>
-      <c r="F137" s="23">
+      <c r="E137" s="24">
+        <v>0</v>
+      </c>
+      <c r="F137" s="24">
         <v>0</v>
       </c>
       <c r="G137" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="138" spans="1:7" ht="30">
+      <c r="H137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="30">
       <c r="A138" t="s">
         <v>93</v>
       </c>
@@ -9679,17 +10025,20 @@
       <c r="D138" t="s">
         <v>10</v>
       </c>
-      <c r="E138" s="23">
-        <v>0</v>
-      </c>
-      <c r="F138" s="23">
+      <c r="E138" s="24">
+        <v>0</v>
+      </c>
+      <c r="F138" s="24">
         <v>0</v>
       </c>
       <c r="G138" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="139" spans="1:7" ht="30">
+      <c r="H138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="30">
       <c r="A139" t="s">
         <v>93</v>
       </c>
@@ -9703,17 +10052,20 @@
       <c r="D139" t="s">
         <v>10</v>
       </c>
-      <c r="E139" s="23">
-        <v>0</v>
-      </c>
-      <c r="F139" s="23">
+      <c r="E139" s="24">
+        <v>0</v>
+      </c>
+      <c r="F139" s="24">
         <v>0</v>
       </c>
       <c r="G139" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="140" spans="1:7" ht="30">
+      <c r="H139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" ht="30">
       <c r="A140" t="s">
         <v>93</v>
       </c>
@@ -9727,17 +10079,20 @@
       <c r="D140" t="s">
         <v>14</v>
       </c>
-      <c r="E140" s="23">
+      <c r="E140" s="24">
         <v>7</v>
       </c>
-      <c r="F140" s="23">
+      <c r="F140" s="24">
         <v>4</v>
       </c>
       <c r="G140" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="141" spans="1:7" ht="30">
+      <c r="H140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" ht="30">
       <c r="A141" t="s">
         <v>93</v>
       </c>
@@ -9751,17 +10106,20 @@
       <c r="D141" t="s">
         <v>14</v>
       </c>
-      <c r="E141" s="23">
+      <c r="E141" s="24">
         <v>6</v>
       </c>
-      <c r="F141" s="23">
+      <c r="F141" s="24">
         <v>4</v>
       </c>
       <c r="G141" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="142" spans="1:7" ht="30">
+      <c r="H141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" ht="30">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -9775,17 +10133,20 @@
       <c r="D142" t="s">
         <v>14</v>
       </c>
-      <c r="E142" s="23">
+      <c r="E142" s="24">
         <v>-2</v>
       </c>
-      <c r="F142" s="23">
+      <c r="F142" s="24">
         <v>2</v>
       </c>
       <c r="G142" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="143" spans="1:7" ht="30">
+      <c r="H142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" ht="30">
       <c r="A143" t="s">
         <v>93</v>
       </c>
@@ -9799,17 +10160,20 @@
       <c r="D143" t="s">
         <v>14</v>
       </c>
-      <c r="E143" s="23">
+      <c r="E143" s="24">
         <v>-3</v>
       </c>
-      <c r="F143" s="23">
+      <c r="F143" s="24">
         <v>3</v>
       </c>
       <c r="G143" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="144" spans="1:7" ht="30">
+      <c r="H143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" ht="30">
       <c r="A144" t="s">
         <v>93</v>
       </c>
@@ -9823,17 +10187,20 @@
       <c r="D144" t="s">
         <v>14</v>
       </c>
-      <c r="E144" s="23">
+      <c r="E144" s="24">
         <v>5</v>
       </c>
-      <c r="F144" s="23">
+      <c r="F144" s="24">
         <v>5</v>
       </c>
       <c r="G144" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="145" spans="1:7" ht="30">
+      <c r="H144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" ht="30">
       <c r="A145" t="s">
         <v>93</v>
       </c>
@@ -9847,17 +10214,20 @@
       <c r="D145" t="s">
         <v>14</v>
       </c>
-      <c r="E145" s="23">
+      <c r="E145" s="24">
         <v>-6</v>
       </c>
-      <c r="F145" s="23">
+      <c r="F145" s="24">
         <v>-2</v>
       </c>
       <c r="G145" s="14" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="146" spans="1:7" ht="30">
+      <c r="H145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" ht="30">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -9871,112 +10241,143 @@
       <c r="D146" t="s">
         <v>14</v>
       </c>
-      <c r="E146" s="23">
-        <v>10</v>
-      </c>
-      <c r="F146" s="23">
+      <c r="E146" s="24">
+        <v>10</v>
+      </c>
+      <c r="F146" s="24">
         <v>8</v>
       </c>
       <c r="G146" s="14" t="s">
         <v>321</v>
       </c>
-    </row>
-    <row r="147" spans="1:7">
+      <c r="H146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="B147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C147, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E147" s="24"/>
+      <c r="F147" s="24"/>
       <c r="G147" s="14"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:8">
       <c r="B148" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C148, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E148" s="24"/>
+      <c r="F148" s="24"/>
       <c r="G148" s="14"/>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:8">
       <c r="B149" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C149, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E149" s="24"/>
+      <c r="F149" s="24"/>
       <c r="G149" s="14"/>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:8">
       <c r="B150" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C150, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E150" s="24"/>
+      <c r="F150" s="24"/>
       <c r="G150" s="14"/>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:8">
       <c r="B151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C151, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E151" s="24"/>
+      <c r="F151" s="24"/>
       <c r="G151" s="14"/>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:8">
       <c r="B152" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C152, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E152" s="24"/>
+      <c r="F152" s="24"/>
       <c r="G152" s="14"/>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:8">
       <c r="B153" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C153, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E153" s="24"/>
+      <c r="F153" s="24"/>
       <c r="G153" s="14"/>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:8">
       <c r="B154" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C154, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E154" s="24"/>
+      <c r="F154" s="24"/>
       <c r="G154" s="14"/>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:8">
       <c r="B155" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C155, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E155" s="24"/>
+      <c r="F155" s="24"/>
       <c r="G155" s="14"/>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:8">
       <c r="B156" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C156, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E156" s="24"/>
+      <c r="F156" s="24"/>
       <c r="G156" s="14"/>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:8">
       <c r="B157" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C157, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E157" s="24"/>
+      <c r="F157" s="24"/>
       <c r="G157" s="14"/>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:8">
       <c r="B158" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C158, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E158" s="24"/>
+      <c r="F158" s="24"/>
       <c r="G158" s="14"/>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:8">
       <c r="B159" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C159, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E159" s="24"/>
+      <c r="F159" s="24"/>
       <c r="G159" s="14"/>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:8">
       <c r="B160" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C160, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E160" s="24"/>
+      <c r="F160" s="24"/>
       <c r="G160" s="14"/>
     </row>
     <row r="161" spans="2:7">
@@ -9984,6 +10385,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C161, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E161" s="24"/>
+      <c r="F161" s="24"/>
       <c r="G161" s="14"/>
     </row>
     <row r="162" spans="2:7">
@@ -9991,6 +10394,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C162, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E162" s="24"/>
+      <c r="F162" s="24"/>
       <c r="G162" s="14"/>
     </row>
     <row r="163" spans="2:7">
@@ -9998,6 +10403,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C163, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E163" s="24"/>
+      <c r="F163" s="24"/>
       <c r="G163" s="14"/>
     </row>
     <row r="164" spans="2:7">
@@ -10005,6 +10412,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C164, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E164" s="24"/>
+      <c r="F164" s="24"/>
       <c r="G164" s="14"/>
     </row>
     <row r="165" spans="2:7">
@@ -10012,6 +10421,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C165, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E165" s="24"/>
+      <c r="F165" s="24"/>
       <c r="G165" s="14"/>
     </row>
     <row r="166" spans="2:7">
@@ -10019,6 +10430,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C166, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E166" s="24"/>
+      <c r="F166" s="24"/>
       <c r="G166" s="14"/>
     </row>
     <row r="167" spans="2:7">
@@ -10026,6 +10439,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C167, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E167" s="24"/>
+      <c r="F167" s="24"/>
       <c r="G167" s="14"/>
     </row>
     <row r="168" spans="2:7">
@@ -10033,6 +10448,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C168, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E168" s="24"/>
+      <c r="F168" s="24"/>
       <c r="G168" s="14"/>
     </row>
     <row r="169" spans="2:7">
@@ -10040,6 +10457,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C169, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E169" s="24"/>
+      <c r="F169" s="24"/>
       <c r="G169" s="14"/>
     </row>
     <row r="170" spans="2:7">
@@ -10047,6 +10466,8 @@
         <f>IFERROR(_xlfn.XLOOKUP(C170, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
+      <c r="E170" s="24"/>
+      <c r="F170" s="24"/>
       <c r="G170" s="14"/>
     </row>
     <row r="171" spans="2:7">

--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A3B8402-5AAB-4030-9BD4-479EC79A1485}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE201DE-57E4-4570-B0A7-FE00438C8AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1686,7 +1686,18 @@
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K327" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
-  <autoFilter ref="A1:K327" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}"/>
+  <autoFilter ref="A1:K327" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="ATO006"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="VERMELHO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{BAF761B8-D6AF-48D3-A1F5-3D35088A4234}" name="event_id"/>
     <tableColumn id="2" xr3:uid="{78C225EA-4EED-44B0-BBCE-FD76B432B72B}" name="actor_id" dataDxfId="2">
@@ -4522,13 +4533,13 @@
         <v>14</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E90">
         <v>35</v>
       </c>
       <c r="F90" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="G90" s="14" t="s">
         <v>332</v>
@@ -6339,7 +6350,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30">
+    <row r="2" spans="1:11" ht="30" hidden="1">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -6366,7 +6377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" hidden="1">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -6393,7 +6404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30">
+    <row r="4" spans="1:11" ht="30" hidden="1">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -6420,7 +6431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30">
+    <row r="5" spans="1:11" ht="30" hidden="1">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -6447,7 +6458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="45">
+    <row r="6" spans="1:11" ht="45" hidden="1">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -6501,7 +6512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60">
+    <row r="8" spans="1:11" ht="60" hidden="1">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -6528,7 +6539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" hidden="1">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -6555,7 +6566,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="30">
+    <row r="10" spans="1:11" ht="30" hidden="1">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -6582,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="30">
+    <row r="11" spans="1:11" ht="30" hidden="1">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -6609,7 +6620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30">
+    <row r="12" spans="1:11" ht="30" hidden="1">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -6636,7 +6647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="30">
+    <row r="13" spans="1:11" ht="30" hidden="1">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -6663,7 +6674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="30">
+    <row r="14" spans="1:11" ht="30" hidden="1">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -6690,7 +6701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="30">
+    <row r="15" spans="1:11" ht="30" hidden="1">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -6717,7 +6728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="30">
+    <row r="16" spans="1:11" ht="30" hidden="1">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -6744,7 +6755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30">
+    <row r="17" spans="1:8" ht="30" hidden="1">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -6771,7 +6782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30">
+    <row r="18" spans="1:8" ht="30" hidden="1">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6798,7 +6809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30">
+    <row r="19" spans="1:8" ht="30" hidden="1">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -6825,7 +6836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30">
+    <row r="20" spans="1:8" ht="30" hidden="1">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -6852,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30">
+    <row r="21" spans="1:8" ht="30" hidden="1">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -6879,7 +6890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30">
+    <row r="22" spans="1:8" ht="30" hidden="1">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -6906,7 +6917,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="42.75">
+    <row r="23" spans="1:8" ht="42.75" hidden="1">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -6933,7 +6944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30">
+    <row r="24" spans="1:8" ht="30" hidden="1">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -6960,7 +6971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" hidden="1">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -6987,7 +6998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30">
+    <row r="26" spans="1:8" ht="30" hidden="1">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -7014,7 +7025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30">
+    <row r="27" spans="1:8" ht="30" hidden="1">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -7041,7 +7052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30">
+    <row r="28" spans="1:8" ht="30" hidden="1">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -7068,7 +7079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="45">
+    <row r="29" spans="1:8" ht="45" hidden="1">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -7095,7 +7106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="30">
+    <row r="30" spans="1:8" ht="30" hidden="1">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -7122,7 +7133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="28.5">
+    <row r="31" spans="1:8" ht="28.5" hidden="1">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -7149,7 +7160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30">
+    <row r="32" spans="1:8" ht="30" hidden="1">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -7176,7 +7187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30">
+    <row r="33" spans="1:8" ht="30" hidden="1">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -7203,7 +7214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30">
+    <row r="34" spans="1:8" ht="30" hidden="1">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -7230,7 +7241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30">
+    <row r="35" spans="1:8" ht="30" hidden="1">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -7257,7 +7268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30">
+    <row r="36" spans="1:8" ht="30" hidden="1">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -7284,7 +7295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30">
+    <row r="37" spans="1:8" ht="30" hidden="1">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -7311,7 +7322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="30">
+    <row r="38" spans="1:8" ht="30" hidden="1">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -7338,7 +7349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30">
+    <row r="39" spans="1:8" ht="30" hidden="1">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -7365,7 +7376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="30">
+    <row r="40" spans="1:8" ht="30" hidden="1">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -7392,7 +7403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30">
+    <row r="41" spans="1:8" ht="30" hidden="1">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -7419,7 +7430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30">
+    <row r="42" spans="1:8" ht="30" hidden="1">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -7446,7 +7457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30">
+    <row r="43" spans="1:8" ht="30" hidden="1">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -7473,7 +7484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30">
+    <row r="44" spans="1:8" ht="30" hidden="1">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -7500,7 +7511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30">
+    <row r="45" spans="1:8" ht="30" hidden="1">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -7527,7 +7538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30">
+    <row r="46" spans="1:8" ht="30" hidden="1">
       <c r="A46" t="s">
         <v>82</v>
       </c>
@@ -7554,7 +7565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="30">
+    <row r="47" spans="1:8" ht="30" hidden="1">
       <c r="A47" t="s">
         <v>82</v>
       </c>
@@ -7581,7 +7592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30">
+    <row r="48" spans="1:8" ht="30" hidden="1">
       <c r="A48" t="s">
         <v>82</v>
       </c>
@@ -7623,7 +7634,7 @@
         <v>14</v>
       </c>
       <c r="E49" s="24">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="F49" s="24">
         <v>-2</v>
@@ -7635,7 +7646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30">
+    <row r="50" spans="1:8" ht="30" hidden="1">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -7662,7 +7673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="30">
+    <row r="51" spans="1:8" ht="30" hidden="1">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -7689,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30">
+    <row r="52" spans="1:8" ht="30" hidden="1">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -7716,7 +7727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="30">
+    <row r="53" spans="1:8" ht="30" hidden="1">
       <c r="A53" t="s">
         <v>82</v>
       </c>
@@ -7743,7 +7754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="30">
+    <row r="54" spans="1:8" ht="30" hidden="1">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -7770,7 +7781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="30">
+    <row r="55" spans="1:8" ht="30" hidden="1">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -7797,7 +7808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="30">
+    <row r="56" spans="1:8" ht="30" hidden="1">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -7824,7 +7835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30">
+    <row r="57" spans="1:8" ht="30" hidden="1">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -7851,7 +7862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="30">
+    <row r="58" spans="1:8" ht="30" hidden="1">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -7878,7 +7889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="30">
+    <row r="59" spans="1:8" ht="30" hidden="1">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -7905,7 +7916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="30">
+    <row r="60" spans="1:8" ht="30" hidden="1">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -7932,7 +7943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="30">
+    <row r="61" spans="1:8" ht="30" hidden="1">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -7959,7 +7970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="30">
+    <row r="62" spans="1:8" ht="30" hidden="1">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -7986,7 +7997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="30">
+    <row r="63" spans="1:8" ht="30" hidden="1">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -8013,7 +8024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="30">
+    <row r="64" spans="1:8" ht="30" hidden="1">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -8040,7 +8051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="30">
+    <row r="65" spans="1:8" ht="30" hidden="1">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -8067,7 +8078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="30">
+    <row r="66" spans="1:8" ht="30" hidden="1">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -8094,7 +8105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="30">
+    <row r="67" spans="1:8" ht="30" hidden="1">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -8121,7 +8132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="30">
+    <row r="68" spans="1:8" ht="30" hidden="1">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -8148,7 +8159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="30">
+    <row r="69" spans="1:8" ht="30" hidden="1">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -8175,7 +8186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="30">
+    <row r="70" spans="1:8" ht="30" hidden="1">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -8202,7 +8213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="30">
+    <row r="71" spans="1:8" ht="30" hidden="1">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -8229,7 +8240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="30">
+    <row r="72" spans="1:8" ht="30" hidden="1">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -8256,7 +8267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="30">
+    <row r="73" spans="1:8" ht="30" hidden="1">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -8283,7 +8294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="30">
+    <row r="74" spans="1:8" ht="30" hidden="1">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -8310,7 +8321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="30">
+    <row r="75" spans="1:8" ht="30" hidden="1">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -8337,7 +8348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="30">
+    <row r="76" spans="1:8" ht="30" hidden="1">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -8364,7 +8375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="30">
+    <row r="77" spans="1:8" ht="30" hidden="1">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -8391,7 +8402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="30">
+    <row r="78" spans="1:8" ht="30" hidden="1">
       <c r="A78" t="s">
         <v>84</v>
       </c>
@@ -8418,7 +8429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="30">
+    <row r="79" spans="1:8" ht="30" hidden="1">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -8445,7 +8456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="30">
+    <row r="80" spans="1:8" ht="30" hidden="1">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -8472,7 +8483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="30">
+    <row r="81" spans="1:8" ht="30" hidden="1">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -8499,7 +8510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="30">
+    <row r="82" spans="1:8" ht="30" hidden="1">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -8526,7 +8537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="30">
+    <row r="83" spans="1:8" ht="30" hidden="1">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -8553,7 +8564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="30">
+    <row r="84" spans="1:8" ht="30" hidden="1">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -8595,7 +8606,7 @@
         <v>14</v>
       </c>
       <c r="E85" s="24">
-        <v>-10</v>
+        <v>-5</v>
       </c>
       <c r="F85" s="24">
         <v>2</v>
@@ -8607,7 +8618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="30">
+    <row r="86" spans="1:8" ht="30" hidden="1">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -8634,7 +8645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="30">
+    <row r="87" spans="1:8" ht="30" hidden="1">
       <c r="A87" t="s">
         <v>84</v>
       </c>
@@ -8661,7 +8672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="30">
+    <row r="88" spans="1:8" ht="30" hidden="1">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -8688,7 +8699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="30">
+    <row r="89" spans="1:8" ht="30" hidden="1">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -8715,7 +8726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="30">
+    <row r="90" spans="1:8" ht="30" hidden="1">
       <c r="A90" t="s">
         <v>85</v>
       </c>
@@ -8742,7 +8753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="30">
+    <row r="91" spans="1:8" ht="30" hidden="1">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -8769,7 +8780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="30">
+    <row r="92" spans="1:8" ht="30" hidden="1">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -8823,7 +8834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="30">
+    <row r="94" spans="1:8" ht="30" hidden="1">
       <c r="A94" t="s">
         <v>85</v>
       </c>
@@ -8850,7 +8861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="30">
+    <row r="95" spans="1:8" ht="30" hidden="1">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -8877,7 +8888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="30">
+    <row r="96" spans="1:8" ht="30" hidden="1">
       <c r="A96" t="s">
         <v>85</v>
       </c>
@@ -8904,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="30">
+    <row r="97" spans="1:8" ht="30" hidden="1">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -8931,7 +8942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="30">
+    <row r="98" spans="1:8" ht="30" hidden="1">
       <c r="A98" t="s">
         <v>90</v>
       </c>
@@ -8958,7 +8969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="30">
+    <row r="99" spans="1:8" ht="30" hidden="1">
       <c r="A99" t="s">
         <v>90</v>
       </c>
@@ -8985,7 +8996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="30">
+    <row r="100" spans="1:8" ht="30" hidden="1">
       <c r="A100" t="s">
         <v>90</v>
       </c>
@@ -9012,7 +9023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="30">
+    <row r="101" spans="1:8" ht="30" hidden="1">
       <c r="A101" t="s">
         <v>90</v>
       </c>
@@ -9039,7 +9050,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="30">
+    <row r="102" spans="1:8" ht="30" hidden="1">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -9066,7 +9077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="30">
+    <row r="103" spans="1:8" ht="30" hidden="1">
       <c r="A103" t="s">
         <v>90</v>
       </c>
@@ -9093,7 +9104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="30">
+    <row r="104" spans="1:8" ht="30" hidden="1">
       <c r="A104" t="s">
         <v>90</v>
       </c>
@@ -9120,7 +9131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="30">
+    <row r="105" spans="1:8" ht="30" hidden="1">
       <c r="A105" t="s">
         <v>90</v>
       </c>
@@ -9147,7 +9158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="30">
+    <row r="106" spans="1:8" ht="30" hidden="1">
       <c r="A106" t="s">
         <v>90</v>
       </c>
@@ -9174,7 +9185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="30">
+    <row r="107" spans="1:8" ht="30" hidden="1">
       <c r="A107" t="s">
         <v>90</v>
       </c>
@@ -9201,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="30">
+    <row r="108" spans="1:8" ht="30" hidden="1">
       <c r="A108" t="s">
         <v>90</v>
       </c>
@@ -9228,7 +9239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="30">
+    <row r="109" spans="1:8" ht="30" hidden="1">
       <c r="A109" t="s">
         <v>90</v>
       </c>
@@ -9255,7 +9266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="30">
+    <row r="110" spans="1:8" ht="30" hidden="1">
       <c r="A110" t="s">
         <v>90</v>
       </c>
@@ -9297,7 +9308,7 @@
         <v>14</v>
       </c>
       <c r="E111" s="24">
-        <v>-9</v>
+        <v>-5</v>
       </c>
       <c r="F111" s="24">
         <v>-3</v>
@@ -9309,7 +9320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="30">
+    <row r="112" spans="1:8" ht="30" hidden="1">
       <c r="A112" t="s">
         <v>91</v>
       </c>
@@ -9336,7 +9347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="30">
+    <row r="113" spans="1:8" ht="30" hidden="1">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -9363,7 +9374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="30">
+    <row r="114" spans="1:8" ht="30" hidden="1">
       <c r="A114" t="s">
         <v>91</v>
       </c>
@@ -9390,7 +9401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="30">
+    <row r="115" spans="1:8" ht="30" hidden="1">
       <c r="A115" t="s">
         <v>91</v>
       </c>
@@ -9417,7 +9428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="30">
+    <row r="116" spans="1:8" ht="30" hidden="1">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -9444,7 +9455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="30">
+    <row r="117" spans="1:8" ht="30" hidden="1">
       <c r="A117" t="s">
         <v>91</v>
       </c>
@@ -9471,7 +9482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="30">
+    <row r="118" spans="1:8" ht="30" hidden="1">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -9498,7 +9509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="30">
+    <row r="119" spans="1:8" ht="30" hidden="1">
       <c r="A119" t="s">
         <v>91</v>
       </c>
@@ -9552,7 +9563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="30">
+    <row r="121" spans="1:8" ht="30" hidden="1">
       <c r="A121" t="s">
         <v>91</v>
       </c>
@@ -9579,7 +9590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="30">
+    <row r="122" spans="1:8" ht="30" hidden="1">
       <c r="A122" t="s">
         <v>92</v>
       </c>
@@ -9606,7 +9617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="30">
+    <row r="123" spans="1:8" ht="30" hidden="1">
       <c r="A123" t="s">
         <v>92</v>
       </c>
@@ -9633,7 +9644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="30">
+    <row r="124" spans="1:8" ht="30" hidden="1">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -9660,7 +9671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="30">
+    <row r="125" spans="1:8" ht="30" hidden="1">
       <c r="A125" t="s">
         <v>92</v>
       </c>
@@ -9687,7 +9698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="30">
+    <row r="126" spans="1:8" ht="30" hidden="1">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -9714,7 +9725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="30">
+    <row r="127" spans="1:8" ht="30" hidden="1">
       <c r="A127" t="s">
         <v>92</v>
       </c>
@@ -9741,7 +9752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="30">
+    <row r="128" spans="1:8" ht="30" hidden="1">
       <c r="A128" t="s">
         <v>92</v>
       </c>
@@ -9783,7 +9794,7 @@
         <v>14</v>
       </c>
       <c r="E129" s="24">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="F129" s="24">
         <v>-2</v>
@@ -9795,7 +9806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="30">
+    <row r="130" spans="1:8" ht="30" hidden="1">
       <c r="A130" t="s">
         <v>92</v>
       </c>
@@ -9822,7 +9833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="30">
+    <row r="131" spans="1:8" ht="30" hidden="1">
       <c r="A131" t="s">
         <v>92</v>
       </c>
@@ -9849,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="30">
+    <row r="132" spans="1:8" ht="30" hidden="1">
       <c r="A132" t="s">
         <v>92</v>
       </c>
@@ -9876,7 +9887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="30">
+    <row r="133" spans="1:8" ht="30" hidden="1">
       <c r="A133" t="s">
         <v>92</v>
       </c>
@@ -9903,7 +9914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="30">
+    <row r="134" spans="1:8" ht="30" hidden="1">
       <c r="A134" t="s">
         <v>93</v>
       </c>
@@ -9930,7 +9941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="30">
+    <row r="135" spans="1:8" ht="30" hidden="1">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -9957,7 +9968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="30">
+    <row r="136" spans="1:8" ht="30" hidden="1">
       <c r="A136" t="s">
         <v>93</v>
       </c>
@@ -9984,7 +9995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="30">
+    <row r="137" spans="1:8" ht="30" hidden="1">
       <c r="A137" t="s">
         <v>93</v>
       </c>
@@ -10011,7 +10022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="30">
+    <row r="138" spans="1:8" ht="30" hidden="1">
       <c r="A138" t="s">
         <v>93</v>
       </c>
@@ -10038,7 +10049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="30">
+    <row r="139" spans="1:8" ht="30" hidden="1">
       <c r="A139" t="s">
         <v>93</v>
       </c>
@@ -10065,7 +10076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="30">
+    <row r="140" spans="1:8" ht="30" hidden="1">
       <c r="A140" t="s">
         <v>93</v>
       </c>
@@ -10092,7 +10103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="30">
+    <row r="141" spans="1:8" ht="30" hidden="1">
       <c r="A141" t="s">
         <v>93</v>
       </c>
@@ -10119,7 +10130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="30">
+    <row r="142" spans="1:8" ht="30" hidden="1">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -10146,7 +10157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="30">
+    <row r="143" spans="1:8" ht="30" hidden="1">
       <c r="A143" t="s">
         <v>93</v>
       </c>
@@ -10173,7 +10184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="30">
+    <row r="144" spans="1:8" ht="30" hidden="1">
       <c r="A144" t="s">
         <v>93</v>
       </c>
@@ -10215,7 +10226,7 @@
         <v>14</v>
       </c>
       <c r="E145" s="24">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="F145" s="24">
         <v>-2</v>
@@ -10227,7 +10238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="30">
+    <row r="146" spans="1:8" ht="30" hidden="1">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -10254,7 +10265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" hidden="1">
       <c r="B147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C147, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10263,7 +10274,7 @@
       <c r="F147" s="24"/>
       <c r="G147" s="14"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" hidden="1">
       <c r="B148" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C148, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10272,7 +10283,7 @@
       <c r="F148" s="24"/>
       <c r="G148" s="14"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" hidden="1">
       <c r="B149" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C149, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10281,7 +10292,7 @@
       <c r="F149" s="24"/>
       <c r="G149" s="14"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" hidden="1">
       <c r="B150" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C150, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10290,7 +10301,7 @@
       <c r="F150" s="24"/>
       <c r="G150" s="14"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" hidden="1">
       <c r="B151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C151, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10299,7 +10310,7 @@
       <c r="F151" s="24"/>
       <c r="G151" s="14"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" hidden="1">
       <c r="B152" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C152, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10308,7 +10319,7 @@
       <c r="F152" s="24"/>
       <c r="G152" s="14"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" hidden="1">
       <c r="B153" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C153, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10317,7 +10328,7 @@
       <c r="F153" s="24"/>
       <c r="G153" s="14"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" hidden="1">
       <c r="B154" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C154, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10326,7 +10337,7 @@
       <c r="F154" s="24"/>
       <c r="G154" s="14"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" hidden="1">
       <c r="B155" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C155, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10335,7 +10346,7 @@
       <c r="F155" s="24"/>
       <c r="G155" s="14"/>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" hidden="1">
       <c r="B156" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C156, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10344,7 +10355,7 @@
       <c r="F156" s="24"/>
       <c r="G156" s="14"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" hidden="1">
       <c r="B157" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C157, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10353,7 +10364,7 @@
       <c r="F157" s="24"/>
       <c r="G157" s="14"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" hidden="1">
       <c r="B158" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C158, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10362,7 +10373,7 @@
       <c r="F158" s="24"/>
       <c r="G158" s="14"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" hidden="1">
       <c r="B159" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C159, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10371,7 +10382,7 @@
       <c r="F159" s="24"/>
       <c r="G159" s="14"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" hidden="1">
       <c r="B160" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C160, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10380,7 +10391,7 @@
       <c r="F160" s="24"/>
       <c r="G160" s="14"/>
     </row>
-    <row r="161" spans="2:7">
+    <row r="161" spans="2:7" hidden="1">
       <c r="B161" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C161, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10389,7 +10400,7 @@
       <c r="F161" s="24"/>
       <c r="G161" s="14"/>
     </row>
-    <row r="162" spans="2:7">
+    <row r="162" spans="2:7" hidden="1">
       <c r="B162" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C162, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10398,7 +10409,7 @@
       <c r="F162" s="24"/>
       <c r="G162" s="14"/>
     </row>
-    <row r="163" spans="2:7">
+    <row r="163" spans="2:7" hidden="1">
       <c r="B163" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C163, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10407,7 +10418,7 @@
       <c r="F163" s="24"/>
       <c r="G163" s="14"/>
     </row>
-    <row r="164" spans="2:7">
+    <row r="164" spans="2:7" hidden="1">
       <c r="B164" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C164, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10416,7 +10427,7 @@
       <c r="F164" s="24"/>
       <c r="G164" s="14"/>
     </row>
-    <row r="165" spans="2:7">
+    <row r="165" spans="2:7" hidden="1">
       <c r="B165" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C165, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10425,7 +10436,7 @@
       <c r="F165" s="24"/>
       <c r="G165" s="14"/>
     </row>
-    <row r="166" spans="2:7">
+    <row r="166" spans="2:7" hidden="1">
       <c r="B166" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C166, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10434,7 +10445,7 @@
       <c r="F166" s="24"/>
       <c r="G166" s="14"/>
     </row>
-    <row r="167" spans="2:7">
+    <row r="167" spans="2:7" hidden="1">
       <c r="B167" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C167, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10443,7 +10454,7 @@
       <c r="F167" s="24"/>
       <c r="G167" s="14"/>
     </row>
-    <row r="168" spans="2:7">
+    <row r="168" spans="2:7" hidden="1">
       <c r="B168" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C168, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10452,7 +10463,7 @@
       <c r="F168" s="24"/>
       <c r="G168" s="14"/>
     </row>
-    <row r="169" spans="2:7">
+    <row r="169" spans="2:7" hidden="1">
       <c r="B169" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C169, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10461,7 +10472,7 @@
       <c r="F169" s="24"/>
       <c r="G169" s="14"/>
     </row>
-    <row r="170" spans="2:7">
+    <row r="170" spans="2:7" hidden="1">
       <c r="B170" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C170, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
@@ -10470,1099 +10481,1099 @@
       <c r="F170" s="24"/>
       <c r="G170" s="14"/>
     </row>
-    <row r="171" spans="2:7">
+    <row r="171" spans="2:7" hidden="1">
       <c r="B171" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C171, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G171" s="14"/>
     </row>
-    <row r="172" spans="2:7">
+    <row r="172" spans="2:7" hidden="1">
       <c r="B172" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C172, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G172" s="14"/>
     </row>
-    <row r="173" spans="2:7">
+    <row r="173" spans="2:7" hidden="1">
       <c r="B173" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C173, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G173" s="14"/>
     </row>
-    <row r="174" spans="2:7">
+    <row r="174" spans="2:7" hidden="1">
       <c r="B174" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C174, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G174" s="14"/>
     </row>
-    <row r="175" spans="2:7">
+    <row r="175" spans="2:7" hidden="1">
       <c r="B175" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C175, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G175" s="14"/>
     </row>
-    <row r="176" spans="2:7">
+    <row r="176" spans="2:7" hidden="1">
       <c r="B176" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C176, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G176" s="14"/>
     </row>
-    <row r="177" spans="2:7">
+    <row r="177" spans="2:7" hidden="1">
       <c r="B177" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C177, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G177" s="14"/>
     </row>
-    <row r="178" spans="2:7">
+    <row r="178" spans="2:7" hidden="1">
       <c r="B178" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C178, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G178" s="14"/>
     </row>
-    <row r="179" spans="2:7">
+    <row r="179" spans="2:7" hidden="1">
       <c r="B179" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C179, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G179" s="14"/>
     </row>
-    <row r="180" spans="2:7">
+    <row r="180" spans="2:7" hidden="1">
       <c r="B180" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C180, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G180" s="14"/>
     </row>
-    <row r="181" spans="2:7">
+    <row r="181" spans="2:7" hidden="1">
       <c r="B181" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C181, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G181" s="14"/>
     </row>
-    <row r="182" spans="2:7">
+    <row r="182" spans="2:7" hidden="1">
       <c r="B182" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C182, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G182" s="14"/>
     </row>
-    <row r="183" spans="2:7">
+    <row r="183" spans="2:7" hidden="1">
       <c r="B183" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C183, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G183" s="14"/>
     </row>
-    <row r="184" spans="2:7">
+    <row r="184" spans="2:7" hidden="1">
       <c r="B184" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C184, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G184" s="14"/>
     </row>
-    <row r="185" spans="2:7">
+    <row r="185" spans="2:7" hidden="1">
       <c r="B185" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C185, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G185" s="14"/>
     </row>
-    <row r="186" spans="2:7">
+    <row r="186" spans="2:7" hidden="1">
       <c r="B186" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C186, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G186" s="14"/>
     </row>
-    <row r="187" spans="2:7">
+    <row r="187" spans="2:7" hidden="1">
       <c r="B187" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C187, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G187" s="14"/>
     </row>
-    <row r="188" spans="2:7">
+    <row r="188" spans="2:7" hidden="1">
       <c r="B188" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C188, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G188" s="14"/>
     </row>
-    <row r="189" spans="2:7">
+    <row r="189" spans="2:7" hidden="1">
       <c r="B189" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C189, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G189" s="14"/>
     </row>
-    <row r="190" spans="2:7">
+    <row r="190" spans="2:7" hidden="1">
       <c r="B190" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C190, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G190" s="14"/>
     </row>
-    <row r="191" spans="2:7">
+    <row r="191" spans="2:7" hidden="1">
       <c r="B191" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C191, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G191" s="14"/>
     </row>
-    <row r="192" spans="2:7">
+    <row r="192" spans="2:7" hidden="1">
       <c r="B192" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C192, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G192" s="14"/>
     </row>
-    <row r="193" spans="2:7">
+    <row r="193" spans="2:7" hidden="1">
       <c r="B193" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C193, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G193" s="14"/>
     </row>
-    <row r="194" spans="2:7">
+    <row r="194" spans="2:7" hidden="1">
       <c r="B194" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C194, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G194" s="14"/>
     </row>
-    <row r="195" spans="2:7">
+    <row r="195" spans="2:7" hidden="1">
       <c r="B195" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C195, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G195" s="14"/>
     </row>
-    <row r="196" spans="2:7">
+    <row r="196" spans="2:7" hidden="1">
       <c r="B196" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C196, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G196" s="14"/>
     </row>
-    <row r="197" spans="2:7">
+    <row r="197" spans="2:7" hidden="1">
       <c r="B197" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C197, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G197" s="14"/>
     </row>
-    <row r="198" spans="2:7">
+    <row r="198" spans="2:7" hidden="1">
       <c r="B198" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C198, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G198" s="14"/>
     </row>
-    <row r="199" spans="2:7">
+    <row r="199" spans="2:7" hidden="1">
       <c r="B199" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C199, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G199" s="14"/>
     </row>
-    <row r="200" spans="2:7">
+    <row r="200" spans="2:7" hidden="1">
       <c r="B200" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C200, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G200" s="14"/>
     </row>
-    <row r="201" spans="2:7">
+    <row r="201" spans="2:7" hidden="1">
       <c r="B201" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C201, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G201" s="14"/>
     </row>
-    <row r="202" spans="2:7">
+    <row r="202" spans="2:7" hidden="1">
       <c r="B202" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C202, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G202" s="14"/>
     </row>
-    <row r="203" spans="2:7">
+    <row r="203" spans="2:7" hidden="1">
       <c r="B203" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C203, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G203" s="14"/>
     </row>
-    <row r="204" spans="2:7">
+    <row r="204" spans="2:7" hidden="1">
       <c r="B204" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C204, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G204" s="14"/>
     </row>
-    <row r="205" spans="2:7">
+    <row r="205" spans="2:7" hidden="1">
       <c r="B205" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C205, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G205" s="14"/>
     </row>
-    <row r="206" spans="2:7">
+    <row r="206" spans="2:7" hidden="1">
       <c r="B206" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C206, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G206" s="14"/>
     </row>
-    <row r="207" spans="2:7">
+    <row r="207" spans="2:7" hidden="1">
       <c r="B207" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C207, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G207" s="14"/>
     </row>
-    <row r="208" spans="2:7">
+    <row r="208" spans="2:7" hidden="1">
       <c r="B208" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C208, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G208" s="14"/>
     </row>
-    <row r="209" spans="2:7">
+    <row r="209" spans="2:7" hidden="1">
       <c r="B209" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C209, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G209" s="14"/>
     </row>
-    <row r="210" spans="2:7">
+    <row r="210" spans="2:7" hidden="1">
       <c r="B210" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C210, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G210" s="14"/>
     </row>
-    <row r="211" spans="2:7">
+    <row r="211" spans="2:7" hidden="1">
       <c r="B211" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C211, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G211" s="14"/>
     </row>
-    <row r="212" spans="2:7">
+    <row r="212" spans="2:7" hidden="1">
       <c r="B212" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C212, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G212" s="14"/>
     </row>
-    <row r="213" spans="2:7">
+    <row r="213" spans="2:7" hidden="1">
       <c r="B213" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C213, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G213" s="14"/>
     </row>
-    <row r="214" spans="2:7">
+    <row r="214" spans="2:7" hidden="1">
       <c r="B214" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C214, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G214" s="14"/>
     </row>
-    <row r="215" spans="2:7">
+    <row r="215" spans="2:7" hidden="1">
       <c r="B215" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C215, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G215" s="14"/>
     </row>
-    <row r="216" spans="2:7">
+    <row r="216" spans="2:7" hidden="1">
       <c r="B216" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C216, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G216" s="14"/>
     </row>
-    <row r="217" spans="2:7">
+    <row r="217" spans="2:7" hidden="1">
       <c r="B217" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C217, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G217" s="14"/>
     </row>
-    <row r="218" spans="2:7">
+    <row r="218" spans="2:7" hidden="1">
       <c r="B218" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C218, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G218" s="14"/>
     </row>
-    <row r="219" spans="2:7">
+    <row r="219" spans="2:7" hidden="1">
       <c r="B219" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C219, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G219" s="14"/>
     </row>
-    <row r="220" spans="2:7">
+    <row r="220" spans="2:7" hidden="1">
       <c r="B220" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C220, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G220" s="14"/>
     </row>
-    <row r="221" spans="2:7">
+    <row r="221" spans="2:7" hidden="1">
       <c r="B221" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C221, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G221" s="14"/>
     </row>
-    <row r="222" spans="2:7">
+    <row r="222" spans="2:7" hidden="1">
       <c r="B222" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C222, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G222" s="14"/>
     </row>
-    <row r="223" spans="2:7">
+    <row r="223" spans="2:7" hidden="1">
       <c r="B223" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C223, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G223" s="14"/>
     </row>
-    <row r="224" spans="2:7">
+    <row r="224" spans="2:7" hidden="1">
       <c r="B224" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C224, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G224" s="14"/>
     </row>
-    <row r="225" spans="2:7">
+    <row r="225" spans="2:7" hidden="1">
       <c r="B225" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C225, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G225" s="14"/>
     </row>
-    <row r="226" spans="2:7">
+    <row r="226" spans="2:7" hidden="1">
       <c r="B226" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C226, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G226" s="14"/>
     </row>
-    <row r="227" spans="2:7">
+    <row r="227" spans="2:7" hidden="1">
       <c r="B227" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C227, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G227" s="14"/>
     </row>
-    <row r="228" spans="2:7">
+    <row r="228" spans="2:7" hidden="1">
       <c r="B228" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C228, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G228" s="14"/>
     </row>
-    <row r="229" spans="2:7">
+    <row r="229" spans="2:7" hidden="1">
       <c r="B229" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C229, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G229" s="14"/>
     </row>
-    <row r="230" spans="2:7">
+    <row r="230" spans="2:7" hidden="1">
       <c r="B230" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C230, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G230" s="14"/>
     </row>
-    <row r="231" spans="2:7">
+    <row r="231" spans="2:7" hidden="1">
       <c r="B231" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C231, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G231" s="14"/>
     </row>
-    <row r="232" spans="2:7">
+    <row r="232" spans="2:7" hidden="1">
       <c r="B232" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C232, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G232" s="14"/>
     </row>
-    <row r="233" spans="2:7">
+    <row r="233" spans="2:7" hidden="1">
       <c r="B233" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C233, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G233" s="14"/>
     </row>
-    <row r="234" spans="2:7">
+    <row r="234" spans="2:7" hidden="1">
       <c r="B234" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C234, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G234" s="14"/>
     </row>
-    <row r="235" spans="2:7">
+    <row r="235" spans="2:7" hidden="1">
       <c r="B235" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C235, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G235" s="14"/>
     </row>
-    <row r="236" spans="2:7">
+    <row r="236" spans="2:7" hidden="1">
       <c r="B236" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C236, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G236" s="14"/>
     </row>
-    <row r="237" spans="2:7">
+    <row r="237" spans="2:7" hidden="1">
       <c r="B237" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C237, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G237" s="14"/>
     </row>
-    <row r="238" spans="2:7">
+    <row r="238" spans="2:7" hidden="1">
       <c r="B238" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C238, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G238" s="14"/>
     </row>
-    <row r="239" spans="2:7">
+    <row r="239" spans="2:7" hidden="1">
       <c r="B239" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C239, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G239" s="14"/>
     </row>
-    <row r="240" spans="2:7">
+    <row r="240" spans="2:7" hidden="1">
       <c r="B240" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C240, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G240" s="14"/>
     </row>
-    <row r="241" spans="2:7">
+    <row r="241" spans="2:7" hidden="1">
       <c r="B241" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C241, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G241" s="14"/>
     </row>
-    <row r="242" spans="2:7">
+    <row r="242" spans="2:7" hidden="1">
       <c r="B242" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C242, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G242" s="14"/>
     </row>
-    <row r="243" spans="2:7">
+    <row r="243" spans="2:7" hidden="1">
       <c r="B243" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C243, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G243" s="14"/>
     </row>
-    <row r="244" spans="2:7">
+    <row r="244" spans="2:7" hidden="1">
       <c r="B244" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C244, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G244" s="14"/>
     </row>
-    <row r="245" spans="2:7">
+    <row r="245" spans="2:7" hidden="1">
       <c r="B245" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C245, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G245" s="14"/>
     </row>
-    <row r="246" spans="2:7">
+    <row r="246" spans="2:7" hidden="1">
       <c r="B246" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C246, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G246" s="14"/>
     </row>
-    <row r="247" spans="2:7">
+    <row r="247" spans="2:7" hidden="1">
       <c r="B247" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C247, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G247" s="14"/>
     </row>
-    <row r="248" spans="2:7">
+    <row r="248" spans="2:7" hidden="1">
       <c r="B248" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C248, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G248" s="14"/>
     </row>
-    <row r="249" spans="2:7">
+    <row r="249" spans="2:7" hidden="1">
       <c r="B249" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C249, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G249" s="14"/>
     </row>
-    <row r="250" spans="2:7">
+    <row r="250" spans="2:7" hidden="1">
       <c r="B250" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C250, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G250" s="14"/>
     </row>
-    <row r="251" spans="2:7">
+    <row r="251" spans="2:7" hidden="1">
       <c r="B251" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C251, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G251" s="14"/>
     </row>
-    <row r="252" spans="2:7">
+    <row r="252" spans="2:7" hidden="1">
       <c r="B252" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C252, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G252" s="14"/>
     </row>
-    <row r="253" spans="2:7">
+    <row r="253" spans="2:7" hidden="1">
       <c r="B253" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C253, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G253" s="14"/>
     </row>
-    <row r="254" spans="2:7">
+    <row r="254" spans="2:7" hidden="1">
       <c r="B254" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C254, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G254" s="14"/>
     </row>
-    <row r="255" spans="2:7">
+    <row r="255" spans="2:7" hidden="1">
       <c r="B255" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C255, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G255" s="14"/>
     </row>
-    <row r="256" spans="2:7">
+    <row r="256" spans="2:7" hidden="1">
       <c r="B256" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C256, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G256" s="14"/>
     </row>
-    <row r="257" spans="2:7">
+    <row r="257" spans="2:7" hidden="1">
       <c r="B257" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C257, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G257" s="14"/>
     </row>
-    <row r="258" spans="2:7">
+    <row r="258" spans="2:7" hidden="1">
       <c r="B258" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C258, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G258" s="14"/>
     </row>
-    <row r="259" spans="2:7">
+    <row r="259" spans="2:7" hidden="1">
       <c r="B259" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C259, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G259" s="14"/>
     </row>
-    <row r="260" spans="2:7">
+    <row r="260" spans="2:7" hidden="1">
       <c r="B260" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C260, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G260" s="14"/>
     </row>
-    <row r="261" spans="2:7">
+    <row r="261" spans="2:7" hidden="1">
       <c r="B261" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C261, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G261" s="14"/>
     </row>
-    <row r="262" spans="2:7">
+    <row r="262" spans="2:7" hidden="1">
       <c r="B262" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C262, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G262" s="14"/>
     </row>
-    <row r="263" spans="2:7">
+    <row r="263" spans="2:7" hidden="1">
       <c r="B263" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C263, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G263" s="14"/>
     </row>
-    <row r="264" spans="2:7">
+    <row r="264" spans="2:7" hidden="1">
       <c r="B264" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C264, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G264" s="14"/>
     </row>
-    <row r="265" spans="2:7">
+    <row r="265" spans="2:7" hidden="1">
       <c r="B265" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C265, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G265" s="14"/>
     </row>
-    <row r="266" spans="2:7">
+    <row r="266" spans="2:7" hidden="1">
       <c r="B266" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C266, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G266" s="14"/>
     </row>
-    <row r="267" spans="2:7">
+    <row r="267" spans="2:7" hidden="1">
       <c r="B267" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C267, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G267" s="14"/>
     </row>
-    <row r="268" spans="2:7">
+    <row r="268" spans="2:7" hidden="1">
       <c r="B268" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C268, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G268" s="14"/>
     </row>
-    <row r="269" spans="2:7">
+    <row r="269" spans="2:7" hidden="1">
       <c r="B269" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C269, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G269" s="14"/>
     </row>
-    <row r="270" spans="2:7">
+    <row r="270" spans="2:7" hidden="1">
       <c r="B270" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C270, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G270" s="14"/>
     </row>
-    <row r="271" spans="2:7">
+    <row r="271" spans="2:7" hidden="1">
       <c r="B271" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C271, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G271" s="14"/>
     </row>
-    <row r="272" spans="2:7">
+    <row r="272" spans="2:7" hidden="1">
       <c r="B272" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C272, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G272" s="14"/>
     </row>
-    <row r="273" spans="2:7">
+    <row r="273" spans="2:7" hidden="1">
       <c r="B273" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C273, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G273" s="14"/>
     </row>
-    <row r="274" spans="2:7">
+    <row r="274" spans="2:7" hidden="1">
       <c r="B274" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C274, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G274" s="14"/>
     </row>
-    <row r="275" spans="2:7">
+    <row r="275" spans="2:7" hidden="1">
       <c r="B275" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C275, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G275" s="14"/>
     </row>
-    <row r="276" spans="2:7">
+    <row r="276" spans="2:7" hidden="1">
       <c r="B276" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C276, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G276" s="14"/>
     </row>
-    <row r="277" spans="2:7">
+    <row r="277" spans="2:7" hidden="1">
       <c r="B277" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C277, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G277" s="14"/>
     </row>
-    <row r="278" spans="2:7">
+    <row r="278" spans="2:7" hidden="1">
       <c r="B278" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C278, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G278" s="14"/>
     </row>
-    <row r="279" spans="2:7">
+    <row r="279" spans="2:7" hidden="1">
       <c r="B279" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C279, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G279" s="14"/>
     </row>
-    <row r="280" spans="2:7">
+    <row r="280" spans="2:7" hidden="1">
       <c r="B280" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C280, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G280" s="14"/>
     </row>
-    <row r="281" spans="2:7">
+    <row r="281" spans="2:7" hidden="1">
       <c r="B281" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C281, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G281" s="14"/>
     </row>
-    <row r="282" spans="2:7">
+    <row r="282" spans="2:7" hidden="1">
       <c r="B282" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C282, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G282" s="14"/>
     </row>
-    <row r="283" spans="2:7">
+    <row r="283" spans="2:7" hidden="1">
       <c r="B283" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C283, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G283" s="14"/>
     </row>
-    <row r="284" spans="2:7">
+    <row r="284" spans="2:7" hidden="1">
       <c r="B284" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C284, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G284" s="14"/>
     </row>
-    <row r="285" spans="2:7">
+    <row r="285" spans="2:7" hidden="1">
       <c r="B285" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C285, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G285" s="14"/>
     </row>
-    <row r="286" spans="2:7">
+    <row r="286" spans="2:7" hidden="1">
       <c r="B286" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C286, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G286" s="14"/>
     </row>
-    <row r="287" spans="2:7">
+    <row r="287" spans="2:7" hidden="1">
       <c r="B287" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C287, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G287" s="14"/>
     </row>
-    <row r="288" spans="2:7">
+    <row r="288" spans="2:7" hidden="1">
       <c r="B288" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C288, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G288" s="14"/>
     </row>
-    <row r="289" spans="2:7">
+    <row r="289" spans="2:7" hidden="1">
       <c r="B289" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C289, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G289" s="14"/>
     </row>
-    <row r="290" spans="2:7">
+    <row r="290" spans="2:7" hidden="1">
       <c r="B290" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C290, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G290" s="14"/>
     </row>
-    <row r="291" spans="2:7">
+    <row r="291" spans="2:7" hidden="1">
       <c r="B291" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C291, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G291" s="14"/>
     </row>
-    <row r="292" spans="2:7">
+    <row r="292" spans="2:7" hidden="1">
       <c r="B292" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C292, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G292" s="14"/>
     </row>
-    <row r="293" spans="2:7">
+    <row r="293" spans="2:7" hidden="1">
       <c r="B293" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C293, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G293" s="14"/>
     </row>
-    <row r="294" spans="2:7">
+    <row r="294" spans="2:7" hidden="1">
       <c r="B294" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C294, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G294" s="14"/>
     </row>
-    <row r="295" spans="2:7">
+    <row r="295" spans="2:7" hidden="1">
       <c r="B295" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C295, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G295" s="14"/>
     </row>
-    <row r="296" spans="2:7">
+    <row r="296" spans="2:7" hidden="1">
       <c r="B296" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C296, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G296" s="14"/>
     </row>
-    <row r="297" spans="2:7">
+    <row r="297" spans="2:7" hidden="1">
       <c r="B297" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C297, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" spans="2:7">
+    <row r="298" spans="2:7" hidden="1">
       <c r="B298" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C298, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G298" s="14"/>
     </row>
-    <row r="299" spans="2:7">
+    <row r="299" spans="2:7" hidden="1">
       <c r="B299" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C299, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" spans="2:7">
+    <row r="300" spans="2:7" hidden="1">
       <c r="B300" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C300, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="2:7">
+    <row r="301" spans="2:7" hidden="1">
       <c r="B301" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C301, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="2:7">
+    <row r="302" spans="2:7" hidden="1">
       <c r="B302" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C302, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="2:7">
+    <row r="303" spans="2:7" hidden="1">
       <c r="B303" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C303, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="2:7">
+    <row r="304" spans="2:7" hidden="1">
       <c r="B304" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C304, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="2:7">
+    <row r="305" spans="2:7" hidden="1">
       <c r="B305" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C305, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" spans="2:7">
+    <row r="306" spans="2:7" hidden="1">
       <c r="B306" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C306, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="2:7">
+    <row r="307" spans="2:7" hidden="1">
       <c r="B307" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C307, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" spans="2:7">
+    <row r="308" spans="2:7" hidden="1">
       <c r="B308" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C308, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" spans="2:7">
+    <row r="309" spans="2:7" hidden="1">
       <c r="B309" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C309, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G309" s="14"/>
     </row>
-    <row r="310" spans="2:7">
+    <row r="310" spans="2:7" hidden="1">
       <c r="B310" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C310, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G310" s="14"/>
     </row>
-    <row r="311" spans="2:7">
+    <row r="311" spans="2:7" hidden="1">
       <c r="B311" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C311, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G311" s="14"/>
     </row>
-    <row r="312" spans="2:7">
+    <row r="312" spans="2:7" hidden="1">
       <c r="B312" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C312, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G312" s="14"/>
     </row>
-    <row r="313" spans="2:7">
+    <row r="313" spans="2:7" hidden="1">
       <c r="B313" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C313, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G313" s="14"/>
     </row>
-    <row r="314" spans="2:7">
+    <row r="314" spans="2:7" hidden="1">
       <c r="B314" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C314, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G314" s="14"/>
     </row>
-    <row r="315" spans="2:7">
+    <row r="315" spans="2:7" hidden="1">
       <c r="B315" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C315, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G315" s="14"/>
     </row>
-    <row r="316" spans="2:7">
+    <row r="316" spans="2:7" hidden="1">
       <c r="B316" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C316, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G316" s="14"/>
     </row>
-    <row r="317" spans="2:7">
+    <row r="317" spans="2:7" hidden="1">
       <c r="B317" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C317, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" spans="2:7">
+    <row r="318" spans="2:7" hidden="1">
       <c r="B318" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C318, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" spans="2:7">
+    <row r="319" spans="2:7" hidden="1">
       <c r="B319" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C319, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G319" s="14"/>
     </row>
-    <row r="320" spans="2:7">
+    <row r="320" spans="2:7" hidden="1">
       <c r="B320" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C320, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G320" s="14"/>
     </row>
-    <row r="321" spans="2:7">
+    <row r="321" spans="2:7" hidden="1">
       <c r="B321" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C321, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G321" s="14"/>
     </row>
-    <row r="322" spans="2:7">
+    <row r="322" spans="2:7" hidden="1">
       <c r="B322" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C322, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G322" s="14"/>
     </row>
-    <row r="323" spans="2:7">
+    <row r="323" spans="2:7" hidden="1">
       <c r="B323" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C323, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G323" s="14"/>
     </row>
-    <row r="324" spans="2:7">
+    <row r="324" spans="2:7" hidden="1">
       <c r="B324" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C324, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G324" s="14"/>
     </row>
-    <row r="325" spans="2:7">
+    <row r="325" spans="2:7" hidden="1">
       <c r="B325" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C325, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G325" s="14"/>
     </row>
-    <row r="326" spans="2:7">
+    <row r="326" spans="2:7" hidden="1">
       <c r="B326" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C326, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G326" s="14"/>
     </row>
-    <row r="327" spans="2:7">
+    <row r="327" spans="2:7" hidden="1">
       <c r="B327" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C327, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>

--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DE201DE-57E4-4570-B0A7-FE00438C8AD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65211D99-8484-4174-A8F8-F183DE21214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4040,7 +4040,7 @@
         <v>10</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E73">
         <v>66</v>
@@ -4243,7 +4243,7 @@
         <v>10</v>
       </c>
       <c r="D80">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E80">
         <v>59</v>
@@ -4359,7 +4359,7 @@
         <v>10</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="E84">
         <v>48</v>
@@ -4475,7 +4475,7 @@
         <v>14</v>
       </c>
       <c r="D88">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E88">
         <v>50</v>

--- a/AZUVER_dashboard_data_2.xlsx
+++ b/AZUVER_dashboard_data_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\srest\PycharmProjects\Dashboard_Informacional2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65211D99-8484-4174-A8F8-F183DE21214C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A0BD1F-5504-44F6-943A-19CCD398CB60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1482" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2141" uniqueCount="423">
   <si>
     <t>data</t>
   </si>
@@ -1071,6 +1071,276 @@
   </si>
   <si>
     <t>Respeito/Temor Baixo (20–39)</t>
+  </si>
+  <si>
+    <t>Surto de Cólera e Crise Humanitária</t>
+  </si>
+  <si>
+    <t>Surto de Cólera e Crise Humanitária (Bocaiúva do Sul / Registro)</t>
+  </si>
+  <si>
+    <t>OCOR X + 1</t>
+  </si>
+  <si>
+    <t>Ações de proteção, apoio à IC e combate a boatos reforçam confiança e competência.</t>
+  </si>
+  <si>
+    <t>Ajuda humanitária direta e apoio à IC geram afinidade pragmática.</t>
+  </si>
+  <si>
+    <t>Apoio à IC, neutralização de boatos e caráter humanitário facilitam trabalho e geram empatia.</t>
+  </si>
+  <si>
+    <t>Reconhecimento pragmático da gestão de crise e busca por legitimidade.</t>
+  </si>
+  <si>
+    <t>Esforços para estabilizar a crise e evitar transbordamento.</t>
+  </si>
+  <si>
+    <t>Ações que promovem estabilidade e protegem IC são bem-vindas.</t>
+  </si>
+  <si>
+    <t>Presença militar gera desconfiança, mas capacidade de ajuda é reconhecida.</t>
+  </si>
+  <si>
+    <t>Ações de AZUL dificultam operações do PCS, gerando hostilidade e temor.</t>
+  </si>
+  <si>
+    <t>Ajuda humanitária pode gerar leve afinidade, mas presença militar é ponto de cautela.</t>
+  </si>
+  <si>
+    <t>Ações que promovem estabilidade e acesso a serviços geram afinidade.</t>
+  </si>
+  <si>
+    <t>Ações humanitárias e de estabilização se alinham com o mandato do CSOI.</t>
+  </si>
+  <si>
+    <t>Estabilidade e gestão de crise contribuem para um ambiente mais favorável.</t>
+  </si>
+  <si>
+    <t>Ações de proteção, controle epidemiológico e capacidade logística reforçam confiança.</t>
+  </si>
+  <si>
+    <t>Coordenação e eficiência na ajuda humanitária geram empatia e disposição para colaborar.</t>
+  </si>
+  <si>
+    <t>Campanha psicológica contra "oportunismo adversário" (AZUL) pode gerar desconfiança na liderança de AZUL.</t>
+  </si>
+  <si>
+    <t>Ataque político pode gerar cautela, mas eficiência na gestão de crise é reconhecida.</t>
+  </si>
+  <si>
+    <t>Eficiência na gestão de crise e coordenação geram afinidade e respeito.</t>
+  </si>
+  <si>
+    <t>Ações que beneficiam as comunidades e demonstram organização geram afinidade.</t>
+  </si>
+  <si>
+    <t>Operações Cibernéticas e Guerra Eletrônica</t>
+  </si>
+  <si>
+    <t>Reforço da segurança digital interna contribui para percepção de proteção e competência.</t>
+  </si>
+  <si>
+    <t>Percepção indireta de competência em segurança, caso evite incidentes públicos.</t>
+  </si>
+  <si>
+    <t>Programa "Ciberpatriotas" e "ECO DIGITAL" geram patriotismo, confiança e respeito pela capacidade de VERMELHO.</t>
+  </si>
+  <si>
+    <t>Mobilização civil e demonstração de poder geram hostilidade, mas também temor/respeito pela capacidade de VERMELHO.</t>
+  </si>
+  <si>
+    <t>Preocupação com diluição das fronteiras da guerra e aumento da tensão regional, mas reconhecimento da capacidade.</t>
+  </si>
+  <si>
+    <t>Preocupação com mobilização civil em conflito e aumento da tensão regional, mas reconhecimento da capacidade.</t>
+  </si>
+  <si>
+    <t>Preocupação com segurança de civis e escalada do conflito, mas reconhecimento da capacidade tecnológica.</t>
+  </si>
+  <si>
+    <t>Demonstração de força e organização pode gerar alinhamento pragmático e respeito pela capacidade.</t>
+  </si>
+  <si>
+    <t>Aumento do controle e vigilância de VERMELHO é desfavorável, mas há temor/respeito pela capacidade cibernética.</t>
+  </si>
+  <si>
+    <t>Sentimento de pertencimento e orgulho nacional pela capacidade tecnológica e militar.</t>
+  </si>
+  <si>
+    <t>Leve aumento de afinidade devido à demonstração de força nacional, e reconhecimento da capacidade.</t>
+  </si>
+  <si>
+    <t>Preocupação com mobilização civil em guerra cibernética e escalada de tensão, mas reconhecimento da capacidade.</t>
+  </si>
+  <si>
+    <t>Aumento da tensão regional pode gerar cautela, mas reconhecimento da capacidade tecnológica.</t>
+  </si>
+  <si>
+    <t>Operações Navais e Aeroespaciais (FENO / Salvador / São Francisco do Sul)</t>
+  </si>
+  <si>
+    <t>Reforço da proteção e soberania aumenta a identificação e confiança.</t>
+  </si>
+  <si>
+    <t>Disrupção econômica e instabilidade percebida deterioram afinidade e respeito.</t>
+  </si>
+  <si>
+    <t>Disrupção econômica e instabilidade percebida afetam investimentos.</t>
+  </si>
+  <si>
+    <t>Aumento da segurança pode ser bem-vindo, mas militarização gera cautela.</t>
+  </si>
+  <si>
+    <t>Aumento da presença militar de AZUL é uma ameaça à autonomia do MPL.</t>
+  </si>
+  <si>
+    <t>Aumento do controle e vigilância de AZUL é desfavorável às operações do PCS.</t>
+  </si>
+  <si>
+    <t>Preocupação com a Seg Marítima e dano ambiental de AZUL</t>
+  </si>
+  <si>
+    <t>Reforço da ordem e capacidade estatal.</t>
+  </si>
+  <si>
+    <t>Segurança é boa, mas presença militar pode ser complexa.</t>
+  </si>
+  <si>
+    <t>Aumento da segurança e controle.</t>
+  </si>
+  <si>
+    <t>Desconfiança da presença militar, mas respeito pela capacidade.</t>
+  </si>
+  <si>
+    <t>O efeito prejudica seus interesses vitais devido às falhas logísticas.</t>
+  </si>
+  <si>
+    <t>Campanhas de descredibilização minam a confiança na liderança de AZUL.</t>
+  </si>
+  <si>
+    <t>Ações de VERMELHO fornecem base para críticas contra AZUL.</t>
+  </si>
+  <si>
+    <t>Denúncias ambientais geram forte desaprovação e desconfiança em AZUL.</t>
+  </si>
+  <si>
+    <t>Leve aumento da afinidade pela proteção civil, mas cautela com a escalada</t>
+  </si>
+  <si>
+    <t>Preocupação com a segurança marítima e danos ambientais de AZUL afeta interesses econômicos.</t>
+  </si>
+  <si>
+    <t>Preocupação com a segurança marítima e falhas logísticas de AZUL afeta interesses empresariais.</t>
+  </si>
+  <si>
+    <t>Ações de VERMELHO se alinham com a postura anti-AZUL do MPL.</t>
+  </si>
+  <si>
+    <t>Percepção de fraqueza de AZUL cria oportunidades para o PCS.</t>
+  </si>
+  <si>
+    <t>A narrativa contra azul foi aceita</t>
+  </si>
+  <si>
+    <t>Movimento Peruíbe Livre (MPL)</t>
+  </si>
+  <si>
+    <t>Classificação como ameaça e ações de combate geram hostilidade e temor/respeito pela capacidade de AZUL.</t>
+  </si>
+  <si>
+    <t>Ações de proteção contra ataques cibernéticos reforçam confiança e capacidade de AZUL.</t>
+  </si>
+  <si>
+    <t>Reconhecimento da necessidade de ações de segurança e proteção contra ameaças.</t>
+  </si>
+  <si>
+    <t>Campanha psicológica para dividir o MPL gera forte hostilidade, mas demonstra capacidade de Op Psc.</t>
+  </si>
+  <si>
+    <t>Percebido como apoio a elemento hostil, gerando hostilidade.</t>
+  </si>
+  <si>
+    <t>Percebido como tática desestabilizadora, diminuindo afinidade.</t>
+  </si>
+  <si>
+    <t>Reação Internacional e Imagem Externa</t>
+  </si>
+  <si>
+    <t>Demonstração de consciência dos princípios de proteção e temporariedade.</t>
+  </si>
+  <si>
+    <t>Mensagem que aborda diretamente suas preocupações com estabilidade e duração da presença militar.</t>
+  </si>
+  <si>
+    <t>Sutil tranquilidade sobre a intenção de não prolongar a desestabilização.</t>
+  </si>
+  <si>
+    <t>Reasseguramento sobre o foco humanitário e os limites da ação militar.</t>
+  </si>
+  <si>
+    <t>Engajamento ativo e obtenção de apoio diplomático constroem forte confiança.</t>
+  </si>
+  <si>
+    <t>Engajamento diplomático direto e declarações favoráveis constroem forte afinidade.</t>
+  </si>
+  <si>
+    <t>Esforços diplomáticos ativos e declarações favoráveis constroem confiança.</t>
+  </si>
+  <si>
+    <t>Engajamento ativo e declarações favoráveis constroem confiança e cooperação.</t>
+  </si>
+  <si>
+    <t>OUTRAS AÇÕES INFORMACIONAIS</t>
+  </si>
+  <si>
+    <t>Horror e indignação por ataques a civis, gerando medo e repulsa.</t>
+  </si>
+  <si>
+    <t>Forte condenação por danos civis e violações do DIH, minando credibilidade.</t>
+  </si>
+  <si>
+    <t>Forte condenação por violações graves do DIH e princípios de proteção civil.</t>
+  </si>
+  <si>
+    <t>Forte desaprovação e preocupação com a escalada e a instabilidade regional.</t>
+  </si>
+  <si>
+    <t>Preocupação com a imprevisibilidade, risco e impacto negativo nos interesses econômicos.</t>
+  </si>
+  <si>
+    <t>Choque moral, preocupação com a imagem internacional e questionamento da ética das ações.</t>
+  </si>
+  <si>
+    <t>FALSE FLAG</t>
+  </si>
+  <si>
+    <t>Maioria abraça a Narrativa 1 (ataque sofrido), gerando patriotismo e apoio à autodefesa.</t>
+  </si>
+  <si>
+    <t>A suspeita da Narrativa 2 (falsa bandeira) destrói a credibilidade e legitimidade diplomática de AZUL.</t>
+  </si>
+  <si>
+    <t>A Narrativa 2 (falsa bandeira) é a pior hipótese; AZUL é visto como agente do caos logístico (R-), mas temível (C+).</t>
+  </si>
+  <si>
+    <t>A Narrativa 2 (falsa bandeira) culpa AZUL por criar deliberadamente a crise humanitária (vítimas/poluição).</t>
+  </si>
+  <si>
+    <t>A maioria da população acredita na Narrativa 1, vendo VERMELHO como o agressor.</t>
+  </si>
+  <si>
+    <t>A Narrativa 1 (ataque a navio civil) é uma grave violação, prejudicando VERMELHO.</t>
+  </si>
+  <si>
+    <t>Visto como suspeito (Narrativa 1) ou como vítima de uma armação (Narrativa 2). Percepção negativa, mas passiva.</t>
+  </si>
+  <si>
+    <t>Visto como o agressor (Narrativa 1) até que se prove o contrário, mas a culpa de AZ</t>
+  </si>
+  <si>
+    <t>Atualização (29 Out 25)</t>
   </si>
 </sst>
 </file>
@@ -1080,7 +1350,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1121,6 +1391,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Aptos"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1275,7 +1551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1331,14 +1607,18 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="24">
-    <dxf>
-      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1590,6 +1870,9 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1646,7 +1929,7 @@
     <tableColumn id="4" xr3:uid="{7F40A552-08DB-47E5-B8C9-D234A3618AC7}" name="R"/>
     <tableColumn id="5" xr3:uid="{6D524766-1B99-4A6B-BBB8-2C07618F12BD}" name="C"/>
     <tableColumn id="6" xr3:uid="{975C8660-93D0-4033-AA43-8AA370C045E9}" name="class_R"/>
-    <tableColumn id="7" xr3:uid="{B6DA6EC3-D88E-4812-89CE-2FD27455D195}" name="class_C" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{B6DA6EC3-D88E-4812-89CE-2FD27455D195}" name="class_C" dataDxfId="22"/>
     <tableColumn id="8" xr3:uid="{2DC65DDE-891F-45C1-A625-9C1EA845FBAC}" name="fonte_regra"/>
     <tableColumn id="9" xr3:uid="{ED276677-25B8-4FBE-A338-C1FDCB7FC603}" name="obs"/>
   </tableColumns>
@@ -1655,59 +1938,48 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A3AD564-B18D-4439-A198-8AF944A99772}" name="tblActors" displayName="tblActors" ref="A1:D17" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" totalsRowBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5A3AD564-B18D-4439-A198-8AF944A99772}" name="tblActors" displayName="tblActors" ref="A1:D17" totalsRowShown="0" headerRowDxfId="21" headerRowBorderDxfId="20" tableBorderDxfId="19" totalsRowBorderDxfId="18">
   <autoFilter ref="A1:D17" xr:uid="{5A3AD564-B18D-4439-A198-8AF944A99772}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{3122FF93-D7C9-47C4-AAE7-E5CBE0FA3A54}" name="actor_id" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{2220D84D-1A4B-4A12-888A-7592053EDECC}" name="nome" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{7244E1B6-C06A-46BA-A29E-7198716E593E}" name="tipo" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{10B1B0CA-D667-4698-9FAC-A50EC4C9BE0A}" name="cluster_opcional" dataDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{3122FF93-D7C9-47C4-AAE7-E5CBE0FA3A54}" name="actor_id" dataDxfId="17"/>
+    <tableColumn id="2" xr3:uid="{2220D84D-1A4B-4A12-888A-7592053EDECC}" name="nome" dataDxfId="16"/>
+    <tableColumn id="3" xr3:uid="{7244E1B6-C06A-46BA-A29E-7198716E593E}" name="tipo" dataDxfId="15"/>
+    <tableColumn id="4" xr3:uid="{10B1B0CA-D667-4698-9FAC-A50EC4C9BE0A}" name="cluster_opcional" dataDxfId="14"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EE140BC-D0AD-4653-A557-FEB72E7706BB}" name="Tabela3" displayName="Tabela3" ref="A1:H279" totalsRowShown="0" headerRowDxfId="14" headerRowBorderDxfId="13" tableBorderDxfId="12">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8EE140BC-D0AD-4653-A557-FEB72E7706BB}" name="Tabela3" displayName="Tabela3" ref="A1:H279" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11">
   <autoFilter ref="A1:H279" xr:uid="{8EE140BC-D0AD-4653-A557-FEB72E7706BB}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{A64D0630-7FB4-4675-AF15-DFA9CC4C3218}" name="event_id"/>
     <tableColumn id="2" xr3:uid="{ABB220E9-794F-4B06-80FB-EA100148E885}" name="data"/>
-    <tableColumn id="3" xr3:uid="{DEFA5E68-941A-4720-891C-051748ACEEE4}" name="titulo" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{2AA18C9F-BAB7-429C-BD76-624D918E02A6}" name="descricao" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{ACAD5301-D426-46EE-A7F5-46CA1210DCDF}" name="tipo" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{C20CACB4-38DD-423C-80F3-2EAB1574530A}" name="tags" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{46484C08-2E71-4200-A22E-BF604C745824}" name="fonte" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{9B6E38A2-36A7-42AA-A46E-F35C16B84F1E}" name="responsabilidade" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{DEFA5E68-941A-4720-891C-051748ACEEE4}" name="titulo" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{2AA18C9F-BAB7-429C-BD76-624D918E02A6}" name="descricao" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{ACAD5301-D426-46EE-A7F5-46CA1210DCDF}" name="tipo" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{C20CACB4-38DD-423C-80F3-2EAB1574530A}" name="tags" dataDxfId="7"/>
+    <tableColumn id="7" xr3:uid="{46484C08-2E71-4200-A22E-BF604C745824}" name="fonte" dataDxfId="6"/>
+    <tableColumn id="8" xr3:uid="{9B6E38A2-36A7-42AA-A46E-F35C16B84F1E}" name="responsabilidade" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K327" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="4" tableBorderDxfId="3">
-  <autoFilter ref="A1:K327" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="ATO006"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="VERMELHO"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}" name="Tabela2" displayName="Tabela2" ref="A1:K327" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
+  <autoFilter ref="A1:K327" xr:uid="{8F935928-F61E-454D-9EE9-3D2DFF7048F4}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{BAF761B8-D6AF-48D3-A1F5-3D35088A4234}" name="event_id"/>
-    <tableColumn id="2" xr3:uid="{78C225EA-4EED-44B0-BBCE-FD76B432B72B}" name="actor_id" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{78C225EA-4EED-44B0-BBCE-FD76B432B72B}" name="actor_id" dataDxfId="1">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(C2, tblActors[nome], tblActors[actor_id], ""), "")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{37AE2979-DF01-47CD-BEA5-BA034C5B3757}" name="actor_name"/>
     <tableColumn id="4" xr3:uid="{7BDACF9C-965E-4CCF-94CF-242CB57A4AC1}" name="partido"/>
     <tableColumn id="5" xr3:uid="{6A802EC2-6140-4C9F-9D92-0F2B0C6B0D2F}" name="delta_R"/>
     <tableColumn id="6" xr3:uid="{5830257E-D8FA-438E-9298-17ED813D6C77}" name="delta_C"/>
-    <tableColumn id="7" xr3:uid="{ED6BE6E1-B0BE-4C05-8C17-6A8218AD71A0}" name="racional" dataDxfId="1"/>
+    <tableColumn id="7" xr3:uid="{ED6BE6E1-B0BE-4C05-8C17-6A8218AD71A0}" name="racional" dataDxfId="0"/>
     <tableColumn id="8" xr3:uid="{481A5440-CA6F-4A3B-984A-1D2FFA263532}" name="atraso_dias"/>
     <tableColumn id="9" xr3:uid="{DD506A33-5271-4DFF-AAA8-7F12E055CCD0}" name="delta_opiniao_direta"/>
     <tableColumn id="10" xr3:uid="{9B94DE7A-D5B7-427A-A880-C7C51E771C9F}" name="delta_midia"/>
@@ -2002,7 +2274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K134"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -4839,6 +5111,934 @@
       </c>
       <c r="I100" t="s">
         <v>286</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B103" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" t="s">
+        <v>10</v>
+      </c>
+      <c r="D103">
+        <v>15</v>
+      </c>
+      <c r="E103">
+        <v>73</v>
+      </c>
+      <c r="F103" t="s">
+        <v>327</v>
+      </c>
+      <c r="G103" t="s">
+        <v>323</v>
+      </c>
+      <c r="H103" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" t="s">
+        <v>10</v>
+      </c>
+      <c r="D104">
+        <v>39</v>
+      </c>
+      <c r="E104">
+        <v>72</v>
+      </c>
+      <c r="F104" t="s">
+        <v>325</v>
+      </c>
+      <c r="G104" t="s">
+        <v>323</v>
+      </c>
+      <c r="H104" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>10</v>
+      </c>
+      <c r="D105">
+        <v>26</v>
+      </c>
+      <c r="E105">
+        <v>63</v>
+      </c>
+      <c r="F105" t="s">
+        <v>322</v>
+      </c>
+      <c r="G105" t="s">
+        <v>323</v>
+      </c>
+      <c r="H105" t="s">
+        <v>12</v>
+      </c>
+      <c r="I105" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B106" t="s">
+        <v>38</v>
+      </c>
+      <c r="C106" t="s">
+        <v>10</v>
+      </c>
+      <c r="D106">
+        <v>51</v>
+      </c>
+      <c r="E106">
+        <v>52</v>
+      </c>
+      <c r="F106" t="s">
+        <v>324</v>
+      </c>
+      <c r="G106" t="s">
+        <v>326</v>
+      </c>
+      <c r="H106" t="s">
+        <v>12</v>
+      </c>
+      <c r="I106" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B107" t="s">
+        <v>39</v>
+      </c>
+      <c r="C107" t="s">
+        <v>10</v>
+      </c>
+      <c r="D107">
+        <v>15</v>
+      </c>
+      <c r="E107">
+        <v>74</v>
+      </c>
+      <c r="F107" t="s">
+        <v>327</v>
+      </c>
+      <c r="G107" t="s">
+        <v>323</v>
+      </c>
+      <c r="H107" t="s">
+        <v>12</v>
+      </c>
+      <c r="I107" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B108" t="s">
+        <v>40</v>
+      </c>
+      <c r="C108" t="s">
+        <v>10</v>
+      </c>
+      <c r="D108">
+        <v>100</v>
+      </c>
+      <c r="E108">
+        <v>100</v>
+      </c>
+      <c r="F108" t="s">
+        <v>328</v>
+      </c>
+      <c r="G108" t="s">
+        <v>329</v>
+      </c>
+      <c r="H108" t="s">
+        <v>12</v>
+      </c>
+      <c r="I108" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B109" t="s">
+        <v>41</v>
+      </c>
+      <c r="C109" t="s">
+        <v>10</v>
+      </c>
+      <c r="D109">
+        <v>51</v>
+      </c>
+      <c r="E109">
+        <v>66</v>
+      </c>
+      <c r="F109" t="s">
+        <v>324</v>
+      </c>
+      <c r="G109" t="s">
+        <v>323</v>
+      </c>
+      <c r="H109" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B110" t="s">
+        <v>42</v>
+      </c>
+      <c r="C110" t="s">
+        <v>10</v>
+      </c>
+      <c r="D110">
+        <v>32</v>
+      </c>
+      <c r="E110">
+        <v>55</v>
+      </c>
+      <c r="F110" t="s">
+        <v>322</v>
+      </c>
+      <c r="G110" t="s">
+        <v>326</v>
+      </c>
+      <c r="H110" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" t="s">
+        <v>10</v>
+      </c>
+      <c r="D111">
+        <v>41</v>
+      </c>
+      <c r="E111">
+        <v>68</v>
+      </c>
+      <c r="F111" t="s">
+        <v>325</v>
+      </c>
+      <c r="G111" t="s">
+        <v>323</v>
+      </c>
+      <c r="H111" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B112" t="s">
+        <v>44</v>
+      </c>
+      <c r="C112" t="s">
+        <v>10</v>
+      </c>
+      <c r="D112">
+        <v>41</v>
+      </c>
+      <c r="E112">
+        <v>68</v>
+      </c>
+      <c r="F112" t="s">
+        <v>325</v>
+      </c>
+      <c r="G112" t="s">
+        <v>323</v>
+      </c>
+      <c r="H112" t="s">
+        <v>12</v>
+      </c>
+      <c r="I112" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B113" t="s">
+        <v>45</v>
+      </c>
+      <c r="C113" t="s">
+        <v>10</v>
+      </c>
+      <c r="D113">
+        <v>70</v>
+      </c>
+      <c r="E113">
+        <v>75</v>
+      </c>
+      <c r="F113" t="s">
+        <v>331</v>
+      </c>
+      <c r="G113" t="s">
+        <v>323</v>
+      </c>
+      <c r="H113" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" t="s">
+        <v>10</v>
+      </c>
+      <c r="D114">
+        <v>15</v>
+      </c>
+      <c r="E114">
+        <v>69</v>
+      </c>
+      <c r="F114" t="s">
+        <v>327</v>
+      </c>
+      <c r="G114" t="s">
+        <v>323</v>
+      </c>
+      <c r="H114" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B115" t="s">
+        <v>47</v>
+      </c>
+      <c r="C115" t="s">
+        <v>10</v>
+      </c>
+      <c r="D115">
+        <v>57</v>
+      </c>
+      <c r="E115">
+        <v>54</v>
+      </c>
+      <c r="F115" t="s">
+        <v>324</v>
+      </c>
+      <c r="G115" t="s">
+        <v>326</v>
+      </c>
+      <c r="H115" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C116" t="s">
+        <v>10</v>
+      </c>
+      <c r="D116">
+        <v>49</v>
+      </c>
+      <c r="E116">
+        <v>77</v>
+      </c>
+      <c r="F116" t="s">
+        <v>325</v>
+      </c>
+      <c r="G116" t="s">
+        <v>323</v>
+      </c>
+      <c r="H116" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B117" t="s">
+        <v>49</v>
+      </c>
+      <c r="C117" t="s">
+        <v>10</v>
+      </c>
+      <c r="D117">
+        <v>59</v>
+      </c>
+      <c r="E117">
+        <v>80</v>
+      </c>
+      <c r="F117" t="s">
+        <v>324</v>
+      </c>
+      <c r="G117" t="s">
+        <v>329</v>
+      </c>
+      <c r="H117" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B118" t="s">
+        <v>71</v>
+      </c>
+      <c r="C118" t="s">
+        <v>10</v>
+      </c>
+      <c r="D118">
+        <v>15</v>
+      </c>
+      <c r="E118">
+        <v>58</v>
+      </c>
+      <c r="F118" t="s">
+        <v>327</v>
+      </c>
+      <c r="G118" t="s">
+        <v>326</v>
+      </c>
+      <c r="H118" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s">
+        <v>14</v>
+      </c>
+      <c r="D119">
+        <v>81</v>
+      </c>
+      <c r="E119">
+        <v>77</v>
+      </c>
+      <c r="F119" t="s">
+        <v>328</v>
+      </c>
+      <c r="G119" t="s">
+        <v>323</v>
+      </c>
+      <c r="H119" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B120" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" t="s">
+        <v>14</v>
+      </c>
+      <c r="D120">
+        <v>61</v>
+      </c>
+      <c r="E120">
+        <v>73</v>
+      </c>
+      <c r="F120" t="s">
+        <v>330</v>
+      </c>
+      <c r="G120" t="s">
+        <v>323</v>
+      </c>
+      <c r="H120" t="s">
+        <v>12</v>
+      </c>
+      <c r="I120" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B121" t="s">
+        <v>20</v>
+      </c>
+      <c r="C121" t="s">
+        <v>14</v>
+      </c>
+      <c r="D121">
+        <v>73</v>
+      </c>
+      <c r="E121">
+        <v>73</v>
+      </c>
+      <c r="F121" t="s">
+        <v>331</v>
+      </c>
+      <c r="G121" t="s">
+        <v>323</v>
+      </c>
+      <c r="H121" t="s">
+        <v>12</v>
+      </c>
+      <c r="I121" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9">
+      <c r="A122" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B122" t="s">
+        <v>38</v>
+      </c>
+      <c r="C122" t="s">
+        <v>14</v>
+      </c>
+      <c r="D122">
+        <v>20</v>
+      </c>
+      <c r="E122">
+        <v>54</v>
+      </c>
+      <c r="F122" t="s">
+        <v>322</v>
+      </c>
+      <c r="G122" t="s">
+        <v>326</v>
+      </c>
+      <c r="H122" t="s">
+        <v>12</v>
+      </c>
+      <c r="I122" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9">
+      <c r="A123" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B123" t="s">
+        <v>39</v>
+      </c>
+      <c r="C123" t="s">
+        <v>14</v>
+      </c>
+      <c r="D123">
+        <v>35</v>
+      </c>
+      <c r="E123">
+        <v>71</v>
+      </c>
+      <c r="F123" t="s">
+        <v>325</v>
+      </c>
+      <c r="G123" t="s">
+        <v>323</v>
+      </c>
+      <c r="H123" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9">
+      <c r="A124" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B124" t="s">
+        <v>40</v>
+      </c>
+      <c r="C124" t="s">
+        <v>14</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>43</v>
+      </c>
+      <c r="F124" t="s">
+        <v>327</v>
+      </c>
+      <c r="G124" t="s">
+        <v>326</v>
+      </c>
+      <c r="H124" t="s">
+        <v>12</v>
+      </c>
+      <c r="I124" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9">
+      <c r="A125" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B125" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" t="s">
+        <v>14</v>
+      </c>
+      <c r="D125">
+        <v>23</v>
+      </c>
+      <c r="E125">
+        <v>63</v>
+      </c>
+      <c r="F125" t="s">
+        <v>322</v>
+      </c>
+      <c r="G125" t="s">
+        <v>323</v>
+      </c>
+      <c r="H125" t="s">
+        <v>12</v>
+      </c>
+      <c r="I125" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9">
+      <c r="A126" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B126" t="s">
+        <v>42</v>
+      </c>
+      <c r="C126" t="s">
+        <v>14</v>
+      </c>
+      <c r="D126">
+        <v>58</v>
+      </c>
+      <c r="E126">
+        <v>54</v>
+      </c>
+      <c r="F126" t="s">
+        <v>324</v>
+      </c>
+      <c r="G126" t="s">
+        <v>326</v>
+      </c>
+      <c r="H126" t="s">
+        <v>12</v>
+      </c>
+      <c r="I126" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9">
+      <c r="A127" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B127" t="s">
+        <v>43</v>
+      </c>
+      <c r="C127" t="s">
+        <v>14</v>
+      </c>
+      <c r="D127">
+        <v>46</v>
+      </c>
+      <c r="E127">
+        <v>72</v>
+      </c>
+      <c r="F127" t="s">
+        <v>325</v>
+      </c>
+      <c r="G127" t="s">
+        <v>323</v>
+      </c>
+      <c r="H127" t="s">
+        <v>12</v>
+      </c>
+      <c r="I127" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9">
+      <c r="A128" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B128" t="s">
+        <v>44</v>
+      </c>
+      <c r="C128" t="s">
+        <v>14</v>
+      </c>
+      <c r="D128">
+        <v>47</v>
+      </c>
+      <c r="E128">
+        <v>72</v>
+      </c>
+      <c r="F128" t="s">
+        <v>325</v>
+      </c>
+      <c r="G128" t="s">
+        <v>323</v>
+      </c>
+      <c r="H128" t="s">
+        <v>12</v>
+      </c>
+      <c r="I128" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9">
+      <c r="A129" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B129" t="s">
+        <v>45</v>
+      </c>
+      <c r="C129" t="s">
+        <v>14</v>
+      </c>
+      <c r="D129">
+        <v>34</v>
+      </c>
+      <c r="E129">
+        <v>52</v>
+      </c>
+      <c r="F129" t="s">
+        <v>322</v>
+      </c>
+      <c r="G129" t="s">
+        <v>326</v>
+      </c>
+      <c r="H129" t="s">
+        <v>12</v>
+      </c>
+      <c r="I129" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9">
+      <c r="A130" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B130" t="s">
+        <v>46</v>
+      </c>
+      <c r="C130" t="s">
+        <v>14</v>
+      </c>
+      <c r="D130">
+        <v>100</v>
+      </c>
+      <c r="E130">
+        <v>79</v>
+      </c>
+      <c r="F130" t="s">
+        <v>328</v>
+      </c>
+      <c r="G130" t="s">
+        <v>323</v>
+      </c>
+      <c r="H130" t="s">
+        <v>12</v>
+      </c>
+      <c r="I130" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9">
+      <c r="A131" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B131" t="s">
+        <v>47</v>
+      </c>
+      <c r="C131" t="s">
+        <v>14</v>
+      </c>
+      <c r="D131">
+        <v>49</v>
+      </c>
+      <c r="E131">
+        <v>55</v>
+      </c>
+      <c r="F131" t="s">
+        <v>325</v>
+      </c>
+      <c r="G131" t="s">
+        <v>326</v>
+      </c>
+      <c r="H131" t="s">
+        <v>12</v>
+      </c>
+      <c r="I131" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9">
+      <c r="A132" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B132" t="s">
+        <v>48</v>
+      </c>
+      <c r="C132" t="s">
+        <v>14</v>
+      </c>
+      <c r="D132">
+        <v>50</v>
+      </c>
+      <c r="E132">
+        <v>73</v>
+      </c>
+      <c r="F132" t="s">
+        <v>324</v>
+      </c>
+      <c r="G132" t="s">
+        <v>323</v>
+      </c>
+      <c r="H132" t="s">
+        <v>12</v>
+      </c>
+      <c r="I132" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9">
+      <c r="A133" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B133" t="s">
+        <v>49</v>
+      </c>
+      <c r="C133" t="s">
+        <v>14</v>
+      </c>
+      <c r="D133">
+        <v>94</v>
+      </c>
+      <c r="E133">
+        <v>94</v>
+      </c>
+      <c r="F133" t="s">
+        <v>328</v>
+      </c>
+      <c r="G133" t="s">
+        <v>329</v>
+      </c>
+      <c r="H133" t="s">
+        <v>12</v>
+      </c>
+      <c r="I133" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9">
+      <c r="A134" s="1">
+        <v>45959</v>
+      </c>
+      <c r="B134" t="s">
+        <v>71</v>
+      </c>
+      <c r="C134" t="s">
+        <v>14</v>
+      </c>
+      <c r="D134">
+        <v>75</v>
+      </c>
+      <c r="E134">
+        <v>77</v>
+      </c>
+      <c r="F134" t="s">
+        <v>331</v>
+      </c>
+      <c r="G134" t="s">
+        <v>323</v>
+      </c>
+      <c r="H134" t="s">
+        <v>12</v>
+      </c>
+      <c r="I134" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -5478,97 +6678,214 @@
         <v>261</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="30">
       <c r="A14" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="B14" s="22">
+        <v>45959</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="14" t="s">
+        <v>295</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="60">
       <c r="A15" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="B15" s="22">
+        <v>45959</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>354</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="F15" s="14" t="s">
+        <v>306</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="60">
       <c r="A16" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="17" spans="1:1">
+      <c r="B16" s="26">
+        <v>45959</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="30">
       <c r="A17" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="18" spans="1:1">
+      <c r="B17" s="26">
+        <v>45959</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>390</v>
+      </c>
+      <c r="G17" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="30">
       <c r="A18" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="19" spans="1:1">
+      <c r="B18" s="26">
+        <v>45959</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="D18" s="14" t="s">
+        <v>397</v>
+      </c>
+      <c r="G18" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="30">
       <c r="A19" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:1">
+      <c r="B19" s="26">
+        <v>45959</v>
+      </c>
+      <c r="C19" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>406</v>
+      </c>
+      <c r="G19" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H19" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30">
       <c r="A20" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="21" spans="1:1">
+      <c r="B20" s="26">
+        <v>45959</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>413</v>
+      </c>
+      <c r="G20" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
         <v>113</v>
       </c>
@@ -6350,7 +7667,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30" hidden="1">
+    <row r="2" spans="1:11" ht="30">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -6377,7 +7694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" hidden="1">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -6404,7 +7721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30" hidden="1">
+    <row r="4" spans="1:11" ht="30">
       <c r="A4" t="s">
         <v>33</v>
       </c>
@@ -6431,7 +7748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30" hidden="1">
+    <row r="5" spans="1:11" ht="30">
       <c r="A5" t="s">
         <v>33</v>
       </c>
@@ -6458,7 +7775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="45" hidden="1">
+    <row r="6" spans="1:11" ht="45">
       <c r="A6" t="s">
         <v>33</v>
       </c>
@@ -6512,7 +7829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="60" hidden="1">
+    <row r="8" spans="1:11" ht="60">
       <c r="A8" t="s">
         <v>33</v>
       </c>
@@ -6539,7 +7856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" hidden="1">
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -6566,7 +7883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="30" hidden="1">
+    <row r="10" spans="1:11" ht="30">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -6593,7 +7910,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="30" hidden="1">
+    <row r="11" spans="1:11" ht="30">
       <c r="A11" t="s">
         <v>33</v>
       </c>
@@ -6620,7 +7937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="30" hidden="1">
+    <row r="12" spans="1:11" ht="30">
       <c r="A12" t="s">
         <v>33</v>
       </c>
@@ -6647,7 +7964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="30" hidden="1">
+    <row r="13" spans="1:11" ht="30">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -6674,7 +7991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="30" hidden="1">
+    <row r="14" spans="1:11" ht="30">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -6701,7 +8018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="30" hidden="1">
+    <row r="15" spans="1:11" ht="30">
       <c r="A15" t="s">
         <v>33</v>
       </c>
@@ -6728,7 +8045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="30" hidden="1">
+    <row r="16" spans="1:11" ht="30">
       <c r="A16" t="s">
         <v>33</v>
       </c>
@@ -6755,7 +8072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="30" hidden="1">
+    <row r="17" spans="1:8" ht="30">
       <c r="A17" t="s">
         <v>33</v>
       </c>
@@ -6782,7 +8099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="30" hidden="1">
+    <row r="18" spans="1:8" ht="30">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -6809,7 +8126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="30" hidden="1">
+    <row r="19" spans="1:8" ht="30">
       <c r="A19" t="s">
         <v>33</v>
       </c>
@@ -6836,7 +8153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" hidden="1">
+    <row r="20" spans="1:8" ht="30">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -6863,7 +8180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="30" hidden="1">
+    <row r="21" spans="1:8" ht="30">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -6890,7 +8207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30" hidden="1">
+    <row r="22" spans="1:8" ht="30">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -6917,7 +8234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="42.75" hidden="1">
+    <row r="23" spans="1:8" ht="42.75">
       <c r="A23" t="s">
         <v>33</v>
       </c>
@@ -6944,7 +8261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30" hidden="1">
+    <row r="24" spans="1:8" ht="30">
       <c r="A24" t="s">
         <v>33</v>
       </c>
@@ -6971,7 +8288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" hidden="1">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -6998,7 +8315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="30" hidden="1">
+    <row r="26" spans="1:8" ht="30">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -7025,7 +8342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30" hidden="1">
+    <row r="27" spans="1:8" ht="30">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -7052,7 +8369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" hidden="1">
+    <row r="28" spans="1:8" ht="30">
       <c r="A28" t="s">
         <v>33</v>
       </c>
@@ -7079,7 +8396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="45" hidden="1">
+    <row r="29" spans="1:8" ht="45">
       <c r="A29" t="s">
         <v>33</v>
       </c>
@@ -7106,7 +8423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="30" hidden="1">
+    <row r="30" spans="1:8" ht="30">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -7133,7 +8450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="28.5" hidden="1">
+    <row r="31" spans="1:8" ht="28.5">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -7160,7 +8477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="30" hidden="1">
+    <row r="32" spans="1:8" ht="30">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -7187,7 +8504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" hidden="1">
+    <row r="33" spans="1:8" ht="30">
       <c r="A33" t="s">
         <v>33</v>
       </c>
@@ -7214,7 +8531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30" hidden="1">
+    <row r="34" spans="1:8" ht="30">
       <c r="A34" t="s">
         <v>81</v>
       </c>
@@ -7241,7 +8558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" hidden="1">
+    <row r="35" spans="1:8" ht="30">
       <c r="A35" t="s">
         <v>81</v>
       </c>
@@ -7268,7 +8585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" hidden="1">
+    <row r="36" spans="1:8" ht="30">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -7295,7 +8612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" hidden="1">
+    <row r="37" spans="1:8" ht="30">
       <c r="A37" t="s">
         <v>81</v>
       </c>
@@ -7322,7 +8639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="30" hidden="1">
+    <row r="38" spans="1:8" ht="30">
       <c r="A38" t="s">
         <v>81</v>
       </c>
@@ -7349,7 +8666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="30" hidden="1">
+    <row r="39" spans="1:8" ht="30">
       <c r="A39" t="s">
         <v>81</v>
       </c>
@@ -7376,7 +8693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="30" hidden="1">
+    <row r="40" spans="1:8" ht="30">
       <c r="A40" t="s">
         <v>81</v>
       </c>
@@ -7403,7 +8720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="30" hidden="1">
+    <row r="41" spans="1:8" ht="30">
       <c r="A41" t="s">
         <v>81</v>
       </c>
@@ -7430,7 +8747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="30" hidden="1">
+    <row r="42" spans="1:8" ht="30">
       <c r="A42" t="s">
         <v>82</v>
       </c>
@@ -7457,7 +8774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="30" hidden="1">
+    <row r="43" spans="1:8" ht="30">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -7484,7 +8801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="30" hidden="1">
+    <row r="44" spans="1:8" ht="30">
       <c r="A44" t="s">
         <v>82</v>
       </c>
@@ -7511,7 +8828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30" hidden="1">
+    <row r="45" spans="1:8" ht="30">
       <c r="A45" t="s">
         <v>82</v>
       </c>
@@ -7538,7 +8855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30" hidden="1">
+    <row r="46" spans="1:8" ht="30">
       <c r="A46" t="s">
         <v>82</v>
       </c>
@@ -7565,7 +8882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="30" hidden="1">
+    <row r="47" spans="1:8" ht="30">
       <c r="A47" t="s">
         <v>82</v>
       </c>
@@ -7592,7 +8909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="30" hidden="1">
+    <row r="48" spans="1:8" ht="30">
       <c r="A48" t="s">
         <v>82</v>
       </c>
@@ -7646,7 +8963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30" hidden="1">
+    <row r="50" spans="1:8" ht="30">
       <c r="A50" t="s">
         <v>82</v>
       </c>
@@ -7673,7 +8990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="30" hidden="1">
+    <row r="51" spans="1:8" ht="30">
       <c r="A51" t="s">
         <v>82</v>
       </c>
@@ -7700,7 +9017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="30" hidden="1">
+    <row r="52" spans="1:8" ht="30">
       <c r="A52" t="s">
         <v>82</v>
       </c>
@@ -7727,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="30" hidden="1">
+    <row r="53" spans="1:8" ht="30">
       <c r="A53" t="s">
         <v>82</v>
       </c>
@@ -7754,7 +9071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="30" hidden="1">
+    <row r="54" spans="1:8" ht="30">
       <c r="A54" t="s">
         <v>83</v>
       </c>
@@ -7781,7 +9098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="30" hidden="1">
+    <row r="55" spans="1:8" ht="30">
       <c r="A55" t="s">
         <v>83</v>
       </c>
@@ -7808,7 +9125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="30" hidden="1">
+    <row r="56" spans="1:8" ht="30">
       <c r="A56" t="s">
         <v>83</v>
       </c>
@@ -7835,7 +9152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="30" hidden="1">
+    <row r="57" spans="1:8" ht="30">
       <c r="A57" t="s">
         <v>83</v>
       </c>
@@ -7862,7 +9179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="30" hidden="1">
+    <row r="58" spans="1:8" ht="30">
       <c r="A58" t="s">
         <v>83</v>
       </c>
@@ -7889,7 +9206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="30" hidden="1">
+    <row r="59" spans="1:8" ht="30">
       <c r="A59" t="s">
         <v>83</v>
       </c>
@@ -7916,7 +9233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="30" hidden="1">
+    <row r="60" spans="1:8" ht="30">
       <c r="A60" t="s">
         <v>83</v>
       </c>
@@ -7943,7 +9260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="30" hidden="1">
+    <row r="61" spans="1:8" ht="30">
       <c r="A61" t="s">
         <v>83</v>
       </c>
@@ -7970,7 +9287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="30" hidden="1">
+    <row r="62" spans="1:8" ht="30">
       <c r="A62" t="s">
         <v>83</v>
       </c>
@@ -7997,7 +9314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="30" hidden="1">
+    <row r="63" spans="1:8" ht="30">
       <c r="A63" t="s">
         <v>83</v>
       </c>
@@ -8024,7 +9341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="30" hidden="1">
+    <row r="64" spans="1:8" ht="30">
       <c r="A64" t="s">
         <v>83</v>
       </c>
@@ -8051,7 +9368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="30" hidden="1">
+    <row r="65" spans="1:8" ht="30">
       <c r="A65" t="s">
         <v>83</v>
       </c>
@@ -8078,7 +9395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="30" hidden="1">
+    <row r="66" spans="1:8" ht="30">
       <c r="A66" t="s">
         <v>83</v>
       </c>
@@ -8105,7 +9422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="30" hidden="1">
+    <row r="67" spans="1:8" ht="30">
       <c r="A67" t="s">
         <v>83</v>
       </c>
@@ -8132,7 +9449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="30" hidden="1">
+    <row r="68" spans="1:8" ht="30">
       <c r="A68" t="s">
         <v>83</v>
       </c>
@@ -8159,7 +9476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="30" hidden="1">
+    <row r="69" spans="1:8" ht="30">
       <c r="A69" t="s">
         <v>83</v>
       </c>
@@ -8186,7 +9503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="30" hidden="1">
+    <row r="70" spans="1:8" ht="30">
       <c r="A70" t="s">
         <v>84</v>
       </c>
@@ -8213,7 +9530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="30" hidden="1">
+    <row r="71" spans="1:8" ht="30">
       <c r="A71" t="s">
         <v>84</v>
       </c>
@@ -8240,7 +9557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="30" hidden="1">
+    <row r="72" spans="1:8" ht="30">
       <c r="A72" t="s">
         <v>84</v>
       </c>
@@ -8267,7 +9584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="30" hidden="1">
+    <row r="73" spans="1:8" ht="30">
       <c r="A73" t="s">
         <v>84</v>
       </c>
@@ -8294,7 +9611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="30" hidden="1">
+    <row r="74" spans="1:8" ht="30">
       <c r="A74" t="s">
         <v>84</v>
       </c>
@@ -8321,7 +9638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="30" hidden="1">
+    <row r="75" spans="1:8" ht="30">
       <c r="A75" t="s">
         <v>84</v>
       </c>
@@ -8348,7 +9665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="30" hidden="1">
+    <row r="76" spans="1:8" ht="30">
       <c r="A76" t="s">
         <v>84</v>
       </c>
@@ -8375,7 +9692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="30" hidden="1">
+    <row r="77" spans="1:8" ht="30">
       <c r="A77" t="s">
         <v>84</v>
       </c>
@@ -8402,7 +9719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="30" hidden="1">
+    <row r="78" spans="1:8" ht="30">
       <c r="A78" t="s">
         <v>84</v>
       </c>
@@ -8429,7 +9746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="30" hidden="1">
+    <row r="79" spans="1:8" ht="30">
       <c r="A79" t="s">
         <v>84</v>
       </c>
@@ -8456,7 +9773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="30" hidden="1">
+    <row r="80" spans="1:8" ht="30">
       <c r="A80" t="s">
         <v>84</v>
       </c>
@@ -8483,7 +9800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:8" ht="30" hidden="1">
+    <row r="81" spans="1:8" ht="30">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -8510,7 +9827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="30" hidden="1">
+    <row r="82" spans="1:8" ht="30">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -8537,7 +9854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="30" hidden="1">
+    <row r="83" spans="1:8" ht="30">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -8564,7 +9881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="30" hidden="1">
+    <row r="84" spans="1:8" ht="30">
       <c r="A84" t="s">
         <v>84</v>
       </c>
@@ -8618,7 +9935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="30" hidden="1">
+    <row r="86" spans="1:8" ht="30">
       <c r="A86" t="s">
         <v>84</v>
       </c>
@@ -8645,7 +9962,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="30" hidden="1">
+    <row r="87" spans="1:8" ht="30">
       <c r="A87" t="s">
         <v>84</v>
       </c>
@@ -8672,7 +9989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="30" hidden="1">
+    <row r="88" spans="1:8" ht="30">
       <c r="A88" t="s">
         <v>85</v>
       </c>
@@ -8699,7 +10016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="30" hidden="1">
+    <row r="89" spans="1:8" ht="30">
       <c r="A89" t="s">
         <v>85</v>
       </c>
@@ -8726,7 +10043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="30" hidden="1">
+    <row r="90" spans="1:8" ht="30">
       <c r="A90" t="s">
         <v>85</v>
       </c>
@@ -8753,7 +10070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:8" ht="30" hidden="1">
+    <row r="91" spans="1:8" ht="30">
       <c r="A91" t="s">
         <v>85</v>
       </c>
@@ -8780,7 +10097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="30" hidden="1">
+    <row r="92" spans="1:8" ht="30">
       <c r="A92" t="s">
         <v>85</v>
       </c>
@@ -8834,7 +10151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="30" hidden="1">
+    <row r="94" spans="1:8" ht="30">
       <c r="A94" t="s">
         <v>85</v>
       </c>
@@ -8861,7 +10178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="30" hidden="1">
+    <row r="95" spans="1:8" ht="30">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -8888,7 +10205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="30" hidden="1">
+    <row r="96" spans="1:8" ht="30">
       <c r="A96" t="s">
         <v>85</v>
       </c>
@@ -8915,7 +10232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="30" hidden="1">
+    <row r="97" spans="1:8" ht="30">
       <c r="A97" t="s">
         <v>85</v>
       </c>
@@ -8942,7 +10259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="30" hidden="1">
+    <row r="98" spans="1:8" ht="30">
       <c r="A98" t="s">
         <v>90</v>
       </c>
@@ -8969,7 +10286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:8" ht="30" hidden="1">
+    <row r="99" spans="1:8" ht="30">
       <c r="A99" t="s">
         <v>90</v>
       </c>
@@ -8996,7 +10313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:8" ht="30" hidden="1">
+    <row r="100" spans="1:8" ht="30">
       <c r="A100" t="s">
         <v>90</v>
       </c>
@@ -9023,7 +10340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:8" ht="30" hidden="1">
+    <row r="101" spans="1:8" ht="30">
       <c r="A101" t="s">
         <v>90</v>
       </c>
@@ -9050,7 +10367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:8" ht="30" hidden="1">
+    <row r="102" spans="1:8" ht="30">
       <c r="A102" t="s">
         <v>90</v>
       </c>
@@ -9077,7 +10394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:8" ht="30" hidden="1">
+    <row r="103" spans="1:8" ht="30">
       <c r="A103" t="s">
         <v>90</v>
       </c>
@@ -9104,7 +10421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:8" ht="30" hidden="1">
+    <row r="104" spans="1:8" ht="30">
       <c r="A104" t="s">
         <v>90</v>
       </c>
@@ -9131,7 +10448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:8" ht="30" hidden="1">
+    <row r="105" spans="1:8" ht="30">
       <c r="A105" t="s">
         <v>90</v>
       </c>
@@ -9158,7 +10475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:8" ht="30" hidden="1">
+    <row r="106" spans="1:8" ht="30">
       <c r="A106" t="s">
         <v>90</v>
       </c>
@@ -9185,7 +10502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:8" ht="30" hidden="1">
+    <row r="107" spans="1:8" ht="30">
       <c r="A107" t="s">
         <v>90</v>
       </c>
@@ -9212,7 +10529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:8" ht="30" hidden="1">
+    <row r="108" spans="1:8" ht="30">
       <c r="A108" t="s">
         <v>90</v>
       </c>
@@ -9239,7 +10556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:8" ht="30" hidden="1">
+    <row r="109" spans="1:8" ht="30">
       <c r="A109" t="s">
         <v>90</v>
       </c>
@@ -9266,7 +10583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:8" ht="30" hidden="1">
+    <row r="110" spans="1:8" ht="30">
       <c r="A110" t="s">
         <v>90</v>
       </c>
@@ -9320,7 +10637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:8" ht="30" hidden="1">
+    <row r="112" spans="1:8" ht="30">
       <c r="A112" t="s">
         <v>91</v>
       </c>
@@ -9347,7 +10664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:8" ht="30" hidden="1">
+    <row r="113" spans="1:8" ht="30">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -9374,7 +10691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:8" ht="30" hidden="1">
+    <row r="114" spans="1:8" ht="30">
       <c r="A114" t="s">
         <v>91</v>
       </c>
@@ -9401,7 +10718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:8" ht="30" hidden="1">
+    <row r="115" spans="1:8" ht="30">
       <c r="A115" t="s">
         <v>91</v>
       </c>
@@ -9428,7 +10745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:8" ht="30" hidden="1">
+    <row r="116" spans="1:8" ht="30">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -9455,7 +10772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:8" ht="30" hidden="1">
+    <row r="117" spans="1:8" ht="30">
       <c r="A117" t="s">
         <v>91</v>
       </c>
@@ -9482,7 +10799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:8" ht="30" hidden="1">
+    <row r="118" spans="1:8" ht="30">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -9509,7 +10826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:8" ht="30" hidden="1">
+    <row r="119" spans="1:8" ht="30">
       <c r="A119" t="s">
         <v>91</v>
       </c>
@@ -9563,7 +10880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:8" ht="30" hidden="1">
+    <row r="121" spans="1:8" ht="30">
       <c r="A121" t="s">
         <v>91</v>
       </c>
@@ -9590,7 +10907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:8" ht="30" hidden="1">
+    <row r="122" spans="1:8" ht="30">
       <c r="A122" t="s">
         <v>92</v>
       </c>
@@ -9617,7 +10934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:8" ht="30" hidden="1">
+    <row r="123" spans="1:8" ht="30">
       <c r="A123" t="s">
         <v>92</v>
       </c>
@@ -9644,7 +10961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:8" ht="30" hidden="1">
+    <row r="124" spans="1:8" ht="30">
       <c r="A124" t="s">
         <v>92</v>
       </c>
@@ -9671,7 +10988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:8" ht="30" hidden="1">
+    <row r="125" spans="1:8" ht="30">
       <c r="A125" t="s">
         <v>92</v>
       </c>
@@ -9698,7 +11015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:8" ht="30" hidden="1">
+    <row r="126" spans="1:8" ht="30">
       <c r="A126" t="s">
         <v>92</v>
       </c>
@@ -9725,7 +11042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:8" ht="30" hidden="1">
+    <row r="127" spans="1:8" ht="30">
       <c r="A127" t="s">
         <v>92</v>
       </c>
@@ -9752,7 +11069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:8" ht="30" hidden="1">
+    <row r="128" spans="1:8" ht="30">
       <c r="A128" t="s">
         <v>92</v>
       </c>
@@ -9806,7 +11123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:8" ht="30" hidden="1">
+    <row r="130" spans="1:8" ht="30">
       <c r="A130" t="s">
         <v>92</v>
       </c>
@@ -9833,7 +11150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:8" ht="30" hidden="1">
+    <row r="131" spans="1:8" ht="30">
       <c r="A131" t="s">
         <v>92</v>
       </c>
@@ -9860,7 +11177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:8" ht="30" hidden="1">
+    <row r="132" spans="1:8" ht="30">
       <c r="A132" t="s">
         <v>92</v>
       </c>
@@ -9887,7 +11204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:8" ht="30" hidden="1">
+    <row r="133" spans="1:8" ht="30">
       <c r="A133" t="s">
         <v>92</v>
       </c>
@@ -9914,7 +11231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:8" ht="30" hidden="1">
+    <row r="134" spans="1:8" ht="30">
       <c r="A134" t="s">
         <v>93</v>
       </c>
@@ -9941,7 +11258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:8" ht="30" hidden="1">
+    <row r="135" spans="1:8" ht="30">
       <c r="A135" t="s">
         <v>93</v>
       </c>
@@ -9968,7 +11285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:8" ht="30" hidden="1">
+    <row r="136" spans="1:8" ht="30">
       <c r="A136" t="s">
         <v>93</v>
       </c>
@@ -9995,7 +11312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:8" ht="30" hidden="1">
+    <row r="137" spans="1:8" ht="30">
       <c r="A137" t="s">
         <v>93</v>
       </c>
@@ -10022,7 +11339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:8" ht="30" hidden="1">
+    <row r="138" spans="1:8" ht="30">
       <c r="A138" t="s">
         <v>93</v>
       </c>
@@ -10049,7 +11366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:8" ht="30" hidden="1">
+    <row r="139" spans="1:8" ht="30">
       <c r="A139" t="s">
         <v>93</v>
       </c>
@@ -10076,7 +11393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:8" ht="30" hidden="1">
+    <row r="140" spans="1:8" ht="30">
       <c r="A140" t="s">
         <v>93</v>
       </c>
@@ -10103,7 +11420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:8" ht="30" hidden="1">
+    <row r="141" spans="1:8" ht="30">
       <c r="A141" t="s">
         <v>93</v>
       </c>
@@ -10130,7 +11447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:8" ht="30" hidden="1">
+    <row r="142" spans="1:8" ht="30">
       <c r="A142" t="s">
         <v>93</v>
       </c>
@@ -10157,7 +11474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:8" ht="30" hidden="1">
+    <row r="143" spans="1:8" ht="30">
       <c r="A143" t="s">
         <v>93</v>
       </c>
@@ -10184,7 +11501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:8" ht="30" hidden="1">
+    <row r="144" spans="1:8" ht="30">
       <c r="A144" t="s">
         <v>93</v>
       </c>
@@ -10238,7 +11555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:8" ht="30" hidden="1">
+    <row r="146" spans="1:8" ht="30">
       <c r="A146" t="s">
         <v>94</v>
       </c>
@@ -10265,1315 +11582,3118 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:8" hidden="1">
+    <row r="147" spans="1:8" ht="28.5">
+      <c r="A147" t="s">
+        <v>96</v>
+      </c>
       <c r="B147" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C147, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E147" s="24"/>
-      <c r="F147" s="24"/>
-      <c r="G147" s="14"/>
-    </row>
-    <row r="148" spans="1:8" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C147" t="s">
+        <v>57</v>
+      </c>
+      <c r="D147" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E147" s="25">
+        <v>5</v>
+      </c>
+      <c r="F147" s="25">
+        <v>4</v>
+      </c>
+      <c r="G147" s="25" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="28.5">
+      <c r="A148" t="s">
+        <v>96</v>
+      </c>
       <c r="B148" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C148, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E148" s="24"/>
-      <c r="F148" s="24"/>
-      <c r="G148" s="14"/>
-    </row>
-    <row r="149" spans="1:8" hidden="1">
+        <v>ATO012</v>
+      </c>
+      <c r="C148" t="s">
+        <v>66</v>
+      </c>
+      <c r="D148" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E148" s="25">
+        <v>4</v>
+      </c>
+      <c r="F148" s="25">
+        <v>3</v>
+      </c>
+      <c r="G148" s="25" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" ht="42.75">
+      <c r="A149" t="s">
+        <v>96</v>
+      </c>
       <c r="B149" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C149, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E149" s="24"/>
-      <c r="F149" s="24"/>
-      <c r="G149" s="14"/>
-    </row>
-    <row r="150" spans="1:8" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C149" t="s">
+        <v>69</v>
+      </c>
+      <c r="D149" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" s="25">
+        <v>6</v>
+      </c>
+      <c r="F149" s="25">
+        <v>5</v>
+      </c>
+      <c r="G149" s="25" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" ht="28.5">
+      <c r="A150" t="s">
+        <v>96</v>
+      </c>
       <c r="B150" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C150, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E150" s="24"/>
-      <c r="F150" s="24"/>
-      <c r="G150" s="14"/>
-    </row>
-    <row r="151" spans="1:8" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C150" t="s">
+        <v>59</v>
+      </c>
+      <c r="D150" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E150" s="25">
+        <v>2</v>
+      </c>
+      <c r="F150" s="25">
+        <v>2</v>
+      </c>
+      <c r="G150" s="25" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" ht="28.5">
+      <c r="A151" t="s">
+        <v>96</v>
+      </c>
       <c r="B151" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C151, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E151" s="24"/>
-      <c r="F151" s="24"/>
-      <c r="G151" s="14"/>
-    </row>
-    <row r="152" spans="1:8" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C151" t="s">
+        <v>63</v>
+      </c>
+      <c r="D151" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E151" s="25">
+        <v>2</v>
+      </c>
+      <c r="F151" s="25">
+        <v>2</v>
+      </c>
+      <c r="G151" s="25" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" ht="28.5">
+      <c r="A152" t="s">
+        <v>96</v>
+      </c>
       <c r="B152" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C152, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E152" s="24"/>
-      <c r="F152" s="24"/>
-      <c r="G152" s="14"/>
-    </row>
-    <row r="153" spans="1:8" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C152" t="s">
+        <v>64</v>
+      </c>
+      <c r="D152" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E152" s="25">
+        <v>2</v>
+      </c>
+      <c r="F152" s="25">
+        <v>2</v>
+      </c>
+      <c r="G152" s="25" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" ht="28.5">
+      <c r="A153" t="s">
+        <v>96</v>
+      </c>
       <c r="B153" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C153, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E153" s="24"/>
-      <c r="F153" s="24"/>
-      <c r="G153" s="14"/>
-    </row>
-    <row r="154" spans="1:8" hidden="1">
+        <v>ATO011</v>
+      </c>
+      <c r="C153" t="s">
+        <v>65</v>
+      </c>
+      <c r="D153" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E153" s="25">
+        <v>3</v>
+      </c>
+      <c r="F153" s="25">
+        <v>3</v>
+      </c>
+      <c r="G153" s="25" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" ht="28.5">
+      <c r="A154" t="s">
+        <v>96</v>
+      </c>
       <c r="B154" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C154, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E154" s="24"/>
-      <c r="F154" s="24"/>
-      <c r="G154" s="14"/>
-    </row>
-    <row r="155" spans="1:8" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C154" t="s">
+        <v>72</v>
+      </c>
+      <c r="D154" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E154" s="25">
+        <v>-2</v>
+      </c>
+      <c r="F154" s="25">
+        <v>2</v>
+      </c>
+      <c r="G154" s="25" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="28.5">
+      <c r="A155" t="s">
+        <v>96</v>
+      </c>
       <c r="B155" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C155, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E155" s="24"/>
-      <c r="F155" s="24"/>
-      <c r="G155" s="14"/>
-    </row>
-    <row r="156" spans="1:8" hidden="1">
+        <v>ATO005</v>
+      </c>
+      <c r="C155" t="s">
+        <v>55</v>
+      </c>
+      <c r="D155" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E155" s="25">
+        <v>-4</v>
+      </c>
+      <c r="F155" s="25">
+        <v>4</v>
+      </c>
+      <c r="G155" s="25" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" ht="42.75">
+      <c r="A156" t="s">
+        <v>96</v>
+      </c>
       <c r="B156" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C156, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E156" s="24"/>
-      <c r="F156" s="24"/>
-      <c r="G156" s="14"/>
-    </row>
-    <row r="157" spans="1:8" hidden="1">
+        <v>ATO004</v>
+      </c>
+      <c r="C156" t="s">
+        <v>54</v>
+      </c>
+      <c r="D156" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="25">
+        <v>1</v>
+      </c>
+      <c r="F156" s="25">
+        <v>1</v>
+      </c>
+      <c r="G156" s="25" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" ht="28.5">
+      <c r="A157" t="s">
+        <v>96</v>
+      </c>
       <c r="B157" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C157, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E157" s="24"/>
-      <c r="F157" s="24"/>
-      <c r="G157" s="14"/>
-    </row>
-    <row r="158" spans="1:8" hidden="1">
+        <v>ATO013</v>
+      </c>
+      <c r="C157" t="s">
+        <v>67</v>
+      </c>
+      <c r="D157" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="25">
+        <v>4</v>
+      </c>
+      <c r="F157" s="25">
+        <v>3</v>
+      </c>
+      <c r="G157" s="25" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="28.5">
+      <c r="A158" t="s">
+        <v>96</v>
+      </c>
       <c r="B158" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C158, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E158" s="24"/>
-      <c r="F158" s="24"/>
-      <c r="G158" s="14"/>
-    </row>
-    <row r="159" spans="1:8" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C158" t="s">
+        <v>52</v>
+      </c>
+      <c r="D158" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="25">
+        <v>3</v>
+      </c>
+      <c r="F158" s="25">
+        <v>3</v>
+      </c>
+      <c r="G158" s="25" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" ht="28.5">
+      <c r="A159" t="s">
+        <v>96</v>
+      </c>
       <c r="B159" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C159, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E159" s="24"/>
-      <c r="F159" s="24"/>
-      <c r="G159" s="14"/>
-    </row>
-    <row r="160" spans="1:8" hidden="1">
+        <v>ATO008</v>
+      </c>
+      <c r="C159" t="s">
+        <v>61</v>
+      </c>
+      <c r="D159" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E159" s="25">
+        <v>1</v>
+      </c>
+      <c r="F159" s="25">
+        <v>1</v>
+      </c>
+      <c r="G159" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" ht="28.5">
+      <c r="A160" t="s">
+        <v>96</v>
+      </c>
       <c r="B160" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C160, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E160" s="24"/>
-      <c r="F160" s="24"/>
-      <c r="G160" s="14"/>
-    </row>
-    <row r="161" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C160" t="s">
+        <v>51</v>
+      </c>
+      <c r="D160" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E160" s="25">
+        <v>1</v>
+      </c>
+      <c r="F160" s="25">
+        <v>1</v>
+      </c>
+      <c r="G160" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" ht="28.5">
+      <c r="A161" t="s">
+        <v>96</v>
+      </c>
       <c r="B161" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C161, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E161" s="24"/>
-      <c r="F161" s="24"/>
-      <c r="G161" s="14"/>
-    </row>
-    <row r="162" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C161" t="s">
+        <v>68</v>
+      </c>
+      <c r="D161" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E161" s="25">
+        <v>1</v>
+      </c>
+      <c r="F161" s="25">
+        <v>1</v>
+      </c>
+      <c r="G161" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" ht="42.75">
+      <c r="A162" t="s">
+        <v>96</v>
+      </c>
       <c r="B162" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C162, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E162" s="24"/>
-      <c r="F162" s="24"/>
-      <c r="G162" s="14"/>
-    </row>
-    <row r="163" spans="2:7" hidden="1">
+        <v>ATO012</v>
+      </c>
+      <c r="C162" t="s">
+        <v>66</v>
+      </c>
+      <c r="D162" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E162" s="25">
+        <v>5</v>
+      </c>
+      <c r="F162" s="25">
+        <v>4</v>
+      </c>
+      <c r="G162" s="25" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" ht="42.75">
+      <c r="A163" t="s">
+        <v>96</v>
+      </c>
       <c r="B163" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C163, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E163" s="24"/>
-      <c r="F163" s="24"/>
-      <c r="G163" s="14"/>
-    </row>
-    <row r="164" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C163" t="s">
+        <v>69</v>
+      </c>
+      <c r="D163" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E163" s="25">
+        <v>5</v>
+      </c>
+      <c r="F163" s="25">
+        <v>4</v>
+      </c>
+      <c r="G163" s="25" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" ht="42.75">
+      <c r="A164" t="s">
+        <v>96</v>
+      </c>
       <c r="B164" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C164, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E164" s="24"/>
-      <c r="F164" s="24"/>
-      <c r="G164" s="14"/>
-    </row>
-    <row r="165" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C164" t="s">
+        <v>57</v>
+      </c>
+      <c r="D164" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E164" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F164" s="25">
+        <v>0</v>
+      </c>
+      <c r="G164" s="25" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" ht="42.75">
+      <c r="A165" t="s">
+        <v>96</v>
+      </c>
       <c r="B165" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C165, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E165" s="24"/>
-      <c r="F165" s="24"/>
-      <c r="G165" s="14"/>
-    </row>
-    <row r="166" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C165" t="s">
+        <v>59</v>
+      </c>
+      <c r="D165" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E165" s="25">
+        <v>-1</v>
+      </c>
+      <c r="F165" s="25">
+        <v>1</v>
+      </c>
+      <c r="G165" s="25" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" ht="28.5">
+      <c r="A166" t="s">
+        <v>96</v>
+      </c>
       <c r="B166" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C166, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E166" s="24"/>
-      <c r="F166" s="24"/>
-      <c r="G166" s="14"/>
-    </row>
-    <row r="167" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C166" t="s">
+        <v>63</v>
+      </c>
+      <c r="D166" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E166" s="25">
+        <v>3</v>
+      </c>
+      <c r="F166" s="25">
+        <v>3</v>
+      </c>
+      <c r="G166" s="25" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" ht="28.5">
+      <c r="A167" t="s">
+        <v>96</v>
+      </c>
       <c r="B167" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C167, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E167" s="24"/>
-      <c r="F167" s="24"/>
-      <c r="G167" s="14"/>
-    </row>
-    <row r="168" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C167" t="s">
+        <v>64</v>
+      </c>
+      <c r="D167" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E167" s="25">
+        <v>3</v>
+      </c>
+      <c r="F167" s="25">
+        <v>3</v>
+      </c>
+      <c r="G167" s="25" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" ht="28.5">
+      <c r="A168" t="s">
+        <v>96</v>
+      </c>
       <c r="B168" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C168, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E168" s="24"/>
-      <c r="F168" s="24"/>
-      <c r="G168" s="14"/>
-    </row>
-    <row r="169" spans="2:7" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C168" t="s">
+        <v>72</v>
+      </c>
+      <c r="D168" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E168" s="25">
+        <v>4</v>
+      </c>
+      <c r="F168" s="25">
+        <v>3</v>
+      </c>
+      <c r="G168" s="25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" ht="28.5">
+      <c r="A169" t="s">
+        <v>96</v>
+      </c>
       <c r="B169" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C169, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E169" s="24"/>
-      <c r="F169" s="24"/>
-      <c r="G169" s="14"/>
-    </row>
-    <row r="170" spans="2:7" hidden="1">
+        <v>ATO004</v>
+      </c>
+      <c r="C169" t="s">
+        <v>54</v>
+      </c>
+      <c r="D169" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169" s="25">
+        <v>3</v>
+      </c>
+      <c r="F169" s="25">
+        <v>2</v>
+      </c>
+      <c r="G169" s="25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" ht="28.5">
+      <c r="A170" t="s">
+        <v>96</v>
+      </c>
       <c r="B170" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C170, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="E170" s="24"/>
-      <c r="F170" s="24"/>
-      <c r="G170" s="14"/>
-    </row>
-    <row r="171" spans="2:7" hidden="1">
+        <v>ATO013</v>
+      </c>
+      <c r="C170" t="s">
+        <v>67</v>
+      </c>
+      <c r="D170" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E170" s="25">
+        <v>4</v>
+      </c>
+      <c r="F170" s="25">
+        <v>3</v>
+      </c>
+      <c r="G170" s="25" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" ht="28.5">
+      <c r="A171" t="s">
+        <v>96</v>
+      </c>
       <c r="B171" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C171, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G171" s="14"/>
-    </row>
-    <row r="172" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C171" t="s">
+        <v>52</v>
+      </c>
+      <c r="D171" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E171" s="25">
+        <v>4</v>
+      </c>
+      <c r="F171" s="25">
+        <v>4</v>
+      </c>
+      <c r="G171" s="25" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="28.5">
+      <c r="A172" t="s">
+        <v>96</v>
+      </c>
       <c r="B172" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C172, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G172" s="14"/>
-    </row>
-    <row r="173" spans="2:7" hidden="1">
+        <v>ATO008</v>
+      </c>
+      <c r="C172" t="s">
+        <v>61</v>
+      </c>
+      <c r="D172" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E172" s="25">
+        <v>2</v>
+      </c>
+      <c r="F172" s="25">
+        <v>2</v>
+      </c>
+      <c r="G172" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="28.5">
+      <c r="A173" t="s">
+        <v>96</v>
+      </c>
       <c r="B173" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C173, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G173" s="14"/>
-    </row>
-    <row r="174" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C173" t="s">
+        <v>51</v>
+      </c>
+      <c r="D173" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E173" s="25">
+        <v>2</v>
+      </c>
+      <c r="F173" s="25">
+        <v>2</v>
+      </c>
+      <c r="G173" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="28.5">
+      <c r="A174" t="s">
+        <v>96</v>
+      </c>
       <c r="B174" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C174, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G174" s="14"/>
-    </row>
-    <row r="175" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C174" t="s">
+        <v>68</v>
+      </c>
+      <c r="D174" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E174" s="25">
+        <v>2</v>
+      </c>
+      <c r="F174" s="25">
+        <v>2</v>
+      </c>
+      <c r="G174" s="25" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="42.75">
+      <c r="A175" t="s">
+        <v>96</v>
+      </c>
       <c r="B175" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C175, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G175" s="14"/>
-    </row>
-    <row r="176" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C175" t="s">
+        <v>57</v>
+      </c>
+      <c r="D175" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E175" s="25">
+        <v>1</v>
+      </c>
+      <c r="F175" s="25">
+        <v>2</v>
+      </c>
+      <c r="G175" s="25" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="28.5">
+      <c r="A176" t="s">
+        <v>96</v>
+      </c>
       <c r="B176" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C176, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G176" s="14"/>
-    </row>
-    <row r="177" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C176" t="s">
+        <v>59</v>
+      </c>
+      <c r="D176" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E176" s="25">
+        <v>1</v>
+      </c>
+      <c r="F176" s="25">
+        <v>1</v>
+      </c>
+      <c r="G176" s="25" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="42.75">
+      <c r="A177" t="s">
+        <v>96</v>
+      </c>
       <c r="B177" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C177, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G177" s="14"/>
-    </row>
-    <row r="178" spans="2:7" hidden="1">
+        <v>ATO012</v>
+      </c>
+      <c r="C177" t="s">
+        <v>66</v>
+      </c>
+      <c r="D177" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" s="25">
+        <v>7</v>
+      </c>
+      <c r="F177" s="25">
+        <v>7</v>
+      </c>
+      <c r="G177" s="25" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="57">
+      <c r="A178" t="s">
+        <v>96</v>
+      </c>
       <c r="B178" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C178, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G178" s="14"/>
-    </row>
-    <row r="179" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C178" t="s">
+        <v>57</v>
+      </c>
+      <c r="D178" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E178" s="25">
+        <v>-4</v>
+      </c>
+      <c r="F178" s="25">
+        <v>5</v>
+      </c>
+      <c r="G178" s="25" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="42.75">
+      <c r="A179" t="s">
+        <v>96</v>
+      </c>
       <c r="B179" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C179, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G179" s="14"/>
-    </row>
-    <row r="180" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C179" t="s">
+        <v>63</v>
+      </c>
+      <c r="D179" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E179" s="25">
+        <v>0</v>
+      </c>
+      <c r="F179" s="25">
+        <v>2</v>
+      </c>
+      <c r="G179" s="25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="42.75">
+      <c r="A180" t="s">
+        <v>96</v>
+      </c>
       <c r="B180" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C180, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G180" s="14"/>
-    </row>
-    <row r="181" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C180" t="s">
+        <v>64</v>
+      </c>
+      <c r="D180" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E180" s="25">
+        <v>0</v>
+      </c>
+      <c r="F180" s="25">
+        <v>2</v>
+      </c>
+      <c r="G180" s="25" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" ht="42.75">
+      <c r="A181" t="s">
+        <v>96</v>
+      </c>
       <c r="B181" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C181, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G181" s="14"/>
-    </row>
-    <row r="182" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C181" t="s">
+        <v>59</v>
+      </c>
+      <c r="D181" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F181" s="25">
+        <v>4</v>
+      </c>
+      <c r="G181" s="25" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" ht="42.75">
+      <c r="A182" t="s">
+        <v>96</v>
+      </c>
       <c r="B182" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C182, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G182" s="14"/>
-    </row>
-    <row r="183" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C182" t="s">
+        <v>69</v>
+      </c>
+      <c r="D182" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E182" s="25">
+        <v>-2</v>
+      </c>
+      <c r="F182" s="25">
+        <v>1</v>
+      </c>
+      <c r="G182" s="25" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="42.75">
+      <c r="A183" t="s">
+        <v>96</v>
+      </c>
       <c r="B183" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C183, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G183" s="14"/>
-    </row>
-    <row r="184" spans="2:7" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C183" t="s">
+        <v>72</v>
+      </c>
+      <c r="D183" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E183" s="25">
+        <v>2</v>
+      </c>
+      <c r="F183" s="25">
+        <v>5</v>
+      </c>
+      <c r="G183" s="25" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="57">
+      <c r="A184" t="s">
+        <v>96</v>
+      </c>
       <c r="B184" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C184, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G184" s="14"/>
-    </row>
-    <row r="185" spans="2:7" hidden="1">
+        <v>ATO005</v>
+      </c>
+      <c r="C184" t="s">
+        <v>55</v>
+      </c>
+      <c r="D184" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E184" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F184" s="25">
+        <v>6</v>
+      </c>
+      <c r="G184" s="25" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" ht="42.75">
+      <c r="A185" t="s">
+        <v>96</v>
+      </c>
       <c r="B185" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C185, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G185" s="14"/>
-    </row>
-    <row r="186" spans="2:7" hidden="1">
+        <v>ATO004</v>
+      </c>
+      <c r="C185" t="s">
+        <v>54</v>
+      </c>
+      <c r="D185" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E185" s="25">
+        <v>2</v>
+      </c>
+      <c r="F185" s="25">
+        <v>2</v>
+      </c>
+      <c r="G185" s="25" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" ht="42.75">
+      <c r="A186" t="s">
+        <v>96</v>
+      </c>
       <c r="B186" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C186, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G186" s="14"/>
-    </row>
-    <row r="187" spans="2:7" hidden="1">
+        <v>ATO013</v>
+      </c>
+      <c r="C186" t="s">
+        <v>67</v>
+      </c>
+      <c r="D186" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E186" s="25">
+        <v>0</v>
+      </c>
+      <c r="F186" s="25">
+        <v>2</v>
+      </c>
+      <c r="G186" s="25" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" ht="42.75">
+      <c r="A187" t="s">
+        <v>96</v>
+      </c>
       <c r="B187" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C187, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G187" s="14"/>
-    </row>
-    <row r="188" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C187" t="s">
+        <v>52</v>
+      </c>
+      <c r="D187" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E187" s="25">
+        <v>-2</v>
+      </c>
+      <c r="F187" s="25">
+        <v>2</v>
+      </c>
+      <c r="G187" s="25" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" ht="42.75">
+      <c r="A188" t="s">
+        <v>96</v>
+      </c>
       <c r="B188" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C188, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G188" s="14"/>
-    </row>
-    <row r="189" spans="2:7" hidden="1">
+        <v>ATO008</v>
+      </c>
+      <c r="C188" t="s">
+        <v>61</v>
+      </c>
+      <c r="D188" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E188" s="25">
+        <v>-1</v>
+      </c>
+      <c r="F188" s="25">
+        <v>4</v>
+      </c>
+      <c r="G188" s="25" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" ht="42.75">
+      <c r="A189" t="s">
+        <v>96</v>
+      </c>
       <c r="B189" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C189, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G189" s="14"/>
-    </row>
-    <row r="190" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C189" t="s">
+        <v>51</v>
+      </c>
+      <c r="D189" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E189" s="25">
+        <v>0</v>
+      </c>
+      <c r="F189" s="25">
+        <v>0</v>
+      </c>
+      <c r="G189" s="25" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" ht="42.75">
+      <c r="A190" t="s">
+        <v>96</v>
+      </c>
       <c r="B190" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C190, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G190" s="14"/>
-    </row>
-    <row r="191" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E190" s="25">
+        <v>0</v>
+      </c>
+      <c r="F190" s="25">
+        <v>0</v>
+      </c>
+      <c r="G190" s="25" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" ht="28.5">
+      <c r="A191" t="s">
+        <v>97</v>
+      </c>
       <c r="B191" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C191, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G191" s="14"/>
-    </row>
-    <row r="192" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C191" t="s">
+        <v>57</v>
+      </c>
+      <c r="D191" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E191" s="25">
+        <v>5</v>
+      </c>
+      <c r="F191" s="25">
+        <v>4</v>
+      </c>
+      <c r="G191" s="25" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" ht="28.5">
+      <c r="A192" t="s">
+        <v>97</v>
+      </c>
       <c r="B192" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C192, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G192" s="14"/>
-    </row>
-    <row r="193" spans="2:7" hidden="1">
+        <v>ATO011</v>
+      </c>
+      <c r="C192" t="s">
+        <v>65</v>
+      </c>
+      <c r="D192" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E192" s="25">
+        <v>4</v>
+      </c>
+      <c r="F192" s="25">
+        <v>3</v>
+      </c>
+      <c r="G192" s="25" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="193" spans="1:7" ht="28.5">
+      <c r="A193" t="s">
+        <v>97</v>
+      </c>
       <c r="B193" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C193, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G193" s="14"/>
-    </row>
-    <row r="194" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C193" t="s">
+        <v>51</v>
+      </c>
+      <c r="D193" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E193" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F193" s="25">
+        <v>-2</v>
+      </c>
+      <c r="G193" s="25" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="194" spans="1:7" ht="28.5">
+      <c r="A194" t="s">
+        <v>97</v>
+      </c>
       <c r="B194" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C194, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G194" s="14"/>
-    </row>
-    <row r="195" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E194" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F194" s="25">
+        <v>-2</v>
+      </c>
+      <c r="G194" s="25" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="195" spans="1:7" ht="28.5">
+      <c r="A195" t="s">
+        <v>97</v>
+      </c>
       <c r="B195" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C195, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G195" s="14"/>
-    </row>
-    <row r="196" spans="2:7" hidden="1">
+        <v>ATO012</v>
+      </c>
+      <c r="C195" t="s">
+        <v>66</v>
+      </c>
+      <c r="D195" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E195" s="25">
+        <v>0</v>
+      </c>
+      <c r="F195" s="25">
+        <v>0</v>
+      </c>
+      <c r="G195" s="25" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="196" spans="1:7" ht="28.5">
+      <c r="A196" t="s">
+        <v>97</v>
+      </c>
       <c r="B196" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C196, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G196" s="14"/>
-    </row>
-    <row r="197" spans="2:7" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C196" t="s">
+        <v>72</v>
+      </c>
+      <c r="D196" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E196" s="25">
+        <v>-4</v>
+      </c>
+      <c r="F196" s="25">
+        <v>3</v>
+      </c>
+      <c r="G196" s="25" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="197" spans="1:7" ht="28.5">
+      <c r="A197" t="s">
+        <v>97</v>
+      </c>
       <c r="B197" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C197, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G197" s="14"/>
-    </row>
-    <row r="198" spans="2:7" hidden="1">
+        <v>ATO005</v>
+      </c>
+      <c r="C197" t="s">
+        <v>55</v>
+      </c>
+      <c r="D197" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E197" s="25">
+        <v>-5</v>
+      </c>
+      <c r="F197" s="25">
+        <v>4</v>
+      </c>
+      <c r="G197" s="25" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="198" spans="1:7" ht="28.5">
+      <c r="A198" t="s">
+        <v>97</v>
+      </c>
       <c r="B198" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C198, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G198" s="14"/>
-    </row>
-    <row r="199" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C198" t="s">
+        <v>63</v>
+      </c>
+      <c r="D198" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E198" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F198" s="25">
+        <v>-2</v>
+      </c>
+      <c r="G198" s="25" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="199" spans="1:7" ht="28.5">
+      <c r="A199" t="s">
+        <v>97</v>
+      </c>
       <c r="B199" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C199, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G199" s="14"/>
-    </row>
-    <row r="200" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C199" t="s">
+        <v>64</v>
+      </c>
+      <c r="D199" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E199" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F199" s="25">
+        <v>-2</v>
+      </c>
+      <c r="G199" s="25" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="200" spans="1:7">
+      <c r="A200" t="s">
+        <v>97</v>
+      </c>
       <c r="B200" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C200, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G200" s="14"/>
-    </row>
-    <row r="201" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C200" t="s">
+        <v>59</v>
+      </c>
+      <c r="D200" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E200" s="25">
+        <v>3</v>
+      </c>
+      <c r="F200" s="25">
+        <v>3</v>
+      </c>
+      <c r="G200" s="25" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="201" spans="1:7" ht="28.5">
+      <c r="A201" t="s">
+        <v>97</v>
+      </c>
       <c r="B201" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C201, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G201" s="14"/>
-    </row>
-    <row r="202" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C201" t="s">
+        <v>69</v>
+      </c>
+      <c r="D201" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E201" s="25">
+        <v>-8</v>
+      </c>
+      <c r="F201" s="25">
+        <v>-7</v>
+      </c>
+      <c r="G201" s="25" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7">
+      <c r="A202" t="s">
+        <v>97</v>
+      </c>
       <c r="B202" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C202, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G202" s="14"/>
-    </row>
-    <row r="203" spans="2:7" hidden="1">
+        <v>ATO013</v>
+      </c>
+      <c r="C202" t="s">
+        <v>67</v>
+      </c>
+      <c r="D202" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E202" s="25">
+        <v>0</v>
+      </c>
+      <c r="F202" s="25">
+        <v>0</v>
+      </c>
+      <c r="G202" s="25" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="28.5">
+      <c r="A203" t="s">
+        <v>97</v>
+      </c>
       <c r="B203" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C203, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G203" s="14"/>
-    </row>
-    <row r="204" spans="2:7" hidden="1">
+        <v>ATO004</v>
+      </c>
+      <c r="C203" t="s">
+        <v>54</v>
+      </c>
+      <c r="D203" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E203" s="25">
+        <v>0</v>
+      </c>
+      <c r="F203" s="25">
+        <v>0</v>
+      </c>
+      <c r="G203" s="25" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="28.5">
+      <c r="A204" t="s">
+        <v>97</v>
+      </c>
       <c r="B204" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C204, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G204" s="14"/>
-    </row>
-    <row r="205" spans="2:7" hidden="1">
+        <v>ATO001</v>
+      </c>
+      <c r="C204" t="s">
+        <v>50</v>
+      </c>
+      <c r="D204" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E204" s="25">
+        <v>-9</v>
+      </c>
+      <c r="F204" s="25">
+        <v>-5</v>
+      </c>
+      <c r="G204" s="25" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" ht="28.5">
+      <c r="A205" t="s">
+        <v>97</v>
+      </c>
       <c r="B205" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C205, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G205" s="14"/>
-    </row>
-    <row r="206" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C205" t="s">
+        <v>57</v>
+      </c>
+      <c r="D205" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E205" s="25">
+        <v>-4</v>
+      </c>
+      <c r="F205" s="25">
+        <v>-2</v>
+      </c>
+      <c r="G205" s="25" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="28.5">
+      <c r="A206" t="s">
+        <v>97</v>
+      </c>
       <c r="B206" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C206, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G206" s="14"/>
-    </row>
-    <row r="207" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C206" t="s">
+        <v>59</v>
+      </c>
+      <c r="D206" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E206" s="25">
+        <v>-4</v>
+      </c>
+      <c r="F206" s="25">
+        <v>-3</v>
+      </c>
+      <c r="G206" s="25" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="28.5">
+      <c r="A207" t="s">
+        <v>97</v>
+      </c>
       <c r="B207" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C207, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G207" s="14"/>
-    </row>
-    <row r="208" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C207" t="s">
+        <v>69</v>
+      </c>
+      <c r="D207" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E207" s="25">
+        <v>0</v>
+      </c>
+      <c r="F207" s="25">
+        <v>0</v>
+      </c>
+      <c r="G207" s="25" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="28.5">
+      <c r="A208" t="s">
+        <v>97</v>
+      </c>
       <c r="B208" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C208, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G208" s="14"/>
-    </row>
-    <row r="209" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C208" t="s">
+        <v>63</v>
+      </c>
+      <c r="D208" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E208" s="25">
+        <v>1</v>
+      </c>
+      <c r="F208" s="25">
+        <v>2</v>
+      </c>
+      <c r="G208" s="25" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7">
+      <c r="A209" t="s">
+        <v>97</v>
+      </c>
       <c r="B209" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C209, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G209" s="14"/>
-    </row>
-    <row r="210" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C209" t="s">
+        <v>64</v>
+      </c>
+      <c r="D209" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E209" s="25">
+        <v>1</v>
+      </c>
+      <c r="F209" s="25">
+        <v>2</v>
+      </c>
+      <c r="G209" s="27"/>
+    </row>
+    <row r="210" spans="1:7" ht="42.75">
+      <c r="A210" t="s">
+        <v>97</v>
+      </c>
       <c r="B210" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C210, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G210" s="14"/>
-    </row>
-    <row r="211" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C210" t="s">
+        <v>51</v>
+      </c>
+      <c r="D210" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E210" s="25">
+        <v>-2</v>
+      </c>
+      <c r="F210" s="25">
+        <v>-1</v>
+      </c>
+      <c r="G210" s="25" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" ht="42.75">
+      <c r="A211" t="s">
+        <v>97</v>
+      </c>
       <c r="B211" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C211, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G211" s="14"/>
-    </row>
-    <row r="212" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E211" s="25">
+        <v>-2</v>
+      </c>
+      <c r="F211" s="25">
+        <v>-1</v>
+      </c>
+      <c r="G211" s="25" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" ht="42.75">
+      <c r="A212" t="s">
+        <v>97</v>
+      </c>
       <c r="B212" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C212, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G212" s="14"/>
-    </row>
-    <row r="213" spans="2:7" hidden="1">
+        <v>ATO011</v>
+      </c>
+      <c r="C212" t="s">
+        <v>65</v>
+      </c>
+      <c r="D212" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E212" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F212" s="25">
+        <v>-1</v>
+      </c>
+      <c r="G212" s="25" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" ht="28.5">
+      <c r="A213" t="s">
+        <v>97</v>
+      </c>
       <c r="B213" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C213, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G213" s="14"/>
-    </row>
-    <row r="214" spans="2:7" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C213" t="s">
+        <v>72</v>
+      </c>
+      <c r="D213" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E213" s="25">
+        <v>5</v>
+      </c>
+      <c r="F213" s="25">
+        <v>4</v>
+      </c>
+      <c r="G213" s="25" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" ht="28.5">
+      <c r="A214" t="s">
+        <v>97</v>
+      </c>
       <c r="B214" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C214, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G214" s="14"/>
-    </row>
-    <row r="215" spans="2:7" hidden="1">
+        <v>ATO005</v>
+      </c>
+      <c r="C214" t="s">
+        <v>55</v>
+      </c>
+      <c r="D214" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E214" s="25">
+        <v>5</v>
+      </c>
+      <c r="F214" s="25">
+        <v>-4</v>
+      </c>
+      <c r="G214" s="25" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7">
+      <c r="A215" t="s">
+        <v>97</v>
+      </c>
       <c r="B215" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C215, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G215" s="14"/>
-    </row>
-    <row r="216" spans="2:7" hidden="1">
+        <v>ATO001</v>
+      </c>
+      <c r="C215" t="s">
+        <v>50</v>
+      </c>
+      <c r="D215" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E215" s="25">
+        <v>5</v>
+      </c>
+      <c r="F215" s="25">
+        <v>3</v>
+      </c>
+      <c r="G215" s="25" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" ht="42.75">
+      <c r="A216" t="s">
+        <v>98</v>
+      </c>
       <c r="B216" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C216, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G216" s="14"/>
-    </row>
-    <row r="217" spans="2:7" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C216" t="s">
+        <v>72</v>
+      </c>
+      <c r="D216" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E216" s="25">
+        <v>-6</v>
+      </c>
+      <c r="F216" s="25">
+        <v>5</v>
+      </c>
+      <c r="G216" s="25" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" ht="42.75">
+      <c r="A217" t="s">
+        <v>98</v>
+      </c>
       <c r="B217" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C217, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G217" s="14"/>
-    </row>
-    <row r="218" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C217" t="s">
+        <v>57</v>
+      </c>
+      <c r="D217" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E217" s="25">
+        <v>3</v>
+      </c>
+      <c r="F217" s="25">
+        <v>4</v>
+      </c>
+      <c r="G217" s="25" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="42.75">
+      <c r="A218" t="s">
+        <v>98</v>
+      </c>
       <c r="B218" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C218, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G218" s="14"/>
-    </row>
-    <row r="219" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C218" t="s">
+        <v>59</v>
+      </c>
+      <c r="D218" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E218" s="25">
+        <v>2</v>
+      </c>
+      <c r="F218" s="25">
+        <v>2</v>
+      </c>
+      <c r="G218" s="25" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="42.75">
+      <c r="A219" t="s">
+        <v>98</v>
+      </c>
       <c r="B219" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C219, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G219" s="14"/>
-    </row>
-    <row r="220" spans="2:7" hidden="1">
+        <v>ATO016</v>
+      </c>
+      <c r="C219" t="s">
+        <v>72</v>
+      </c>
+      <c r="D219" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E219" s="25">
+        <v>-5</v>
+      </c>
+      <c r="F219" s="25">
+        <v>4</v>
+      </c>
+      <c r="G219" s="25" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="28.5">
+      <c r="A220" t="s">
+        <v>98</v>
+      </c>
       <c r="B220" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C220, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G220" s="14"/>
-    </row>
-    <row r="221" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C220" t="s">
+        <v>57</v>
+      </c>
+      <c r="D220" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E220" s="25">
+        <v>-2</v>
+      </c>
+      <c r="F220" s="25">
+        <v>2</v>
+      </c>
+      <c r="G220" s="25" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" ht="28.5">
+      <c r="A221" t="s">
+        <v>98</v>
+      </c>
       <c r="B221" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C221, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G221" s="14"/>
-    </row>
-    <row r="222" spans="2:7" hidden="1">
+        <v>ATO007</v>
+      </c>
+      <c r="C221" t="s">
+        <v>59</v>
+      </c>
+      <c r="D221" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E221" s="25">
+        <v>-3</v>
+      </c>
+      <c r="F221" s="25">
+        <v>2</v>
+      </c>
+      <c r="G221" s="25" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" ht="28.5">
+      <c r="A222" t="s">
+        <v>99</v>
+      </c>
       <c r="B222" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C222, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G222" s="14"/>
-    </row>
-    <row r="223" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C222" t="s">
+        <v>52</v>
+      </c>
+      <c r="D222" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E222" s="25">
+        <v>1</v>
+      </c>
+      <c r="F222" s="25">
+        <v>1</v>
+      </c>
+      <c r="G222" s="25" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="42.75">
+      <c r="A223" t="s">
+        <v>99</v>
+      </c>
       <c r="B223" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C223, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G223" s="14"/>
-    </row>
-    <row r="224" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C223" t="s">
+        <v>63</v>
+      </c>
+      <c r="D223" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E223" s="25">
+        <v>2</v>
+      </c>
+      <c r="F223" s="25">
+        <v>2</v>
+      </c>
+      <c r="G223" s="25" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="42.75">
+      <c r="A224" t="s">
+        <v>99</v>
+      </c>
       <c r="B224" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C224, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G224" s="14"/>
-    </row>
-    <row r="225" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C224" t="s">
+        <v>64</v>
+      </c>
+      <c r="D224" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E224" s="25">
+        <v>2</v>
+      </c>
+      <c r="F224" s="25">
+        <v>2</v>
+      </c>
+      <c r="G224" s="25" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="28.5">
+      <c r="A225" t="s">
+        <v>99</v>
+      </c>
       <c r="B225" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C225, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G225" s="14"/>
-    </row>
-    <row r="226" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C225" t="s">
+        <v>51</v>
+      </c>
+      <c r="D225" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E225" s="25">
+        <v>1</v>
+      </c>
+      <c r="F225" s="25">
+        <v>1</v>
+      </c>
+      <c r="G225" s="25" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="28.5">
+      <c r="A226" t="s">
+        <v>99</v>
+      </c>
       <c r="B226" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C226, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G226" s="14"/>
-    </row>
-    <row r="227" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E226" s="25">
+        <v>1</v>
+      </c>
+      <c r="F226" s="25">
+        <v>1</v>
+      </c>
+      <c r="G226" s="25" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="28.5">
+      <c r="A227" t="s">
+        <v>99</v>
+      </c>
       <c r="B227" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C227, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G227" s="14"/>
-    </row>
-    <row r="228" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C227" t="s">
+        <v>69</v>
+      </c>
+      <c r="D227" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E227" s="25">
+        <v>3</v>
+      </c>
+      <c r="F227" s="25">
+        <v>2</v>
+      </c>
+      <c r="G227" s="25" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="228" spans="1:7" ht="28.5">
+      <c r="A228" t="s">
+        <v>99</v>
+      </c>
       <c r="B228" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C228, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G228" s="14"/>
-    </row>
-    <row r="229" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C228" t="s">
+        <v>52</v>
+      </c>
+      <c r="D228" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E228" s="25">
+        <v>6</v>
+      </c>
+      <c r="F228" s="25">
+        <v>5</v>
+      </c>
+      <c r="G228" s="25" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" ht="42.75">
+      <c r="A229" t="s">
+        <v>99</v>
+      </c>
       <c r="B229" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C229, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G229" s="14"/>
-    </row>
-    <row r="230" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C229" t="s">
+        <v>63</v>
+      </c>
+      <c r="D229" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E229" s="25">
+        <v>7</v>
+      </c>
+      <c r="F229" s="25">
+        <v>6</v>
+      </c>
+      <c r="G229" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="42.75">
+      <c r="A230" t="s">
+        <v>99</v>
+      </c>
       <c r="B230" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C230, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G230" s="14"/>
-    </row>
-    <row r="231" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C230" t="s">
+        <v>64</v>
+      </c>
+      <c r="D230" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E230" s="25">
+        <v>7</v>
+      </c>
+      <c r="F230" s="25">
+        <v>6</v>
+      </c>
+      <c r="G230" s="25" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="42.75">
+      <c r="A231" t="s">
+        <v>99</v>
+      </c>
       <c r="B231" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C231, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G231" s="14"/>
-    </row>
-    <row r="232" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C231" t="s">
+        <v>51</v>
+      </c>
+      <c r="D231" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E231" s="25">
+        <v>5</v>
+      </c>
+      <c r="F231" s="25">
+        <v>4</v>
+      </c>
+      <c r="G231" s="25" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" ht="42.75">
+      <c r="A232" t="s">
+        <v>99</v>
+      </c>
       <c r="B232" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C232, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G232" s="14"/>
-    </row>
-    <row r="233" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E232" s="25">
+        <v>5</v>
+      </c>
+      <c r="F232" s="25">
+        <v>4</v>
+      </c>
+      <c r="G232" s="25" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="42.75">
+      <c r="A233" t="s">
+        <v>99</v>
+      </c>
       <c r="B233" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C233, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G233" s="14"/>
-    </row>
-    <row r="234" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C233" t="s">
+        <v>69</v>
+      </c>
+      <c r="D233" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="E233" s="25">
+        <v>6</v>
+      </c>
+      <c r="F233" s="25">
+        <v>5</v>
+      </c>
+      <c r="G233" s="25" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="28.5">
+      <c r="A234" t="s">
+        <v>100</v>
+      </c>
       <c r="B234" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C234, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G234" s="14"/>
-    </row>
-    <row r="235" spans="2:7" hidden="1">
+        <v>ATO012</v>
+      </c>
+      <c r="C234" t="s">
+        <v>66</v>
+      </c>
+      <c r="D234" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E234" s="25">
+        <v>-10</v>
+      </c>
+      <c r="F234" s="25">
+        <v>7</v>
+      </c>
+      <c r="G234" s="25" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="28.5">
+      <c r="A235" t="s">
+        <v>100</v>
+      </c>
       <c r="B235" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C235, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G235" s="14"/>
-    </row>
-    <row r="236" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C235" t="s">
+        <v>69</v>
+      </c>
+      <c r="D235" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E235" s="25">
+        <v>-9</v>
+      </c>
+      <c r="F235" s="25">
+        <v>-8</v>
+      </c>
+      <c r="G235" s="25" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="28.5">
+      <c r="A236" t="s">
+        <v>100</v>
+      </c>
       <c r="B236" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C236, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G236" s="14"/>
-    </row>
-    <row r="237" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C236" t="s">
+        <v>52</v>
+      </c>
+      <c r="D236" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E236" s="25">
+        <v>-9</v>
+      </c>
+      <c r="F236" s="25">
+        <v>-8</v>
+      </c>
+      <c r="G236" s="25" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="28.5">
+      <c r="A237" t="s">
+        <v>100</v>
+      </c>
       <c r="B237" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C237, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G237" s="14"/>
-    </row>
-    <row r="238" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C237" t="s">
+        <v>63</v>
+      </c>
+      <c r="D237" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E237" s="25">
+        <v>-8</v>
+      </c>
+      <c r="F237" s="25">
+        <v>-7</v>
+      </c>
+      <c r="G237" s="25" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="28.5">
+      <c r="A238" t="s">
+        <v>100</v>
+      </c>
       <c r="B238" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C238, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G238" s="14"/>
-    </row>
-    <row r="239" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C238" t="s">
+        <v>64</v>
+      </c>
+      <c r="D238" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E238" s="25">
+        <v>-8</v>
+      </c>
+      <c r="F238" s="25">
+        <v>-7</v>
+      </c>
+      <c r="G238" s="25" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="42.75">
+      <c r="A239" t="s">
+        <v>100</v>
+      </c>
       <c r="B239" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C239, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G239" s="14"/>
-    </row>
-    <row r="240" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C239" t="s">
+        <v>51</v>
+      </c>
+      <c r="D239" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E239" s="25">
+        <v>-7</v>
+      </c>
+      <c r="F239" s="25">
+        <v>-6</v>
+      </c>
+      <c r="G239" s="25" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="42.75">
+      <c r="A240" t="s">
+        <v>100</v>
+      </c>
       <c r="B240" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C240, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G240" s="14"/>
-    </row>
-    <row r="241" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E240" s="25">
+        <v>-7</v>
+      </c>
+      <c r="F240" s="25">
+        <v>-6</v>
+      </c>
+      <c r="G240" s="25" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="241" spans="1:7" ht="42.75">
+      <c r="A241" t="s">
+        <v>100</v>
+      </c>
       <c r="B241" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C241, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G241" s="14"/>
-    </row>
-    <row r="242" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C241" t="s">
+        <v>57</v>
+      </c>
+      <c r="D241" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="E241" s="25">
+        <v>-6</v>
+      </c>
+      <c r="F241" s="25">
+        <v>-5</v>
+      </c>
+      <c r="G241" s="25" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="30">
+      <c r="A242" t="s">
+        <v>101</v>
+      </c>
       <c r="B242" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C242, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G242" s="14"/>
-    </row>
-    <row r="243" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C242" t="s">
+        <v>57</v>
+      </c>
+      <c r="D242" t="s">
+        <v>10</v>
+      </c>
+      <c r="E242">
+        <v>6</v>
+      </c>
+      <c r="F242">
+        <v>5</v>
+      </c>
+      <c r="G242" s="14" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="45">
+      <c r="A243" t="s">
+        <v>101</v>
+      </c>
       <c r="B243" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C243, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G243" s="14"/>
-    </row>
-    <row r="244" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C243" t="s">
+        <v>52</v>
+      </c>
+      <c r="D243" t="s">
+        <v>10</v>
+      </c>
+      <c r="E243">
+        <v>-7</v>
+      </c>
+      <c r="F243">
+        <v>-5</v>
+      </c>
+      <c r="G243" s="14" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="45">
+      <c r="A244" t="s">
+        <v>101</v>
+      </c>
       <c r="B244" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C244, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G244" s="14"/>
-    </row>
-    <row r="245" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>10</v>
+      </c>
+      <c r="E244">
+        <v>-9</v>
+      </c>
+      <c r="F244">
+        <v>6</v>
+      </c>
+      <c r="G244" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="245" spans="1:7" ht="45">
+      <c r="A245" t="s">
+        <v>101</v>
+      </c>
       <c r="B245" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C245, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G245" s="14"/>
-    </row>
-    <row r="246" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C245" t="s">
+        <v>51</v>
+      </c>
+      <c r="D245" t="s">
+        <v>10</v>
+      </c>
+      <c r="E245">
+        <v>-9</v>
+      </c>
+      <c r="F245">
+        <v>6</v>
+      </c>
+      <c r="G245" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="246" spans="1:7" ht="45">
+      <c r="A246" t="s">
+        <v>101</v>
+      </c>
       <c r="B246" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C246, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G246" s="14"/>
-    </row>
-    <row r="247" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C246" t="s">
+        <v>63</v>
+      </c>
+      <c r="D246" t="s">
+        <v>10</v>
+      </c>
+      <c r="E246">
+        <v>-9</v>
+      </c>
+      <c r="F246">
+        <v>6</v>
+      </c>
+      <c r="G246" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="45">
+      <c r="A247" t="s">
+        <v>101</v>
+      </c>
       <c r="B247" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C247, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G247" s="14"/>
-    </row>
-    <row r="248" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C247" t="s">
+        <v>64</v>
+      </c>
+      <c r="D247" t="s">
+        <v>10</v>
+      </c>
+      <c r="E247">
+        <v>-9</v>
+      </c>
+      <c r="F247">
+        <v>6</v>
+      </c>
+      <c r="G247" s="14" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="45">
+      <c r="A248" t="s">
+        <v>101</v>
+      </c>
       <c r="B248" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C248, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G248" s="14"/>
-    </row>
-    <row r="249" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C248" t="s">
+        <v>69</v>
+      </c>
+      <c r="D248" t="s">
+        <v>10</v>
+      </c>
+      <c r="E248">
+        <v>-8</v>
+      </c>
+      <c r="F248">
+        <v>3</v>
+      </c>
+      <c r="G248" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="30">
+      <c r="A249" t="s">
+        <v>101</v>
+      </c>
       <c r="B249" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C249, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G249" s="14"/>
-    </row>
-    <row r="250" spans="2:7" hidden="1">
+        <v>ATO006</v>
+      </c>
+      <c r="C249" t="s">
+        <v>57</v>
+      </c>
+      <c r="D249" t="s">
+        <v>14</v>
+      </c>
+      <c r="E249">
+        <v>-7</v>
+      </c>
+      <c r="F249">
+        <v>3</v>
+      </c>
+      <c r="G249" s="14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="30">
+      <c r="A250" t="s">
+        <v>101</v>
+      </c>
       <c r="B250" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C250, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G250" s="14"/>
-    </row>
-    <row r="251" spans="2:7" hidden="1">
+        <v>ATO003</v>
+      </c>
+      <c r="C250" t="s">
+        <v>52</v>
+      </c>
+      <c r="D250" t="s">
+        <v>14</v>
+      </c>
+      <c r="E250">
+        <v>-5</v>
+      </c>
+      <c r="F250">
+        <v>-3</v>
+      </c>
+      <c r="G250" s="14" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="45">
+      <c r="A251" t="s">
+        <v>101</v>
+      </c>
       <c r="B251" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C251, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G251" s="14"/>
-    </row>
-    <row r="252" spans="2:7" hidden="1">
+        <v>ATO014</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>14</v>
+      </c>
+      <c r="E251">
+        <v>-4</v>
+      </c>
+      <c r="F251">
+        <v>0</v>
+      </c>
+      <c r="G251" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="45">
+      <c r="A252" t="s">
+        <v>101</v>
+      </c>
       <c r="B252" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C252, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G252" s="14"/>
-    </row>
-    <row r="253" spans="2:7" hidden="1">
+        <v>ATO002</v>
+      </c>
+      <c r="C252" t="s">
+        <v>51</v>
+      </c>
+      <c r="D252" t="s">
+        <v>14</v>
+      </c>
+      <c r="E252">
+        <v>-4</v>
+      </c>
+      <c r="F252">
+        <v>0</v>
+      </c>
+      <c r="G252" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="253" spans="1:7" ht="45">
+      <c r="A253" t="s">
+        <v>101</v>
+      </c>
       <c r="B253" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C253, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G253" s="14"/>
-    </row>
-    <row r="254" spans="2:7" hidden="1">
+        <v>ATO009</v>
+      </c>
+      <c r="C253" t="s">
+        <v>63</v>
+      </c>
+      <c r="D253" t="s">
+        <v>14</v>
+      </c>
+      <c r="E253">
+        <v>-4</v>
+      </c>
+      <c r="F253">
+        <v>0</v>
+      </c>
+      <c r="G253" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="45">
+      <c r="A254" t="s">
+        <v>101</v>
+      </c>
       <c r="B254" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C254, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G254" s="14"/>
-    </row>
-    <row r="255" spans="2:7" hidden="1">
+        <v>ATO010</v>
+      </c>
+      <c r="C254" t="s">
+        <v>64</v>
+      </c>
+      <c r="D254" t="s">
+        <v>14</v>
+      </c>
+      <c r="E254">
+        <v>-4</v>
+      </c>
+      <c r="F254">
+        <v>0</v>
+      </c>
+      <c r="G254" s="14" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="30">
+      <c r="A255" t="s">
+        <v>101</v>
+      </c>
       <c r="B255" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C255, tblActors[nome], tblActors[actor_id], ""), "")</f>
-        <v/>
-      </c>
-      <c r="G255" s="14"/>
-    </row>
-    <row r="256" spans="2:7" hidden="1">
+        <v>ATO015</v>
+      </c>
+      <c r="C255" t="s">
+        <v>69</v>
+      </c>
+      <c r="D255" t="s">
+        <v>14</v>
+      </c>
+      <c r="E255">
+        <v>-3</v>
+      </c>
+      <c r="F255">
+        <v>0</v>
+      </c>
+      <c r="G255" s="14" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7">
       <c r="B256" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C256, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G256" s="14"/>
     </row>
-    <row r="257" spans="2:7" hidden="1">
+    <row r="257" spans="2:7">
       <c r="B257" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C257, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G257" s="14"/>
     </row>
-    <row r="258" spans="2:7" hidden="1">
+    <row r="258" spans="2:7">
       <c r="B258" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C258, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G258" s="14"/>
     </row>
-    <row r="259" spans="2:7" hidden="1">
+    <row r="259" spans="2:7">
       <c r="B259" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C259, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G259" s="14"/>
     </row>
-    <row r="260" spans="2:7" hidden="1">
+    <row r="260" spans="2:7">
       <c r="B260" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C260, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G260" s="14"/>
     </row>
-    <row r="261" spans="2:7" hidden="1">
+    <row r="261" spans="2:7">
       <c r="B261" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C261, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G261" s="14"/>
     </row>
-    <row r="262" spans="2:7" hidden="1">
+    <row r="262" spans="2:7">
       <c r="B262" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C262, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G262" s="14"/>
     </row>
-    <row r="263" spans="2:7" hidden="1">
+    <row r="263" spans="2:7">
       <c r="B263" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C263, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G263" s="14"/>
     </row>
-    <row r="264" spans="2:7" hidden="1">
+    <row r="264" spans="2:7">
       <c r="B264" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C264, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G264" s="14"/>
     </row>
-    <row r="265" spans="2:7" hidden="1">
+    <row r="265" spans="2:7">
       <c r="B265" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C265, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G265" s="14"/>
     </row>
-    <row r="266" spans="2:7" hidden="1">
+    <row r="266" spans="2:7">
       <c r="B266" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C266, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G266" s="14"/>
     </row>
-    <row r="267" spans="2:7" hidden="1">
+    <row r="267" spans="2:7">
       <c r="B267" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C267, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G267" s="14"/>
     </row>
-    <row r="268" spans="2:7" hidden="1">
+    <row r="268" spans="2:7">
       <c r="B268" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C268, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G268" s="14"/>
     </row>
-    <row r="269" spans="2:7" hidden="1">
+    <row r="269" spans="2:7">
       <c r="B269" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C269, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G269" s="14"/>
     </row>
-    <row r="270" spans="2:7" hidden="1">
+    <row r="270" spans="2:7">
       <c r="B270" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C270, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G270" s="14"/>
     </row>
-    <row r="271" spans="2:7" hidden="1">
+    <row r="271" spans="2:7">
       <c r="B271" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C271, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G271" s="14"/>
     </row>
-    <row r="272" spans="2:7" hidden="1">
+    <row r="272" spans="2:7">
       <c r="B272" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C272, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G272" s="14"/>
     </row>
-    <row r="273" spans="2:7" hidden="1">
+    <row r="273" spans="2:7">
       <c r="B273" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C273, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G273" s="14"/>
     </row>
-    <row r="274" spans="2:7" hidden="1">
+    <row r="274" spans="2:7">
       <c r="B274" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C274, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G274" s="14"/>
     </row>
-    <row r="275" spans="2:7" hidden="1">
+    <row r="275" spans="2:7">
       <c r="B275" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C275, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G275" s="14"/>
     </row>
-    <row r="276" spans="2:7" hidden="1">
+    <row r="276" spans="2:7">
       <c r="B276" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C276, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G276" s="14"/>
     </row>
-    <row r="277" spans="2:7" hidden="1">
+    <row r="277" spans="2:7">
       <c r="B277" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C277, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G277" s="14"/>
     </row>
-    <row r="278" spans="2:7" hidden="1">
+    <row r="278" spans="2:7">
       <c r="B278" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C278, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G278" s="14"/>
     </row>
-    <row r="279" spans="2:7" hidden="1">
+    <row r="279" spans="2:7">
       <c r="B279" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C279, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G279" s="14"/>
     </row>
-    <row r="280" spans="2:7" hidden="1">
+    <row r="280" spans="2:7">
       <c r="B280" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C280, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G280" s="14"/>
     </row>
-    <row r="281" spans="2:7" hidden="1">
+    <row r="281" spans="2:7">
       <c r="B281" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C281, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G281" s="14"/>
     </row>
-    <row r="282" spans="2:7" hidden="1">
+    <row r="282" spans="2:7">
       <c r="B282" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C282, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G282" s="14"/>
     </row>
-    <row r="283" spans="2:7" hidden="1">
+    <row r="283" spans="2:7">
       <c r="B283" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C283, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G283" s="14"/>
     </row>
-    <row r="284" spans="2:7" hidden="1">
+    <row r="284" spans="2:7">
       <c r="B284" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C284, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G284" s="14"/>
     </row>
-    <row r="285" spans="2:7" hidden="1">
+    <row r="285" spans="2:7">
       <c r="B285" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C285, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G285" s="14"/>
     </row>
-    <row r="286" spans="2:7" hidden="1">
+    <row r="286" spans="2:7">
       <c r="B286" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C286, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G286" s="14"/>
     </row>
-    <row r="287" spans="2:7" hidden="1">
+    <row r="287" spans="2:7">
       <c r="B287" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C287, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G287" s="14"/>
     </row>
-    <row r="288" spans="2:7" hidden="1">
+    <row r="288" spans="2:7">
       <c r="B288" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C288, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G288" s="14"/>
     </row>
-    <row r="289" spans="2:7" hidden="1">
+    <row r="289" spans="2:7">
       <c r="B289" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C289, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G289" s="14"/>
     </row>
-    <row r="290" spans="2:7" hidden="1">
+    <row r="290" spans="2:7">
       <c r="B290" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C290, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G290" s="14"/>
     </row>
-    <row r="291" spans="2:7" hidden="1">
+    <row r="291" spans="2:7">
       <c r="B291" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C291, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G291" s="14"/>
     </row>
-    <row r="292" spans="2:7" hidden="1">
+    <row r="292" spans="2:7">
       <c r="B292" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C292, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G292" s="14"/>
     </row>
-    <row r="293" spans="2:7" hidden="1">
+    <row r="293" spans="2:7">
       <c r="B293" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C293, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G293" s="14"/>
     </row>
-    <row r="294" spans="2:7" hidden="1">
+    <row r="294" spans="2:7">
       <c r="B294" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C294, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G294" s="14"/>
     </row>
-    <row r="295" spans="2:7" hidden="1">
+    <row r="295" spans="2:7">
       <c r="B295" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C295, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G295" s="14"/>
     </row>
-    <row r="296" spans="2:7" hidden="1">
+    <row r="296" spans="2:7">
       <c r="B296" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C296, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G296" s="14"/>
     </row>
-    <row r="297" spans="2:7" hidden="1">
+    <row r="297" spans="2:7">
       <c r="B297" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C297, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G297" s="14"/>
     </row>
-    <row r="298" spans="2:7" hidden="1">
+    <row r="298" spans="2:7">
       <c r="B298" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C298, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G298" s="14"/>
     </row>
-    <row r="299" spans="2:7" hidden="1">
+    <row r="299" spans="2:7">
       <c r="B299" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C299, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G299" s="14"/>
     </row>
-    <row r="300" spans="2:7" hidden="1">
+    <row r="300" spans="2:7">
       <c r="B300" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C300, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G300" s="14"/>
     </row>
-    <row r="301" spans="2:7" hidden="1">
+    <row r="301" spans="2:7">
       <c r="B301" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C301, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G301" s="14"/>
     </row>
-    <row r="302" spans="2:7" hidden="1">
+    <row r="302" spans="2:7">
       <c r="B302" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C302, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G302" s="14"/>
     </row>
-    <row r="303" spans="2:7" hidden="1">
+    <row r="303" spans="2:7">
       <c r="B303" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C303, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G303" s="14"/>
     </row>
-    <row r="304" spans="2:7" hidden="1">
+    <row r="304" spans="2:7">
       <c r="B304" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C304, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G304" s="14"/>
     </row>
-    <row r="305" spans="2:7" hidden="1">
+    <row r="305" spans="2:7">
       <c r="B305" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C305, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G305" s="14"/>
     </row>
-    <row r="306" spans="2:7" hidden="1">
+    <row r="306" spans="2:7">
       <c r="B306" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C306, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G306" s="14"/>
     </row>
-    <row r="307" spans="2:7" hidden="1">
+    <row r="307" spans="2:7">
       <c r="B307" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C307, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G307" s="14"/>
     </row>
-    <row r="308" spans="2:7" hidden="1">
+    <row r="308" spans="2:7">
       <c r="B308" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C308, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G308" s="14"/>
     </row>
-    <row r="309" spans="2:7" hidden="1">
+    <row r="309" spans="2:7">
       <c r="B309" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C309, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G309" s="14"/>
     </row>
-    <row r="310" spans="2:7" hidden="1">
+    <row r="310" spans="2:7">
       <c r="B310" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C310, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G310" s="14"/>
     </row>
-    <row r="311" spans="2:7" hidden="1">
+    <row r="311" spans="2:7">
       <c r="B311" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C311, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G311" s="14"/>
     </row>
-    <row r="312" spans="2:7" hidden="1">
+    <row r="312" spans="2:7">
       <c r="B312" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C312, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G312" s="14"/>
     </row>
-    <row r="313" spans="2:7" hidden="1">
+    <row r="313" spans="2:7">
       <c r="B313" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C313, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G313" s="14"/>
     </row>
-    <row r="314" spans="2:7" hidden="1">
+    <row r="314" spans="2:7">
       <c r="B314" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C314, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G314" s="14"/>
     </row>
-    <row r="315" spans="2:7" hidden="1">
+    <row r="315" spans="2:7">
       <c r="B315" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C315, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G315" s="14"/>
     </row>
-    <row r="316" spans="2:7" hidden="1">
+    <row r="316" spans="2:7">
       <c r="B316" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C316, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G316" s="14"/>
     </row>
-    <row r="317" spans="2:7" hidden="1">
+    <row r="317" spans="2:7">
       <c r="B317" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C317, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G317" s="14"/>
     </row>
-    <row r="318" spans="2:7" hidden="1">
+    <row r="318" spans="2:7">
       <c r="B318" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C318, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G318" s="14"/>
     </row>
-    <row r="319" spans="2:7" hidden="1">
+    <row r="319" spans="2:7">
       <c r="B319" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C319, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G319" s="14"/>
     </row>
-    <row r="320" spans="2:7" hidden="1">
+    <row r="320" spans="2:7">
       <c r="B320" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C320, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G320" s="14"/>
     </row>
-    <row r="321" spans="2:7" hidden="1">
+    <row r="321" spans="2:7">
       <c r="B321" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C321, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G321" s="14"/>
     </row>
-    <row r="322" spans="2:7" hidden="1">
+    <row r="322" spans="2:7">
       <c r="B322" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C322, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G322" s="14"/>
     </row>
-    <row r="323" spans="2:7" hidden="1">
+    <row r="323" spans="2:7">
       <c r="B323" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C323, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G323" s="14"/>
     </row>
-    <row r="324" spans="2:7" hidden="1">
+    <row r="324" spans="2:7">
       <c r="B324" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C324, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G324" s="14"/>
     </row>
-    <row r="325" spans="2:7" hidden="1">
+    <row r="325" spans="2:7">
       <c r="B325" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C325, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G325" s="14"/>
     </row>
-    <row r="326" spans="2:7" hidden="1">
+    <row r="326" spans="2:7">
       <c r="B326" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C326, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
       </c>
       <c r="G326" s="14"/>
     </row>
-    <row r="327" spans="2:7" hidden="1">
+    <row r="327" spans="2:7">
       <c r="B327" t="str">
         <f>IFERROR(_xlfn.XLOOKUP(C327, tblActors[nome], tblActors[actor_id], ""), "")</f>
         <v/>
